--- a/filtered_news/all_literature_reclassified_11cats.xlsx
+++ b/filtered_news/all_literature_reclassified_11cats.xlsx
@@ -3228,7 +3228,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S21"/>
+  <dimension ref="A1:S18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3508,13 +3508,13 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ClimeFi Publishes 2026 Insights On The Durable Carbon Removal Market</t>
+          <t>Impact of different carbon policies on integrated planning of hydrogen supply chain and power system</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://carbonherald.com/climefi-publishes-2026-insights-on-the-durable-carbon-removal-market/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=climefi-publishes-2026-insights-on-the-durable-carbon-removal-market</t>
+          <t>https://www.sciencedirect.com/science/article/pii/S0306261926001078?dgcid=rss_sd_all</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -3523,53 +3523,53 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.570215106010437</v>
+        <v>0.5597981214523315</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
-        <v>0.396820604801178</v>
+        <v>0.3529542684555054</v>
       </c>
       <c r="K5" t="n">
-        <v>0.352628231048584</v>
+        <v>0.2835289537906647</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3644706010818481</v>
+        <v>0.2475181668996811</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4871716201305389</v>
+        <v>0.2394848167896271</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3662385642528534</v>
+        <v>0.2598558068275452</v>
       </c>
       <c r="O5" t="n">
-        <v>0.42010697722435</v>
+        <v>0.1782487481832504</v>
       </c>
       <c r="P5" t="n">
-        <v>0.420903205871582</v>
+        <v>0.2976193726062775</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3836469948291779</v>
+        <v>0.4165871143341064</v>
       </c>
       <c r="R5" t="n">
-        <v>0.543264627456665</v>
+        <v>0.38028684258461</v>
       </c>
       <c r="S5" t="n">
-        <v>0.570215106010437</v>
+        <v>0.5597981214523315</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Impact of different carbon policies on integrated planning of hydrogen supply chain and power system</t>
+          <t>Policy-driven innovation pathways for strategic green technologies: The case of hydrogen and carbon capture, utilization, and storage (CCUS) in South Korea</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.sciencedirect.com/science/article/pii/S0306261926001078?dgcid=rss_sd_all</t>
+          <t>https://www.sciencedirect.com/science/article/pii/S0301421526001850?dgcid=rss_sd_all</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -3578,53 +3578,53 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.5597981214523315</v>
+        <v>0.5268201231956482</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
-        <v>0.3529542684555054</v>
+        <v>0.3144336342811584</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2835289537906647</v>
+        <v>0.2728826403617859</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2475181668996811</v>
+        <v>0.2500182092189789</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2394848167896271</v>
+        <v>0.2086189687252045</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2598558068275452</v>
+        <v>0.1981524974107742</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1782487481832504</v>
+        <v>0.1771543174982071</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2976193726062775</v>
+        <v>0.3143160939216614</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.4165871143341064</v>
+        <v>0.2573734521865845</v>
       </c>
       <c r="R6" t="n">
-        <v>0.38028684258461</v>
+        <v>0.3852896094322205</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5597981214523315</v>
+        <v>0.5268201231956482</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DP World Launches Carbon Inset Trial To Reduce Ocean Freight Emissions</t>
+          <t>Why China and Europe should collaborate to ‘defossilize’ the world’s carbon</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://carbonherald.com/dp-world-launches-carbon-inset-trial-to-reduce-ocean-freight-emissions/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=dp-world-launches-carbon-inset-trial-to-reduce-ocean-freight-emissions</t>
+          <t>https://www.nature.com/articles/d41586-026-00383-5</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -3633,53 +3633,53 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.5426489114761353</v>
+        <v>0.5153917074203491</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="n">
-        <v>0.2629168331623077</v>
+        <v>0.2821428179740906</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2522498667240143</v>
+        <v>0.2602448165416718</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2255542427301407</v>
+        <v>0.2741019129753113</v>
       </c>
       <c r="M7" t="n">
-        <v>0.241143986582756</v>
+        <v>0.3691781461238861</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2099184542894363</v>
+        <v>0.2373314201831818</v>
       </c>
       <c r="O7" t="n">
-        <v>0.284855991601944</v>
+        <v>0.2807146012783051</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3600887060165405</v>
+        <v>0.2988126277923584</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.3462141454219818</v>
+        <v>0.2515015304088593</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3592546284198761</v>
+        <v>0.4305571913719177</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5426489114761353</v>
+        <v>0.5153917074203491</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Policy-driven innovation pathways for strategic green technologies: The case of hydrogen and carbon capture, utilization, and storage (CCUS) in South Korea</t>
+          <t>Nanoconfined Multi‐Scale Metal Catalysts: Confinement‐Induced Geometric, Electronic, and Microenvironment Regulation for Selective Multi‑Electron CO2 Reduction</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.sciencedirect.com/science/article/pii/S0301421526001850?dgcid=rss_sd_all</t>
+          <t>https://advanced.onlinelibrary.wiley.com/doi/10.1002/aenm.70795?af=R</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -3688,53 +3688,65 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.5268201231956482</v>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
+        <v>0.5123154520988464</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>政策与产业化</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>policy_keywords</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="n">
-        <v>0.3144336342811584</v>
+        <v>0.4693675637245178</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2728826403617859</v>
+        <v>0.4507119059562683</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2500182092189789</v>
+        <v>0.5123154520988464</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2086189687252045</v>
+        <v>0.3035015165805817</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1981524974107742</v>
+        <v>0.3193438351154327</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1771543174982071</v>
+        <v>0.3725414276123047</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3143160939216614</v>
+        <v>0.2026843875646591</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.2573734521865845</v>
+        <v>0.3454430401325226</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3852896094322205</v>
+        <v>0.2122789472341537</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5268201231956482</v>
+        <v>0.2352246940135956</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Why China and Europe should collaborate to ‘defossilize’ the world’s carbon</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
+          <t>Too late for CCS and hydrogen</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Fifty years after carbon capture and storage (CCS) was commercialized, global capacity has reached just 0.09% of global emissions; even if installation rates immediately expand 10-fold, this will make no quantitatively important contribution to climate mitigation by 2050. Deployment of emission-free electricity generation is also constrained, so there will be no quantitatively important supply of hydrogen or negative-emission technologies by 2050 either, and climate policy must turn to other more achievable options. The bulk materials must be produced without process emissions, powered solely by emission-free electricity, within a constrained global electricity budget. Primary production of steel and paper can be fully electrified, although the electrical intensity of green hydrogen will constrain new steel processes. However, steel, aluminum, glass, plastic and potentially cement can all be recycled without emissions and with high efficiency. This reality should direct research toward improving the quality of recycled production, making better use of less material, and should be central to any advice given by academics to the policy community.</t>
+        </is>
+      </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.nature.com/articles/d41586-026-00383-5</t>
+          <t>https://www.nature.com/articles/s44286-025-00344-1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -3743,53 +3755,53 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.5153917074203491</v>
+        <v>0.4828121066093445</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="n">
-        <v>0.2821428179740906</v>
+        <v>0.354022353887558</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2602448165416718</v>
+        <v>0.3289662301540375</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2741019129753113</v>
+        <v>0.3373440206050873</v>
       </c>
       <c r="M9" t="n">
-        <v>0.3691781461238861</v>
+        <v>0.4155100584030151</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2373314201831818</v>
+        <v>0.2924463450908661</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2807146012783051</v>
+        <v>0.3558771312236786</v>
       </c>
       <c r="P9" t="n">
-        <v>0.2988126277923584</v>
+        <v>0.3384537994861603</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.2515015304088593</v>
+        <v>0.3281620442867279</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4305571913719177</v>
+        <v>0.4471813440322876</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5153917074203491</v>
+        <v>0.4828121066093445</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Nanoconfined Multi‐Scale Metal Catalysts: Confinement‐Induced Geometric, Electronic, and Microenvironment Regulation for Selective Multi‑Electron CO2 Reduction</t>
+          <t>Innovation or contraction? Unpacking the effects of carbon taxes and subsidies on emissions in Brazil</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://advanced.onlinelibrary.wiley.com/doi/10.1002/aenm.70795?af=R</t>
+          <t>https://www.sciencedirect.com/science/article/pii/S0301421526000297?dgcid=rss_sd_all</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -3798,65 +3810,57 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.5123154520988464</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>政策与产业化</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>policy_keywords</t>
-        </is>
-      </c>
+        <v>0.4758036434650421</v>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="n">
-        <v>0.4693675637245178</v>
+        <v>0.1912024468183517</v>
       </c>
       <c r="K10" t="n">
-        <v>0.4507119059562683</v>
+        <v>0.1525763273239136</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5123154520988464</v>
+        <v>0.1643282473087311</v>
       </c>
       <c r="M10" t="n">
-        <v>0.3035015165805817</v>
+        <v>0.253757506608963</v>
       </c>
       <c r="N10" t="n">
-        <v>0.3193438351154327</v>
+        <v>0.1720636039972305</v>
       </c>
       <c r="O10" t="n">
-        <v>0.3725414276123047</v>
+        <v>0.1665950864553452</v>
       </c>
       <c r="P10" t="n">
-        <v>0.2026843875646591</v>
+        <v>0.2272517532110214</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.3454430401325226</v>
+        <v>0.1653658300638199</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2122789472341537</v>
+        <v>0.4145342409610748</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2352246940135956</v>
+        <v>0.4758036434650421</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Too late for CCS and hydrogen</t>
+          <t>Unlocking Multi-Stage Flexibility Enables Cost-Competitive Hydrogen-Based Steelmaking in China</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Fifty years after carbon capture and storage (CCS) was commercialized, global capacity has reached just 0.09% of global emissions; even if installation rates immediately expand 10-fold, this will make no quantitatively important contribution to climate mitigation by 2050. Deployment of emission-free electricity generation is also constrained, so there will be no quantitatively important supply of hydrogen or negative-emission technologies by 2050 either, and climate policy must turn to other more achievable options. The bulk materials must be produced without process emissions, powered solely by emission-free electricity, within a constrained global electricity budget. Primary production of steel and paper can be fully electrified, although the electrical intensity of green hydrogen will constrain new steel processes. However, steel, aluminum, glass, plastic and potentially cement can all be recycled without emissions and with high efficiency. This reality should direct research toward improving the quality of recycled production, making better use of less material, and should be central to any advice given by academics to the policy community.</t>
+          <t>Addressing climate change requires decarbonizing the iron and steel industry, which accounts for about 7% of global CO₂ emissions. Hydrogen-based direct reduced iron with electric arc furnaces (H₂-DRI-EAF) emerges as a promising pathway, yet its economic viability hinges on effectively managing the variability of renewable energy. However, heterogeneous flexibility potentials across electricity, hydrogen, iron, and steel production, together with the distinct characteristics of intermediate product storage, make coordinated capacity investment highly complex. This study develops a system-level modeling framework for renewable-centric, multi-stage H₂-DRI-EAF that jointly optimizes capacity sizing and flexible operations across production stages under flexibility strategies in representative Chinese steelmaking cities. We find that fully deploying flexibility across all production stages could reduce the levelized cost of steel (LCOS) by 6–10% relative to baseline configurations relying on flexible electrolysis alone. By 2035, flexible H₂-DRI-EAF can achieve near cost parity with conventional steelmaking under moderate carbon pricing ($38 t⁻¹ CO₂) and 50% low-cost scrap addition. Flexibility systematically alters investment patterns through significantly reducing the required capacities of solar and energy storage while moderately inducing differentiated overcapacity in electrolyzers, DRI furnaces, and EAFs. For a 1 Mt yr⁻¹ H₂-DRI-EAF plant, renewable deployment exceeds 100 km²; a PV-only configuration halves the land footprint but raises LCOS by $5–64 t⁻¹. This study provides quantitative insights to support the scalable deployment of green steel pathways under high renewable penetration.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.nature.com/articles/s44286-025-00344-1</t>
+          <t>http://pubs.rsc.org/en/Content/ArticleLanding/2026/EE/D6EE00643D</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -3865,53 +3869,53 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.4828121066093445</v>
+        <v>0.4521330893039703</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="n">
-        <v>0.354022353887558</v>
+        <v>0.3247283399105072</v>
       </c>
       <c r="K11" t="n">
-        <v>0.3289662301540375</v>
+        <v>0.32675701379776</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3373440206050873</v>
+        <v>0.2928089201450348</v>
       </c>
       <c r="M11" t="n">
-        <v>0.4155100584030151</v>
+        <v>0.2280701845884323</v>
       </c>
       <c r="N11" t="n">
-        <v>0.2924463450908661</v>
+        <v>0.2701369225978851</v>
       </c>
       <c r="O11" t="n">
-        <v>0.3558771312236786</v>
+        <v>0.1722106337547302</v>
       </c>
       <c r="P11" t="n">
-        <v>0.3384537994861603</v>
+        <v>0.2293830662965775</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.3281620442867279</v>
+        <v>0.3483736515045166</v>
       </c>
       <c r="R11" t="n">
-        <v>0.4471813440322876</v>
+        <v>0.3856188654899597</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4828121066093445</v>
+        <v>0.4521330893039703</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Carbon Centric’s Kirkenær BECCS Project Successfully Advances Towards Certification</t>
+          <t>Energy policy strategies for cleaner production: The roles of renewable energy and green innovation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://carbonherald.com/carbon-centrics-kirkenaer-beccs-project-successfully-advances-towards-certification/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=carbon-centrics-kirkenaer-beccs-project-successfully-advances-towards-certification</t>
+          <t>https://www.sciencedirect.com/science/article/pii/S0301421526001485?dgcid=rss_sd_all</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -3920,53 +3924,53 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.4787318110466003</v>
+        <v>0.4425559937953949</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="n">
-        <v>0.2066167443990707</v>
+        <v>0.2600087821483612</v>
       </c>
       <c r="K12" t="n">
-        <v>0.2985424995422363</v>
+        <v>0.1649389863014221</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2628288269042969</v>
+        <v>0.2494099140167236</v>
       </c>
       <c r="M12" t="n">
-        <v>0.3317215442657471</v>
+        <v>0.1825735419988632</v>
       </c>
       <c r="N12" t="n">
-        <v>0.2188104838132858</v>
+        <v>0.2717984318733215</v>
       </c>
       <c r="O12" t="n">
-        <v>0.2618997991085052</v>
+        <v>0.1719227433204651</v>
       </c>
       <c r="P12" t="n">
-        <v>0.3697130084037781</v>
+        <v>0.2122164219617844</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.311633288860321</v>
+        <v>0.25140380859375</v>
       </c>
       <c r="R12" t="n">
-        <v>0.3695617020130157</v>
+        <v>0.3550816476345062</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4787318110466003</v>
+        <v>0.4425559937953949</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Innovation or contraction? Unpacking the effects of carbon taxes and subsidies on emissions in Brazil</t>
+          <t>Energy optimization for data centers via carbon-aware multi-energy market coordination</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.sciencedirect.com/science/article/pii/S0301421526000297?dgcid=rss_sd_all</t>
+          <t>https://www.sciencedirect.com/science/article/pii/S0306261926000231?dgcid=rss_sd_all</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -3975,57 +3979,53 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.4758036434650421</v>
+        <v>0.4401353895664215</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="n">
-        <v>0.1912024468183517</v>
+        <v>0.2853460609912872</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1525763273239136</v>
+        <v>0.2619348168373108</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1643282473087311</v>
+        <v>0.2105976194143295</v>
       </c>
       <c r="M13" t="n">
-        <v>0.253757506608963</v>
+        <v>0.3255856335163116</v>
       </c>
       <c r="N13" t="n">
-        <v>0.1720636039972305</v>
+        <v>0.2161763608455658</v>
       </c>
       <c r="O13" t="n">
-        <v>0.1665950864553452</v>
+        <v>0.1738513112068176</v>
       </c>
       <c r="P13" t="n">
-        <v>0.2272517532110214</v>
+        <v>0.3137782216072083</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.1653658300638199</v>
+        <v>0.3676945269107819</v>
       </c>
       <c r="R13" t="n">
-        <v>0.4145342409610748</v>
+        <v>0.3861423134803772</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4758036434650421</v>
+        <v>0.4401353895664215</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Unlocking Multi-Stage Flexibility Enables Cost-Competitive Hydrogen-Based Steelmaking in China</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Addressing climate change requires decarbonizing the iron and steel industry, which accounts for about 7% of global CO₂ emissions. Hydrogen-based direct reduced iron with electric arc furnaces (H₂-DRI-EAF) emerges as a promising pathway, yet its economic viability hinges on effectively managing the variability of renewable energy. However, heterogeneous flexibility potentials across electricity, hydrogen, iron, and steel production, together with the distinct characteristics of intermediate product storage, make coordinated capacity investment highly complex. This study develops a system-level modeling framework for renewable-centric, multi-stage H₂-DRI-EAF that jointly optimizes capacity sizing and flexible operations across production stages under flexibility strategies in representative Chinese steelmaking cities. We find that fully deploying flexibility across all production stages could reduce the levelized cost of steel (LCOS) by 6–10% relative to baseline configurations relying on flexible electrolysis alone. By 2035, flexible H₂-DRI-EAF can achieve near cost parity with conventional steelmaking under moderate carbon pricing ($38 t⁻¹ CO₂) and 50% low-cost scrap addition. Flexibility systematically alters investment patterns through significantly reducing the required capacities of solar and energy storage while moderately inducing differentiated overcapacity in electrolyzers, DRI furnaces, and EAFs. For a 1 Mt yr⁻¹ H₂-DRI-EAF plant, renewable deployment exceeds 100 km²; a PV-only configuration halves the land footprint but raises LCOS by $5–64 t⁻¹. This study provides quantitative insights to support the scalable deployment of green steel pathways under high renewable penetration.</t>
-        </is>
-      </c>
+          <t>A fair and low-carbon V2G scheduling framework based on carbon-economic contracts and fulfillment-aware dispatch</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>http://pubs.rsc.org/en/Content/ArticleLanding/2026/EE/D6EE00643D</t>
+          <t>https://www.sciencedirect.com/science/article/pii/S0306261926001224?dgcid=rss_sd_all</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -4034,53 +4034,53 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.4521330893039703</v>
+        <v>0.4395878612995148</v>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="n">
-        <v>0.3247283399105072</v>
+        <v>0.2293173968791962</v>
       </c>
       <c r="K14" t="n">
-        <v>0.32675701379776</v>
+        <v>0.2668124437332153</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2928089201450348</v>
+        <v>0.2477942109107971</v>
       </c>
       <c r="M14" t="n">
-        <v>0.2280701845884323</v>
+        <v>0.320143461227417</v>
       </c>
       <c r="N14" t="n">
-        <v>0.2701369225978851</v>
+        <v>0.2854484617710114</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1722106337547302</v>
+        <v>0.2374722212553024</v>
       </c>
       <c r="P14" t="n">
-        <v>0.2293830662965775</v>
+        <v>0.2927966117858887</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.3483736515045166</v>
+        <v>0.3096142411231995</v>
       </c>
       <c r="R14" t="n">
-        <v>0.3856188654899597</v>
+        <v>0.3509569466114044</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4521330893039703</v>
+        <v>0.4395878612995148</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Energy policy strategies for cleaner production: The roles of renewable energy and green innovation</t>
+          <t>The EU carbon border adjustment mechanism: Does it impact the competitiveness of China's export trade?</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://www.sciencedirect.com/science/article/pii/S0301421526001485?dgcid=rss_sd_all</t>
+          <t>https://www.sciencedirect.com/science/article/pii/S0301421526000959?dgcid=rss_sd_all</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -4089,53 +4089,53 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.4425559937953949</v>
+        <v>0.4359561502933502</v>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
-        <v>0.2600087821483612</v>
+        <v>0.1605668812990189</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1649389863014221</v>
+        <v>0.2374075502157211</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2494099140167236</v>
+        <v>0.2756598889827728</v>
       </c>
       <c r="M15" t="n">
-        <v>0.1825735419988632</v>
+        <v>0.2680164873600006</v>
       </c>
       <c r="N15" t="n">
-        <v>0.2717984318733215</v>
+        <v>0.1868060827255249</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1719227433204651</v>
+        <v>0.2137974053621292</v>
       </c>
       <c r="P15" t="n">
-        <v>0.2122164219617844</v>
+        <v>0.2226813435554504</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.25140380859375</v>
+        <v>0.2438400834798813</v>
       </c>
       <c r="R15" t="n">
-        <v>0.3550816476345062</v>
+        <v>0.3597668707370758</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4425559937953949</v>
+        <v>0.4359561502933502</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Energy optimization for data centers via carbon-aware multi-energy market coordination</t>
+          <t>Optimizing economy-energy-environment (3Es) policy mixes for decarbonization: Synergies, trade-offs, and regional implementation in China</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://www.sciencedirect.com/science/article/pii/S0306261926000231?dgcid=rss_sd_all</t>
+          <t>https://www.sciencedirect.com/science/article/pii/S0301421526001072?dgcid=rss_sd_all</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -4144,53 +4144,53 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.4401353895664215</v>
+        <v>0.4337338209152222</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="n">
-        <v>0.2853460609912872</v>
+        <v>0.1778945028781891</v>
       </c>
       <c r="K16" t="n">
-        <v>0.2619348168373108</v>
+        <v>0.2398143261671066</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2105976194143295</v>
+        <v>0.1514323204755783</v>
       </c>
       <c r="M16" t="n">
-        <v>0.3255856335163116</v>
+        <v>0.1950347870588303</v>
       </c>
       <c r="N16" t="n">
-        <v>0.2161763608455658</v>
+        <v>0.1388393193483353</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1738513112068176</v>
+        <v>0.126801609992981</v>
       </c>
       <c r="P16" t="n">
-        <v>0.3137782216072083</v>
+        <v>0.1190654560923576</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.3676945269107819</v>
+        <v>0.2586649656295776</v>
       </c>
       <c r="R16" t="n">
-        <v>0.3861423134803772</v>
+        <v>0.3811448812484741</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4401353895664215</v>
+        <v>0.4337338209152222</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A fair and low-carbon V2G scheduling framework based on carbon-economic contracts and fulfillment-aware dispatch</t>
+          <t>Two-layer coordinated operation of multi-energy system considering carbon-oriented collaborative pricing mechanism via two-stage stochastic programming approach</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://www.sciencedirect.com/science/article/pii/S0306261926001224?dgcid=rss_sd_all</t>
+          <t>https://www.sciencedirect.com/science/article/pii/S0306261925020288?dgcid=rss_sd_all</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -4199,53 +4199,53 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.4395878612995148</v>
+        <v>0.4334600865840912</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="n">
-        <v>0.2293173968791962</v>
+        <v>0.2940990030765533</v>
       </c>
       <c r="K17" t="n">
-        <v>0.2668124437332153</v>
+        <v>0.3437499403953552</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2477942109107971</v>
+        <v>0.2976899147033691</v>
       </c>
       <c r="M17" t="n">
-        <v>0.320143461227417</v>
+        <v>0.2638961374759674</v>
       </c>
       <c r="N17" t="n">
-        <v>0.2854484617710114</v>
+        <v>0.2695200145244598</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2374722212553024</v>
+        <v>0.180839791893959</v>
       </c>
       <c r="P17" t="n">
-        <v>0.2927966117858887</v>
+        <v>0.2238616049289703</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.3096142411231995</v>
+        <v>0.3166567087173462</v>
       </c>
       <c r="R17" t="n">
-        <v>0.3509569466114044</v>
+        <v>0.3709921538829803</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4395878612995148</v>
+        <v>0.4334600865840912</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>The EU carbon border adjustment mechanism: Does it impact the competitiveness of China's export trade?</t>
+          <t>The decline of fossil fuels and the search for viable alternatives: A critical review of biodiesel, electric, and biogas energy systems under global socio-political and technical constraints</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://www.sciencedirect.com/science/article/pii/S0301421526000959?dgcid=rss_sd_all</t>
+          <t>https://www.sciencedirect.com/science/article/pii/S0306261926002990?dgcid=rss_sd_all</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -4254,205 +4254,40 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.4359561502933502</v>
+        <v>0.4303023815155029</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="n">
-        <v>0.1605668812990189</v>
+        <v>0.2585082650184631</v>
       </c>
       <c r="K18" t="n">
-        <v>0.2374075502157211</v>
+        <v>0.3364328444004059</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2756598889827728</v>
+        <v>0.3143483996391296</v>
       </c>
       <c r="M18" t="n">
-        <v>0.2680164873600006</v>
+        <v>0.2595475614070892</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1868060827255249</v>
+        <v>0.3741083443164825</v>
       </c>
       <c r="O18" t="n">
-        <v>0.2137974053621292</v>
+        <v>0.1958951950073242</v>
       </c>
       <c r="P18" t="n">
-        <v>0.2226813435554504</v>
+        <v>0.2684126794338226</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.2438400834798813</v>
+        <v>0.2857156991958618</v>
       </c>
       <c r="R18" t="n">
-        <v>0.3597668707370758</v>
+        <v>0.3948679864406586</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4359561502933502</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Optimizing economy-energy-environment (3Es) policy mixes for decarbonization: Synergies, trade-offs, and regional implementation in China</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>https://www.sciencedirect.com/science/article/pii/S0301421526001072?dgcid=rss_sd_all</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>政策与产业化</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>0.4337338209152222</v>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="n">
-        <v>0.1778945028781891</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0.2398143261671066</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0.1514323204755783</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0.1950347870588303</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0.1388393193483353</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0.126801609992981</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0.1190654560923576</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0.2586649656295776</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0.3811448812484741</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0.4337338209152222</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Two-layer coordinated operation of multi-energy system considering carbon-oriented collaborative pricing mechanism via two-stage stochastic programming approach</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>https://www.sciencedirect.com/science/article/pii/S0306261925020288?dgcid=rss_sd_all</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>政策与产业化</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>0.4334600865840912</v>
-      </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="n">
-        <v>0.2940990030765533</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0.3437499403953552</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0.2976899147033691</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0.2638961374759674</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0.2695200145244598</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0.180839791893959</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0.2238616049289703</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0.3166567087173462</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0.3709921538829803</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0.4334600865840912</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>The decline of fossil fuels and the search for viable alternatives: A critical review of biodiesel, electric, and biogas energy systems under global socio-political and technical constraints</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>https://www.sciencedirect.com/science/article/pii/S0306261926002990?dgcid=rss_sd_all</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>政策与产业化</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>0.4303023815155029</v>
-      </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="n">
-        <v>0.2585082650184631</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0.3364328444004059</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0.3143483996391296</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0.2595475614070892</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0.3741083443164825</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0.1958951950073242</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0.2684126794338226</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0.2857156991958618</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0.3948679864406586</v>
-      </c>
-      <c r="S21" t="n">
         <v>0.4303023815155029</v>
       </c>
     </row>
@@ -4467,7 +4302,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S88"/>
+  <dimension ref="A1:S86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5604,13 +5439,13 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BURN Secures Nigeria’s Authorization To Sell Carbon Credits To CORSIA</t>
+          <t>Optimization of hydrogen supply operations for decarbonizing energy-intensive industries: A multi-timescale rolling horizon approach</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://carbonherald.com/burn-secures-nigerias-authorization-to-sell-carbon-credits-to-corsia/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=burn-secures-nigerias-authorization-to-sell-carbon-credits-to-corsia</t>
+          <t>https://www.sciencedirect.com/science/article/pii/S0306261926003843?dgcid=rss_sd_all</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -5619,53 +5454,57 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.3757350444793701</v>
+        <v>0.3746091425418854</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="n">
-        <v>0.2978591620922089</v>
+        <v>0.2865710556507111</v>
       </c>
       <c r="K20" t="n">
-        <v>0.3612282872200012</v>
+        <v>0.2622427642345428</v>
       </c>
       <c r="L20" t="n">
-        <v>0.3141746819019318</v>
+        <v>0.2248470187187195</v>
       </c>
       <c r="M20" t="n">
-        <v>0.3701478242874146</v>
+        <v>0.1390183717012405</v>
       </c>
       <c r="N20" t="n">
-        <v>0.3210085928440094</v>
+        <v>0.2027392089366913</v>
       </c>
       <c r="O20" t="n">
-        <v>0.3553363680839539</v>
+        <v>0.1026576906442642</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2714496552944183</v>
+        <v>0.1545259803533554</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.301957756280899</v>
+        <v>0.3746091425418854</v>
       </c>
       <c r="R20" t="n">
-        <v>0.2970605790615082</v>
+        <v>0.2905342876911163</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3757350444793701</v>
+        <v>0.3652403354644775</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Optimization of hydrogen supply operations for decarbonizing energy-intensive industries: A multi-timescale rolling horizon approach</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
+          <t>Millennial land carbon emissions in China offset by carbon sinks of the past four decades</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>China experienced substantial millennial-scale climate and anthropogenic land use changes, yet their combined impacts on land carbon dynamics remain largely unexamined. Here, we quantify spatiotemporal changes in terrestrial organic carbon over 851–2022 using a land surface model driven by reconstructed climate and land cover forcings. Simulated results show China’s pre-industrial millennial land carbon dynamics aligned with global carbon stock and atmospheric CO2 fluctuations, such as the ~284 ppm peak in the 12th century linked to land use during the Medieval Climate Anomaly-warmed Song Dynasty. Notably, China’s total land carbon emissions (13 ± 0.5 PgC) accounted for 22% of global land carbon emissions during 1700–1900, with Northeast and Southwest China experiencing the largest historical land carbon losses from intensive deforestation. Nevertheless, the 17.0 ± 1.7 PgC emissions during 851–1980 were fully offset by rapid carbon sinks over 1980–2022, driven by CO2 fertilization and large-scale afforestation. These findings provide insights into China’s historical land carbon dynamics, their underlying drivers, and global implications.</t>
+        </is>
+      </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://www.sciencedirect.com/science/article/pii/S0306261926003843?dgcid=rss_sd_all</t>
+          <t>https://www.nature.com/articles/s41467-026-70049-3</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -5674,57 +5513,53 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.3746091425418854</v>
+        <v>0.374101996421814</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="n">
-        <v>0.2865710556507111</v>
+        <v>0.2590482831001282</v>
       </c>
       <c r="K21" t="n">
-        <v>0.2622427642345428</v>
+        <v>0.2305388897657394</v>
       </c>
       <c r="L21" t="n">
-        <v>0.2248470187187195</v>
+        <v>0.1843396723270416</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1390183717012405</v>
+        <v>0.3237777352333069</v>
       </c>
       <c r="N21" t="n">
-        <v>0.2027392089366913</v>
+        <v>0.2290011048316956</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1026576906442642</v>
+        <v>0.2874977886676788</v>
       </c>
       <c r="P21" t="n">
-        <v>0.1545259803533554</v>
+        <v>0.2695263028144836</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.3746091425418854</v>
+        <v>0.2158897519111633</v>
       </c>
       <c r="R21" t="n">
-        <v>0.2905342876911163</v>
+        <v>0.3723159730434418</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3652403354644775</v>
+        <v>0.374101996421814</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Millennial land carbon emissions in China offset by carbon sinks of the past four decades</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>China experienced substantial millennial-scale climate and anthropogenic land use changes, yet their combined impacts on land carbon dynamics remain largely unexamined. Here, we quantify spatiotemporal changes in terrestrial organic carbon over 851–2022 using a land surface model driven by reconstructed climate and land cover forcings. Simulated results show China’s pre-industrial millennial land carbon dynamics aligned with global carbon stock and atmospheric CO2 fluctuations, such as the ~284 ppm peak in the 12th century linked to land use during the Medieval Climate Anomaly-warmed Song Dynasty. Notably, China’s total land carbon emissions (13 ± 0.5 PgC) accounted for 22% of global land carbon emissions during 1700–1900, with Northeast and Southwest China experiencing the largest historical land carbon losses from intensive deforestation. Nevertheless, the 17.0 ± 1.7 PgC emissions during 851–1980 were fully offset by rapid carbon sinks over 1980–2022, driven by CO2 fertilization and large-scale afforestation. These findings provide insights into China’s historical land carbon dynamics, their underlying drivers, and global implications.</t>
-        </is>
-      </c>
+          <t>Imputing unjustified bulk density values to soils with biochar addition biases soil carbon sequestration estimates</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://www.nature.com/articles/s41467-026-70049-3</t>
+          <t>https://www.pnas.org/doi/abs/10.1073/pnas.2528257123?mi=eymic2&amp;af=R&amp;access=on&amp;content=articlesChapters&amp;publication=pnas&amp;sortBy=Earliest&amp;target=default</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -5733,53 +5568,57 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.374101996421814</v>
+        <v>0.3740656673908234</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="n">
-        <v>0.2590482831001282</v>
+        <v>0.06642290204763412</v>
       </c>
       <c r="K22" t="n">
-        <v>0.2305388897657394</v>
+        <v>0.06858353316783905</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1843396723270416</v>
+        <v>0.0783829465508461</v>
       </c>
       <c r="M22" t="n">
-        <v>0.3237777352333069</v>
+        <v>0.3031059205532074</v>
       </c>
       <c r="N22" t="n">
-        <v>0.2290011048316956</v>
+        <v>0.1884581744670868</v>
       </c>
       <c r="O22" t="n">
-        <v>0.2874977886676788</v>
+        <v>0.2004041075706482</v>
       </c>
       <c r="P22" t="n">
-        <v>0.2695263028144836</v>
+        <v>0.3740656673908234</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.2158897519111633</v>
+        <v>0.1504422575235367</v>
       </c>
       <c r="R22" t="n">
-        <v>0.3723159730434418</v>
+        <v>0.2214814722537994</v>
       </c>
       <c r="S22" t="n">
-        <v>0.374101996421814</v>
+        <v>0.3135522603988647</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Imputing unjustified bulk density values to soils with biochar addition biases soil carbon sequestration estimates</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
+          <t>Quaternary Carbon Centers via Electrochemical Direct Dehydroxylative Alkylation</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Abstract The construction of all‐carbon quaternary centers remains a formidable challenge in organic synthesis due to the steric congestion and limited accessibility of suitable precursors. Herein, we report a modular electrochemical strategy for the direct dehydroxylative alkylation of tertiary alcohols via a polar‐to‐radical transduction mechanism. This unified activation platform enables C(sp 3 )─C(sp 3 ) bond formation with electron‐deficient alkenes and benzyl chlorides, employing readily available reagents under mild, operationally simple conditions. Key to this transformation is the use of halide‐based reagents that mediate Lewis acid‐promoted C─OH bond cleavage while enabling subsequent radical generation via cathodic reduction. The method exhibits broad substrate scope, including complex and functionalized tertiary alcohols, diverse Michael acceptors, and sterically hindered coupling partners. It is further applicable to the late‐stage modification of bioactive molecules and scalable synthesis. Mechanistic studies support the involvement of both carbocation and carbon radical intermediates, validating the effectiveness of this dual‐mode strategy. This work provides a general and practical approach to quaternary carbon construction from unactivated tertiary alcohols, expanding the synthetic toolbox for C(sp 3 )─C(sp 3 ) bond formation.</t>
+        </is>
+      </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://www.pnas.org/doi/abs/10.1073/pnas.2528257123?mi=eymic2&amp;af=R&amp;access=on&amp;content=articlesChapters&amp;publication=pnas&amp;sortBy=Earliest&amp;target=default</t>
+          <t>https://onlinelibrary.wiley.com/doi/10.1002/anie.202520816?af=R</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -5788,57 +5627,57 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.3740656673908234</v>
+        <v>0.3730997741222382</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="n">
-        <v>0.06642290204763412</v>
+        <v>0.2753382623195648</v>
       </c>
       <c r="K23" t="n">
-        <v>0.06858353316783905</v>
+        <v>0.2576480805873871</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0783829465508461</v>
+        <v>0.3730997741222382</v>
       </c>
       <c r="M23" t="n">
-        <v>0.3031059205532074</v>
+        <v>0.204716369509697</v>
       </c>
       <c r="N23" t="n">
-        <v>0.1884581744670868</v>
+        <v>0.302416056394577</v>
       </c>
       <c r="O23" t="n">
-        <v>0.2004041075706482</v>
+        <v>0.2260400354862213</v>
       </c>
       <c r="P23" t="n">
-        <v>0.3740656673908234</v>
+        <v>0.03860605880618095</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.1504422575235367</v>
+        <v>0.1913462728261948</v>
       </c>
       <c r="R23" t="n">
-        <v>0.2214814722537994</v>
+        <v>0.1021685302257538</v>
       </c>
       <c r="S23" t="n">
-        <v>0.3135522603988647</v>
+        <v>0.1794845759868622</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Quaternary Carbon Centers via Electrochemical Direct Dehydroxylative Alkylation</t>
+          <t>Lanthanum‐Induced Gradient Fields in Asymmetric Heterointerface Catalysts for Enhanced Oxygen Electrocatalysis</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Abstract The construction of all‐carbon quaternary centers remains a formidable challenge in organic synthesis due to the steric congestion and limited accessibility of suitable precursors. Herein, we report a modular electrochemical strategy for the direct dehydroxylative alkylation of tertiary alcohols via a polar‐to‐radical transduction mechanism. This unified activation platform enables C(sp 3 )─C(sp 3 ) bond formation with electron‐deficient alkenes and benzyl chlorides, employing readily available reagents under mild, operationally simple conditions. Key to this transformation is the use of halide‐based reagents that mediate Lewis acid‐promoted C─OH bond cleavage while enabling subsequent radical generation via cathodic reduction. The method exhibits broad substrate scope, including complex and functionalized tertiary alcohols, diverse Michael acceptors, and sterically hindered coupling partners. It is further applicable to the late‐stage modification of bioactive molecules and scalable synthesis. Mechanistic studies support the involvement of both carbocation and carbon radical intermediates, validating the effectiveness of this dual‐mode strategy. This work provides a general and practical approach to quaternary carbon construction from unactivated tertiary alcohols, expanding the synthetic toolbox for C(sp 3 )─C(sp 3 ) bond formation.</t>
+          <t>Abstract Metal‐nitrogen‐carbon (M‐N‐C) catalysts display considerable potential as cost‐effective alternatives to noble metals in oxygen electrocatalysis. However, uncontrolled atomic migration and random structural rearrangement during pyrolysis often lead to disordered coordination environments and sparse active sites, fundamentally limiting their intrinsic catalytic activities and long‐term durability. Herein, a novel strategy is reported for use in directionally regulating atomic migration pathways via the incorporation of a foreign metal (La). By exploiting the differences in the atomic migration priorities via the Kirkendall effect, directional control of atomic diffusion is achieved to fabricate a well‐defined asymmetric multiphase heterointerface catalyst (LaN/LaFe‐NC). The presence of high‐density, structurally well‐defined active sites – along with a built‐in directional electric field across the heterointerface – substantially enhances the efficiency of interfacial charge transport, thus improving the intrinsic activity and stability in oxygen electrocatalysis. When incorporated into a rechargeable Zn‐air battery, LaN/LaFe‐NC delivers a high power density of 211 mW cm −2 , with an exceptional cycling stability of &amp;gt;240 h. This study establishes a generalizable atomic‐level design strategy for use in engineering robust heterointerface catalysts and offers valuable insights for application in advancing next‐generation renewable energy conversion and storage systems.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://onlinelibrary.wiley.com/doi/10.1002/anie.202520816?af=R</t>
+          <t>https://advanced.onlinelibrary.wiley.com/doi/10.1002/adma.202511117?af=R</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5847,57 +5686,57 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.3730997741222382</v>
+        <v>0.3681514263153076</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="n">
-        <v>0.2753382623195648</v>
+        <v>0.3299074172973633</v>
       </c>
       <c r="K24" t="n">
-        <v>0.2576480805873871</v>
+        <v>0.234417200088501</v>
       </c>
       <c r="L24" t="n">
-        <v>0.3730997741222382</v>
+        <v>0.3681514263153076</v>
       </c>
       <c r="M24" t="n">
-        <v>0.204716369509697</v>
+        <v>0.1768877059221268</v>
       </c>
       <c r="N24" t="n">
-        <v>0.302416056394577</v>
+        <v>0.2188163101673126</v>
       </c>
       <c r="O24" t="n">
-        <v>0.2260400354862213</v>
+        <v>0.2383786886930466</v>
       </c>
       <c r="P24" t="n">
-        <v>0.03860605880618095</v>
+        <v>0.1210604906082153</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.1913462728261948</v>
+        <v>0.1935160160064697</v>
       </c>
       <c r="R24" t="n">
-        <v>0.1021685302257538</v>
+        <v>0.1358908265829086</v>
       </c>
       <c r="S24" t="n">
-        <v>0.1794845759868622</v>
+        <v>0.156982347369194</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Lanthanum‐Induced Gradient Fields in Asymmetric Heterointerface Catalysts for Enhanced Oxygen Electrocatalysis</t>
+          <t>Coupled geomorphic and climate-driven biogeochemical processes regulate soil organic carbon stocks in agricultural terraces</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Abstract Metal‐nitrogen‐carbon (M‐N‐C) catalysts display considerable potential as cost‐effective alternatives to noble metals in oxygen electrocatalysis. However, uncontrolled atomic migration and random structural rearrangement during pyrolysis often lead to disordered coordination environments and sparse active sites, fundamentally limiting their intrinsic catalytic activities and long‐term durability. Herein, a novel strategy is reported for use in directionally regulating atomic migration pathways via the incorporation of a foreign metal (La). By exploiting the differences in the atomic migration priorities via the Kirkendall effect, directional control of atomic diffusion is achieved to fabricate a well‐defined asymmetric multiphase heterointerface catalyst (LaN/LaFe‐NC). The presence of high‐density, structurally well‐defined active sites – along with a built‐in directional electric field across the heterointerface – substantially enhances the efficiency of interfacial charge transport, thus improving the intrinsic activity and stability in oxygen electrocatalysis. When incorporated into a rechargeable Zn‐air battery, LaN/LaFe‐NC delivers a high power density of 211 mW cm −2 , with an exceptional cycling stability of &amp;gt;240 h. This study establishes a generalizable atomic‐level design strategy for use in engineering robust heterointerface catalysts and offers valuable insights for application in advancing next‐generation renewable energy conversion and storage systems.</t>
+          <t>Agricultural terraces are among the most widespread human-made landforms. They profoundly reshape soil landscapes and influence the carbon cycle, yet the extent and drivers of their impact remain highly uncertain. By integrating field observations from 14 well-drained terrace landforms across a climatic-geochemical gradient with a data synthesis, we show that changes in soil organic carbon (SOC) stocks after terracing are governed by two coupled C turnover-geomorphic processes: replacement of lost topsoil C at eroding positions and stabilization of buried SOC at depositional positions. Climate strongly modulates these processes by shaping soil geochemistry and plant productivity, which in turn control SOC replacement and stabilization within terraces. Thus, terracing effects on SOC stocks shift from consistently positive in humid regions to mixed (positive and negative) outcomes in dry regions. This study establishes a framework for elucidating SOC dynamics in well-drained terrace systems and provides a scientific basis for targeted management strategies to enhance C sequestration in agricultural terraces globally.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://advanced.onlinelibrary.wiley.com/doi/10.1002/adma.202511117?af=R</t>
+          <t>https://www.science.org/doi/abs/10.1126/sciadv.aea8560?af=R</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5906,57 +5745,57 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.3681514263153076</v>
+        <v>0.3653692007064819</v>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="n">
-        <v>0.3299074172973633</v>
+        <v>0.255673885345459</v>
       </c>
       <c r="K25" t="n">
-        <v>0.234417200088501</v>
+        <v>0.1569070518016815</v>
       </c>
       <c r="L25" t="n">
-        <v>0.3681514263153076</v>
+        <v>0.1478928178548813</v>
       </c>
       <c r="M25" t="n">
-        <v>0.1768877059221268</v>
+        <v>0.3653692007064819</v>
       </c>
       <c r="N25" t="n">
-        <v>0.2188163101673126</v>
+        <v>0.2430629730224609</v>
       </c>
       <c r="O25" t="n">
-        <v>0.2383786886930466</v>
+        <v>0.2592366337776184</v>
       </c>
       <c r="P25" t="n">
-        <v>0.1210604906082153</v>
+        <v>0.3643072545528412</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.1935160160064697</v>
+        <v>0.1705301553010941</v>
       </c>
       <c r="R25" t="n">
-        <v>0.1358908265829086</v>
+        <v>0.2453699707984924</v>
       </c>
       <c r="S25" t="n">
-        <v>0.156982347369194</v>
+        <v>0.3000662326812744</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Coupled geomorphic and climate-driven biogeochemical processes regulate soil organic carbon stocks in agricultural terraces</t>
+          <t>MOF‐Derived High‐Entropy Biphasic Sulfides for Zn‐I2‐S Synergistic Batteries with Machine‐Learning‐Assisted Prediction and In Situ Synchrotron Spectroscopy</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Agricultural terraces are among the most widespread human-made landforms. They profoundly reshape soil landscapes and influence the carbon cycle, yet the extent and drivers of their impact remain highly uncertain. By integrating field observations from 14 well-drained terrace landforms across a climatic-geochemical gradient with a data synthesis, we show that changes in soil organic carbon (SOC) stocks after terracing are governed by two coupled C turnover-geomorphic processes: replacement of lost topsoil C at eroding positions and stabilization of buried SOC at depositional positions. Climate strongly modulates these processes by shaping soil geochemistry and plant productivity, which in turn control SOC replacement and stabilization within terraces. Thus, terracing effects on SOC stocks shift from consistently positive in humid regions to mixed (positive and negative) outcomes in dry regions. This study establishes a framework for elucidating SOC dynamics in well-drained terrace systems and provides a scientific basis for targeted management strategies to enhance C sequestration in agricultural terraces globally.</t>
+          <t>ABSTRACT The practical application of aqueous zinc batteries remains constrained by the intrinsic limitations of monocomponent systems, such as the shuttle effect in Zn‐I 2 batteries and the sluggish kinetics in Zn─S batteries. To overcome these limitations, we developed a Zn‐S‐I 2 synergistic battery that synergistically exploits the complementary advantages of dual redox couples. A bifunctional high‐entropy sulfide (HES) catalyst anchored on N‐doped carbon nanosheets was engineered via a surfactant‐assisted metal‐organic framework (MOF) derivatization route. The entropy‐stabilized HES forms a unique wurtzite/zincblende biphasic structure, creating abundant grain boundaries and synergistic active sites. Electrochemical studies demonstrate that the synergistic battery exhibits outstanding electrochemical performance and cycling stability. Machine learning (ML) models were established to predict electrochemical behavior under various operating conditions. Operando synchrotron‐based spectroscopy combined with theoretical calculations revealed that the biphasic HES synergistically catalyzes multi‐step conversion reactions, simultaneously lowering energy barriers and suppressing shuttle effects. This work offers new insights into high‐entropy electrocatalysts for complex multi‐step energy storage reactions.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://www.science.org/doi/abs/10.1126/sciadv.aea8560?af=R</t>
+          <t>https://advanced.onlinelibrary.wiley.com/doi/10.1002/adma.202523371?af=R</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5965,57 +5804,53 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.3653692007064819</v>
+        <v>0.3623897433280945</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="n">
-        <v>0.255673885345459</v>
+        <v>0.3373323976993561</v>
       </c>
       <c r="K26" t="n">
-        <v>0.1569070518016815</v>
+        <v>0.2930814623832703</v>
       </c>
       <c r="L26" t="n">
-        <v>0.1478928178548813</v>
+        <v>0.3623897433280945</v>
       </c>
       <c r="M26" t="n">
-        <v>0.3653692007064819</v>
+        <v>0.2155590057373047</v>
       </c>
       <c r="N26" t="n">
-        <v>0.2430629730224609</v>
+        <v>0.276935338973999</v>
       </c>
       <c r="O26" t="n">
-        <v>0.2592366337776184</v>
+        <v>0.2704308927059174</v>
       </c>
       <c r="P26" t="n">
-        <v>0.3643072545528412</v>
+        <v>0.1649534404277802</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.1705301553010941</v>
+        <v>0.2344474494457245</v>
       </c>
       <c r="R26" t="n">
-        <v>0.2453699707984924</v>
+        <v>0.1518922746181488</v>
       </c>
       <c r="S26" t="n">
-        <v>0.3000662326812744</v>
+        <v>0.1612250953912735</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>MOF‐Derived High‐Entropy Biphasic Sulfides for Zn‐I2‐S Synergistic Batteries with Machine‐Learning‐Assisted Prediction and In Situ Synchrotron Spectroscopy</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>ABSTRACT The practical application of aqueous zinc batteries remains constrained by the intrinsic limitations of monocomponent systems, such as the shuttle effect in Zn‐I 2 batteries and the sluggish kinetics in Zn─S batteries. To overcome these limitations, we developed a Zn‐S‐I 2 synergistic battery that synergistically exploits the complementary advantages of dual redox couples. A bifunctional high‐entropy sulfide (HES) catalyst anchored on N‐doped carbon nanosheets was engineered via a surfactant‐assisted metal‐organic framework (MOF) derivatization route. The entropy‐stabilized HES forms a unique wurtzite/zincblende biphasic structure, creating abundant grain boundaries and synergistic active sites. Electrochemical studies demonstrate that the synergistic battery exhibits outstanding electrochemical performance and cycling stability. Machine learning (ML) models were established to predict electrochemical behavior under various operating conditions. Operando synchrotron‐based spectroscopy combined with theoretical calculations revealed that the biphasic HES synergistically catalyzes multi‐step conversion reactions, simultaneously lowering energy barriers and suppressing shuttle effects. This work offers new insights into high‐entropy electrocatalysts for complex multi‐step energy storage reactions.</t>
-        </is>
-      </c>
+          <t>Energy-system optimization for hydrogen-based green steel production from medium-grade iron ore</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://advanced.onlinelibrary.wiley.com/doi/10.1002/adma.202523371?af=R</t>
+          <t>https://www.sciencedirect.com/science/article/pii/S0306261926002151?dgcid=rss_sd_all</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -6024,53 +5859,57 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.3623897433280945</v>
+        <v>0.3612125217914581</v>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="n">
-        <v>0.3373323976993561</v>
+        <v>0.3612125217914581</v>
       </c>
       <c r="K27" t="n">
-        <v>0.2930814623832703</v>
+        <v>0.3277168273925781</v>
       </c>
       <c r="L27" t="n">
-        <v>0.3623897433280945</v>
+        <v>0.2977233529090881</v>
       </c>
       <c r="M27" t="n">
-        <v>0.2155590057373047</v>
+        <v>0.3072916269302368</v>
       </c>
       <c r="N27" t="n">
-        <v>0.276935338973999</v>
+        <v>0.2644420862197876</v>
       </c>
       <c r="O27" t="n">
-        <v>0.2704308927059174</v>
+        <v>0.1588450074195862</v>
       </c>
       <c r="P27" t="n">
-        <v>0.1649534404277802</v>
+        <v>0.188843846321106</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.2344474494457245</v>
+        <v>0.3154664039611816</v>
       </c>
       <c r="R27" t="n">
-        <v>0.1518922746181488</v>
+        <v>0.2559088468551636</v>
       </c>
       <c r="S27" t="n">
-        <v>0.1612250953912735</v>
+        <v>0.2496501803398132</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Energy-system optimization for hydrogen-based green steel production from medium-grade iron ore</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr"/>
+          <t>Transition-metal-free electrochemical cross-electrophile coupling of activated benzyl alcohols and primary alkyl bromides</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Cross-electrophile coupling (XEC) has emerged as a powerful strategy for constructing carbon─carbon bonds. Here, we report the first transition-metal-free electrochemical XEC between readily available benzyl alcohol derivatives and primary alkyl bromides, enabling the efficient construction of C(sp 3 )─C(sp 3 ) bonds to access valuable benzylic quaternary and tertiary carbon centers. This method expands the reaction profiles of both benzyl alcohols and electrochemistry. A key to unlocking this transformation is the identification of 4- tert -butylbenzoyl (TBBz) as an effective activating group for benzyl alcohols. This modular protocol features broad substrate scope, compatibility with CO 2 and chlorosilanes as coupling partners, and is amenable to gram-scale synthesis. The synthetic utility of this method is exemplified by the simplified synthesis of high-value commercial building blocks and advanced intermediates for bioactive compounds, as well as the facile access to bioisosteric analogs of drug molecules.</t>
+        </is>
+      </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://www.sciencedirect.com/science/article/pii/S0306261926002151?dgcid=rss_sd_all</t>
+          <t>https://www.science.org/doi/abs/10.1126/sciadv.aeb3720?af=R</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -6079,57 +5918,53 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.3612125217914581</v>
+        <v>0.3610813021659851</v>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="n">
-        <v>0.3612125217914581</v>
+        <v>0.2253213226795197</v>
       </c>
       <c r="K28" t="n">
-        <v>0.3277168273925781</v>
+        <v>0.184800997376442</v>
       </c>
       <c r="L28" t="n">
-        <v>0.2977233529090881</v>
+        <v>0.3610813021659851</v>
       </c>
       <c r="M28" t="n">
-        <v>0.3072916269302368</v>
+        <v>0.09392640739679337</v>
       </c>
       <c r="N28" t="n">
-        <v>0.2644420862197876</v>
+        <v>0.2622015476226807</v>
       </c>
       <c r="O28" t="n">
-        <v>0.1588450074195862</v>
+        <v>0.2279926687479019</v>
       </c>
       <c r="P28" t="n">
-        <v>0.188843846321106</v>
+        <v>0.03713621571660042</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.3154664039611816</v>
+        <v>0.1762492507696152</v>
       </c>
       <c r="R28" t="n">
-        <v>0.2559088468551636</v>
+        <v>0.1441168636083603</v>
       </c>
       <c r="S28" t="n">
-        <v>0.2496501803398132</v>
+        <v>0.1318343877792358</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Transition-metal-free electrochemical cross-electrophile coupling of activated benzyl alcohols and primary alkyl bromides</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Cross-electrophile coupling (XEC) has emerged as a powerful strategy for constructing carbon─carbon bonds. Here, we report the first transition-metal-free electrochemical XEC between readily available benzyl alcohol derivatives and primary alkyl bromides, enabling the efficient construction of C(sp 3 )─C(sp 3 ) bonds to access valuable benzylic quaternary and tertiary carbon centers. This method expands the reaction profiles of both benzyl alcohols and electrochemistry. A key to unlocking this transformation is the identification of 4- tert -butylbenzoyl (TBBz) as an effective activating group for benzyl alcohols. This modular protocol features broad substrate scope, compatibility with CO 2 and chlorosilanes as coupling partners, and is amenable to gram-scale synthesis. The synthetic utility of this method is exemplified by the simplified synthesis of high-value commercial building blocks and advanced intermediates for bioactive compounds, as well as the facile access to bioisosteric analogs of drug molecules.</t>
-        </is>
-      </c>
+          <t>Emission trading scheme reshapes the decarbonisation pathways of China's power sector</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://www.science.org/doi/abs/10.1126/sciadv.aeb3720?af=R</t>
+          <t>https://www.sciencedirect.com/science/article/pii/S0306261926003788?dgcid=rss_sd_all</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6138,53 +5973,57 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.3610813021659851</v>
+        <v>0.3610729277133942</v>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="n">
-        <v>0.2253213226795197</v>
+        <v>0.1319659203290939</v>
       </c>
       <c r="K29" t="n">
-        <v>0.184800997376442</v>
+        <v>0.1902054697275162</v>
       </c>
       <c r="L29" t="n">
-        <v>0.3610813021659851</v>
+        <v>0.1530309915542603</v>
       </c>
       <c r="M29" t="n">
-        <v>0.09392640739679337</v>
+        <v>0.1189483851194382</v>
       </c>
       <c r="N29" t="n">
-        <v>0.2622015476226807</v>
+        <v>0.1094591096043587</v>
       </c>
       <c r="O29" t="n">
-        <v>0.2279926687479019</v>
+        <v>0.1493438482284546</v>
       </c>
       <c r="P29" t="n">
-        <v>0.03713621571660042</v>
+        <v>0.1281545460224152</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.1762492507696152</v>
+        <v>0.2167919278144836</v>
       </c>
       <c r="R29" t="n">
-        <v>0.1441168636083603</v>
+        <v>0.3094412386417389</v>
       </c>
       <c r="S29" t="n">
-        <v>0.1318343877792358</v>
+        <v>0.3610729277133942</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Emission trading scheme reshapes the decarbonisation pathways of China's power sector</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr"/>
+          <t>Selective Upcycling of Polycarbonate Waste to Cyclohexanol via RuLa Dual‐Atom Catalysis</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>ABSTRACT Cyclohexanol is a key intermediate for nylon manufacture, yet its industrial synthesis relies on partial oxidation of cyclohexane at ∼2 MPa with &amp;lt;5% single‐pass conversion, an energetically wasteful and atom‐inefficient process that demands extensive recycle and generates substantial emissions. Here, we introduce an oxygen‐atom‐efficient synthetic strategy that transforms polycarbonate (PC) waste directly into cyclohexanol through a non‐oxidative catalytic route. The method leverages the intrinsic oxygen functionality of the polymer as a built‐in source of hydroxyl groups, thereby eliminating the conventional oxidation step. A RuLa dual‐atom (RuLa‐DA) catalyst anchored on CoAl oxide enables cooperative hydrogen activation and spillover through moderated Ru–H binding, driving selective aromatic‐ring hydrogenation under mild gas‐phase conditions. Operating at 0.25 MPa and a 4.2 s residence time, the tandem hydropyrolysis–hydrogenation process affords a 69.9% yield and 95.4% selectivity for cyclohexanol, maintaining &amp;gt;95% selectivity for post‐consumer PC over 100 feed cycles. Life‐cycle and techno‐economic analyses indicate the potential environmental and economic advantages, showing a 35% cost reduction and a threefold lower carbon footprint relative to the fossil route. This oxygen‐retentive hydrogenation paradigm establishes a general approach for valorizing oxygen‐rich substrates and suggests a conceptually viable pathway toward atom‐economical synthesis and circular chemical manufacturing.</t>
+        </is>
+      </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>https://www.sciencedirect.com/science/article/pii/S0306261926003788?dgcid=rss_sd_all</t>
+          <t>https://onlinelibrary.wiley.com/doi/10.1002/anie.202524681?af=R</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6193,57 +6032,57 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.3610729277133942</v>
+        <v>0.3604544997215271</v>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="n">
-        <v>0.1319659203290939</v>
+        <v>0.3604544997215271</v>
       </c>
       <c r="K30" t="n">
-        <v>0.1902054697275162</v>
+        <v>0.338040679693222</v>
       </c>
       <c r="L30" t="n">
-        <v>0.1530309915542603</v>
+        <v>0.3269653022289276</v>
       </c>
       <c r="M30" t="n">
-        <v>0.1189483851194382</v>
+        <v>0.214959129691124</v>
       </c>
       <c r="N30" t="n">
-        <v>0.1094591096043587</v>
+        <v>0.2323064059019089</v>
       </c>
       <c r="O30" t="n">
-        <v>0.1493438482284546</v>
+        <v>0.2567310929298401</v>
       </c>
       <c r="P30" t="n">
-        <v>0.1281545460224152</v>
+        <v>0.1218976229429245</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.2167919278144836</v>
+        <v>0.1986588835716248</v>
       </c>
       <c r="R30" t="n">
-        <v>0.3094412386417389</v>
+        <v>0.1841015666723251</v>
       </c>
       <c r="S30" t="n">
-        <v>0.3610729277133942</v>
+        <v>0.1951326280832291</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Selective Upcycling of Polycarbonate Waste to Cyclohexanol via RuLa Dual‐Atom Catalysis</t>
+          <t>Dual‐Metal Synergy in Sn‐Sb‐CNF Membrane Anodes Boosts Electro‐Filtration Oxidation of Emerging Contaminants</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ABSTRACT Cyclohexanol is a key intermediate for nylon manufacture, yet its industrial synthesis relies on partial oxidation of cyclohexane at ∼2 MPa with &amp;lt;5% single‐pass conversion, an energetically wasteful and atom‐inefficient process that demands extensive recycle and generates substantial emissions. Here, we introduce an oxygen‐atom‐efficient synthetic strategy that transforms polycarbonate (PC) waste directly into cyclohexanol through a non‐oxidative catalytic route. The method leverages the intrinsic oxygen functionality of the polymer as a built‐in source of hydroxyl groups, thereby eliminating the conventional oxidation step. A RuLa dual‐atom (RuLa‐DA) catalyst anchored on CoAl oxide enables cooperative hydrogen activation and spillover through moderated Ru–H binding, driving selective aromatic‐ring hydrogenation under mild gas‐phase conditions. Operating at 0.25 MPa and a 4.2 s residence time, the tandem hydropyrolysis–hydrogenation process affords a 69.9% yield and 95.4% selectivity for cyclohexanol, maintaining &amp;gt;95% selectivity for post‐consumer PC over 100 feed cycles. Life‐cycle and techno‐economic analyses indicate the potential environmental and economic advantages, showing a 35% cost reduction and a threefold lower carbon footprint relative to the fossil route. This oxygen‐retentive hydrogenation paradigm establishes a general approach for valorizing oxygen‐rich substrates and suggests a conceptually viable pathway toward atom‐economical synthesis and circular chemical manufacturing.</t>
+          <t>Abstract Emerging contaminants, including pharmaceutical and personal care products (PPCPs), pose significant threats to aquatic ecosystems and human health. This study demonstrates efficient electrochemical oxidation of PPCPs using a novel tin‐antimony doped carbon nanofiber membrane (Sn‐Sb‐CNF) anode leveraging dual‐metal synergy. Oxygen vacancies generated through this synergistic effect function as active sites, enhancing pollutant adsorption capacity and oxidant activation capability. The degradation mechanism proceeds primarily via dominant hydroxyl radical ( • OH) generation, leading to complete contaminant mineralization. Notably, Sn/Sb dual‐metal doping modulates the electronic structure, altering the d‐band center from −4.777 to −2.175 eV and significantly lowering reaction energy barriers. This electronic optimization facilitates electron transfer kinetics and accelerates pollutant degradation. Owing to this synergy, the Sn‐Sb‐CNF anode achieved high removal efficiencies (&amp;gt;90%) within 30 min for multiple PPCPs: ofloxacin (95%), enrofloxacin (91%), carbamazepine (90%), acetaminophen (82%), and ibuprofen (96%). Furthermore, the membrane exhibits potent antimicrobial activity, achieving 4‐log inactivation of tetracycline‐resistant Escherichia coli and 5‐log reduction of T7 bacteriophage within 30 min. In real wastewater containing antibiotic‐resistant bacteria from a treatment plant, the system attained 62% mineralization rate. This work establishes a dual‐metal synergy strategy that provides new avenues for efficient PPCP elimination in complex aqueous matrices.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>https://onlinelibrary.wiley.com/doi/10.1002/anie.202524681?af=R</t>
+          <t>https://advanced.onlinelibrary.wiley.com/doi/10.1002/adma.202512066?af=R</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6252,57 +6091,53 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.3604544997215271</v>
+        <v>0.3584416508674622</v>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="n">
-        <v>0.3604544997215271</v>
+        <v>0.2529509663581848</v>
       </c>
       <c r="K31" t="n">
-        <v>0.338040679693222</v>
+        <v>0.127617210149765</v>
       </c>
       <c r="L31" t="n">
-        <v>0.3269653022289276</v>
+        <v>0.3336505591869354</v>
       </c>
       <c r="M31" t="n">
-        <v>0.214959129691124</v>
+        <v>0.1825208812952042</v>
       </c>
       <c r="N31" t="n">
-        <v>0.2323064059019089</v>
+        <v>0.2436193078756332</v>
       </c>
       <c r="O31" t="n">
-        <v>0.2567310929298401</v>
+        <v>0.3584416508674622</v>
       </c>
       <c r="P31" t="n">
-        <v>0.1218976229429245</v>
+        <v>0.219718724489212</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.1986588835716248</v>
+        <v>0.2681414186954498</v>
       </c>
       <c r="R31" t="n">
-        <v>0.1841015666723251</v>
+        <v>0.09837063401937485</v>
       </c>
       <c r="S31" t="n">
-        <v>0.1951326280832291</v>
+        <v>0.1553592681884766</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Dual‐Metal Synergy in Sn‐Sb‐CNF Membrane Anodes Boosts Electro‐Filtration Oxidation of Emerging Contaminants</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Abstract Emerging contaminants, including pharmaceutical and personal care products (PPCPs), pose significant threats to aquatic ecosystems and human health. This study demonstrates efficient electrochemical oxidation of PPCPs using a novel tin‐antimony doped carbon nanofiber membrane (Sn‐Sb‐CNF) anode leveraging dual‐metal synergy. Oxygen vacancies generated through this synergistic effect function as active sites, enhancing pollutant adsorption capacity and oxidant activation capability. The degradation mechanism proceeds primarily via dominant hydroxyl radical ( • OH) generation, leading to complete contaminant mineralization. Notably, Sn/Sb dual‐metal doping modulates the electronic structure, altering the d‐band center from −4.777 to −2.175 eV and significantly lowering reaction energy barriers. This electronic optimization facilitates electron transfer kinetics and accelerates pollutant degradation. Owing to this synergy, the Sn‐Sb‐CNF anode achieved high removal efficiencies (&amp;gt;90%) within 30 min for multiple PPCPs: ofloxacin (95%), enrofloxacin (91%), carbamazepine (90%), acetaminophen (82%), and ibuprofen (96%). Furthermore, the membrane exhibits potent antimicrobial activity, achieving 4‐log inactivation of tetracycline‐resistant Escherichia coli and 5‐log reduction of T7 bacteriophage within 30 min. In real wastewater containing antibiotic‐resistant bacteria from a treatment plant, the system attained 62% mineralization rate. This work establishes a dual‐metal synergy strategy that provides new avenues for efficient PPCP elimination in complex aqueous matrices.</t>
-        </is>
-      </c>
+          <t>How do Indian states fare in electricity decarbonization? A consumption-based decomposition analysis at subnational level</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
-          <t>https://advanced.onlinelibrary.wiley.com/doi/10.1002/adma.202512066?af=R</t>
+          <t>https://www.sciencedirect.com/science/article/pii/S0301421526001473?dgcid=rss_sd_all</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6311,53 +6146,57 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.3584416508674622</v>
+        <v>0.3528234362602234</v>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="n">
-        <v>0.2529509663581848</v>
+        <v>0.1017529517412186</v>
       </c>
       <c r="K32" t="n">
-        <v>0.127617210149765</v>
+        <v>0.1646056771278381</v>
       </c>
       <c r="L32" t="n">
-        <v>0.3336505591869354</v>
+        <v>0.1466772556304932</v>
       </c>
       <c r="M32" t="n">
-        <v>0.1825208812952042</v>
+        <v>0.07596547156572342</v>
       </c>
       <c r="N32" t="n">
-        <v>0.2436193078756332</v>
+        <v>0.07928614318370819</v>
       </c>
       <c r="O32" t="n">
-        <v>0.3584416508674622</v>
+        <v>0.1207266300916672</v>
       </c>
       <c r="P32" t="n">
-        <v>0.219718724489212</v>
+        <v>0.03051304444670677</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.2681414186954498</v>
+        <v>0.1505586057901382</v>
       </c>
       <c r="R32" t="n">
-        <v>0.09837063401937485</v>
+        <v>0.3528234362602234</v>
       </c>
       <c r="S32" t="n">
-        <v>0.1553592681884766</v>
+        <v>0.2882726788520813</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>How do Indian states fare in electricity decarbonization? A consumption-based decomposition analysis at subnational level</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr"/>
+          <t>Molecularly Engineered Cellulose: the Next-Generation Sustainable Polymer Electrolyte Materials</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Growing environmental imperatives are driving the need to substitute petroleum-derived materials with renewable and sustainable alternatives to enable the production of biodegradable and carbon-neutral products. As a naturally abundant and versatile biopolymer, cellulose has been extensively utilized in conventional industries such as papermaking and textiles, and is increasingly being applied in emerging advanced fields, including energy storage, food technology, emulsions, coatings, cosmetics, and biomedical applications. With the iteration and development of energy technology, cellulose-mediated polymer electrolyte materials (PEMs) have re-emerged as the materials of notable scientific and commercial communities due to their exceptional performance advantages in electrochemical energy storage. In this review, we comprehensively summarize and analyze the molecule engineering strategies, key features, and the corresponding construction strategies utilizing cellulose for the preparation of novel PEMs. Particularly, we provide a material and structural perspective how the ion conductivity, ion selectivity, anti-swelling property, self-healing property, flame retardancy, porosity, mechanical property, and photoelectric stability of cellulose-mediated PEMs can be regulated through molecular chemistry. Finally, we examine the potential of these strategies in advancing circular economy principles and environmental sustainability objectives, while also identifying key challenges and outlining promising future research directions. We emphasize the critical need for advanced molecular-level chemical engineering to fully harness the potential of cellulose for energy-related applications.</t>
+        </is>
+      </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>https://www.sciencedirect.com/science/article/pii/S0301421526001473?dgcid=rss_sd_all</t>
+          <t>http://pubs.rsc.org/en/Content/ArticleLanding/2026/EE/D5EE05398F</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6366,57 +6205,53 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.3528234362602234</v>
+        <v>0.3481834232807159</v>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="n">
-        <v>0.1017529517412186</v>
+        <v>0.2368689328432083</v>
       </c>
       <c r="K33" t="n">
-        <v>0.1646056771278381</v>
+        <v>0.1554520577192307</v>
       </c>
       <c r="L33" t="n">
-        <v>0.1466772556304932</v>
+        <v>0.3481834232807159</v>
       </c>
       <c r="M33" t="n">
-        <v>0.07596547156572342</v>
+        <v>0.2474187016487122</v>
       </c>
       <c r="N33" t="n">
-        <v>0.07928614318370819</v>
+        <v>0.2809361219406128</v>
       </c>
       <c r="O33" t="n">
-        <v>0.1207266300916672</v>
+        <v>0.3151056468486786</v>
       </c>
       <c r="P33" t="n">
-        <v>0.03051304444670677</v>
+        <v>0.0795421376824379</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.1505586057901382</v>
+        <v>0.2233236283063889</v>
       </c>
       <c r="R33" t="n">
-        <v>0.3528234362602234</v>
+        <v>0.09470903873443604</v>
       </c>
       <c r="S33" t="n">
-        <v>0.2882726788520813</v>
+        <v>0.1183729320764542</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Molecularly Engineered Cellulose: the Next-Generation Sustainable Polymer Electrolyte Materials</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Growing environmental imperatives are driving the need to substitute petroleum-derived materials with renewable and sustainable alternatives to enable the production of biodegradable and carbon-neutral products. As a naturally abundant and versatile biopolymer, cellulose has been extensively utilized in conventional industries such as papermaking and textiles, and is increasingly being applied in emerging advanced fields, including energy storage, food technology, emulsions, coatings, cosmetics, and biomedical applications. With the iteration and development of energy technology, cellulose-mediated polymer electrolyte materials (PEMs) have re-emerged as the materials of notable scientific and commercial communities due to their exceptional performance advantages in electrochemical energy storage. In this review, we comprehensively summarize and analyze the molecule engineering strategies, key features, and the corresponding construction strategies utilizing cellulose for the preparation of novel PEMs. Particularly, we provide a material and structural perspective how the ion conductivity, ion selectivity, anti-swelling property, self-healing property, flame retardancy, porosity, mechanical property, and photoelectric stability of cellulose-mediated PEMs can be regulated through molecular chemistry. Finally, we examine the potential of these strategies in advancing circular economy principles and environmental sustainability objectives, while also identifying key challenges and outlining promising future research directions. We emphasize the critical need for advanced molecular-level chemical engineering to fully harness the potential of cellulose for energy-related applications.</t>
-        </is>
-      </c>
+          <t>Accelerating net-zero transition: Satellite insight reveals Decarbonization potential of coal-fired power plants</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
         <is>
-          <t>http://pubs.rsc.org/en/Content/ArticleLanding/2026/EE/D5EE05398F</t>
+          <t>https://www.sciencedirect.com/science/article/pii/S0306261925020239?dgcid=rss_sd_all</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -6425,53 +6260,57 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.3481834232807159</v>
+        <v>0.3479990065097809</v>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="n">
-        <v>0.2368689328432083</v>
+        <v>0.2213805913925171</v>
       </c>
       <c r="K34" t="n">
-        <v>0.1554520577192307</v>
+        <v>0.2179853171110153</v>
       </c>
       <c r="L34" t="n">
-        <v>0.3481834232807159</v>
+        <v>0.1069133132696152</v>
       </c>
       <c r="M34" t="n">
-        <v>0.2474187016487122</v>
+        <v>0.2237639725208282</v>
       </c>
       <c r="N34" t="n">
-        <v>0.2809361219406128</v>
+        <v>0.1111921668052673</v>
       </c>
       <c r="O34" t="n">
-        <v>0.3151056468486786</v>
+        <v>0.1470969319343567</v>
       </c>
       <c r="P34" t="n">
-        <v>0.0795421376824379</v>
+        <v>0.2577376365661621</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.2233236283063889</v>
+        <v>0.2020016014575958</v>
       </c>
       <c r="R34" t="n">
-        <v>0.09470903873443604</v>
+        <v>0.3479990065097809</v>
       </c>
       <c r="S34" t="n">
-        <v>0.1183729320764542</v>
+        <v>0.2792136967182159</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Accelerating net-zero transition: Satellite insight reveals Decarbonization potential of coal-fired power plants</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr"/>
+          <t>[ASAP] Electrooxidation of Ethylene Glycol to Glycolic Acid in a Neutral Electrolyte via Enhanced *OH Generation and Directional Spillover</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Electrochemical upcycling of polyethylene terephthalate (PET)-derived ethylene glycol (EG) into glycolic acid (GA) presents a sustainable route toward circular plastic economy. While recent advances have improved EG oxidation reaction (EGOR) performance in alkaline media, the downstream separation of GA remains cumbersome and inevitably coproduces waste salts. Neutral media offer a promising alternative but are constrained by the difficulty in generating and utilizing *OH, a pivotal EGOR intermediate. Although Ir has been reported to promote H2O dissociation into active *OH species, a major challenge lies in ensuring that the generated *OH effectively participates in EGOR, rather than undergoing self-dehydrogenation (*OH → *O). To address this, we designed an atomically isolated Ir decorated Pd alloy with high-density Ir–Pd interfaces, which establishes an *OH transfer network that promotes *OH-mediated EGOR while suppressing *OH self-dehydrogenation. In situ spectroscopic characterizations reveal that Ir1Pd-SAA facilitates the efficient dissociation of H2O into *OH at Ir single-atom sites, followed by *OH spillover to adjacent Pd sites within an atomic scale, thus triggering EGOR. Ir1Pd-SAA delivers a peak current of 56.2 mA cm–2 at 0.89 V vs RHE, outperforming pure Pd (10.7 mA cm–2 at 0.95 V vs RHE) and IrNPPd (7.3 mA cm–2 0.92 V vs RHE), along with high GA selectivity (80.1%), FE (76.3%), and stability over 330 h. Theoretical calculations confirm the Ir–Pd synergistic effect, where Ir promotes *OH generation and optimizes the electronic structure of Pd to initiate EGOR. This work provides fundamental insights for rational catalyst design for alcohol-to-organic acid conversion in neutral media.</t>
+        </is>
+      </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>https://www.sciencedirect.com/science/article/pii/S0306261925020239?dgcid=rss_sd_all</t>
+          <t>http://dx.doi.org/10.1021/jacs.6c01709</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -6480,57 +6319,57 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.3479990065097809</v>
+        <v>0.3474744856357574</v>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="n">
-        <v>0.2213805913925171</v>
+        <v>0.2839102447032928</v>
       </c>
       <c r="K35" t="n">
-        <v>0.2179853171110153</v>
+        <v>0.2076517045497894</v>
       </c>
       <c r="L35" t="n">
-        <v>0.1069133132696152</v>
+        <v>0.3474744856357574</v>
       </c>
       <c r="M35" t="n">
-        <v>0.2237639725208282</v>
+        <v>0.1574579775333405</v>
       </c>
       <c r="N35" t="n">
-        <v>0.1111921668052673</v>
+        <v>0.2548983991146088</v>
       </c>
       <c r="O35" t="n">
-        <v>0.1470969319343567</v>
+        <v>0.2269209176301956</v>
       </c>
       <c r="P35" t="n">
-        <v>0.2577376365661621</v>
+        <v>0.07710257917642593</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.2020016014575958</v>
+        <v>0.1908403038978577</v>
       </c>
       <c r="R35" t="n">
-        <v>0.3479990065097809</v>
+        <v>0.127028152346611</v>
       </c>
       <c r="S35" t="n">
-        <v>0.2792136967182159</v>
+        <v>0.05645062774419785</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>[ASAP] Electrooxidation of Ethylene Glycol to Glycolic Acid in a Neutral Electrolyte via Enhanced *OH Generation and Directional Spillover</t>
+          <t>Charge‐Spin‐Orbit Modulated Carbon‐Encapsulated FeP/Fe3O4 Heterojunctions for Ultrafast and Stable Conversion of Low‐Concentration Nitrate to Ammonia</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Electrochemical upcycling of polyethylene terephthalate (PET)-derived ethylene glycol (EG) into glycolic acid (GA) presents a sustainable route toward circular plastic economy. While recent advances have improved EG oxidation reaction (EGOR) performance in alkaline media, the downstream separation of GA remains cumbersome and inevitably coproduces waste salts. Neutral media offer a promising alternative but are constrained by the difficulty in generating and utilizing *OH, a pivotal EGOR intermediate. Although Ir has been reported to promote H2O dissociation into active *OH species, a major challenge lies in ensuring that the generated *OH effectively participates in EGOR, rather than undergoing self-dehydrogenation (*OH → *O). To address this, we designed an atomically isolated Ir decorated Pd alloy with high-density Ir–Pd interfaces, which establishes an *OH transfer network that promotes *OH-mediated EGOR while suppressing *OH self-dehydrogenation. In situ spectroscopic characterizations reveal that Ir1Pd-SAA facilitates the efficient dissociation of H2O into *OH at Ir single-atom sites, followed by *OH spillover to adjacent Pd sites within an atomic scale, thus triggering EGOR. Ir1Pd-SAA delivers a peak current of 56.2 mA cm–2 at 0.89 V vs RHE, outperforming pure Pd (10.7 mA cm–2 at 0.95 V vs RHE) and IrNPPd (7.3 mA cm–2 0.92 V vs RHE), along with high GA selectivity (80.1%), FE (76.3%), and stability over 330 h. Theoretical calculations confirm the Ir–Pd synergistic effect, where Ir promotes *OH generation and optimizes the electronic structure of Pd to initiate EGOR. This work provides fundamental insights for rational catalyst design for alcohol-to-organic acid conversion in neutral media.</t>
+          <t>Abstract Electrocatalytic nitrate reduction reaction offers an effective route for ammonia synthesis and actual wastewater treatment. Despite some important achievements, the progress is still low than expected, especially in low‐concentration nitrate, mostly because of slow hydrogenation kinetics and interfering substances. In this work, we presented that, by engineering spin orbital orientation, a carbon‐encapsulated FeP/Fe 3 O 4 heterojunctions (FeP/Fe 3 O 4 @C) enabled ultrafast and stable NH 3 electrosynthesis from low‐concentration nitrate. In‐situ characterization and theoretical calculation confirmed that FeP/Fe 3 O 4 heterojunctions induced spin orbit splitting of Fe, resulting in electron transition from low spin to high spin. The resulted non‐degenerate orbitals caused the energy levels shift up and guided the electron migration from FeP to Fe 3 O 4 , which thus activated additional 3d orbital electron states. This spin orbital orientation further optimized the chemisorption properties of nitrogen‐oxygen intermediates and H* spillover, thus accelerating hydrogenation kinetics for ultrafast NH 3 electrosynthesis. Meanwhile, FeP/Fe 3 O 4 @C electrocatalyst alleviated the phosphate poisoning of active metal sites during industrial wastewater treatment, demonstrating excellent anti‐interference capability and environmental sustainability for real application. This work by modulating the “charge‐spin‐orbit” structure of active sites provided a new strategy for rational design of high‐performance electrocatalysts for various electrocatalytic reactions.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>http://dx.doi.org/10.1021/jacs.6c01709</t>
+          <t>https://onlinelibrary.wiley.com/doi/10.1002/anie.202519571?af=R</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6539,57 +6378,57 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.3474744856357574</v>
+        <v>0.342134952545166</v>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="n">
-        <v>0.2839102447032928</v>
+        <v>0.3023344576358795</v>
       </c>
       <c r="K36" t="n">
-        <v>0.2076517045497894</v>
+        <v>0.2498351782560349</v>
       </c>
       <c r="L36" t="n">
-        <v>0.3474744856357574</v>
+        <v>0.3262722194194794</v>
       </c>
       <c r="M36" t="n">
-        <v>0.1574579775333405</v>
+        <v>0.1736057102680206</v>
       </c>
       <c r="N36" t="n">
-        <v>0.2548983991146088</v>
+        <v>0.342134952545166</v>
       </c>
       <c r="O36" t="n">
-        <v>0.2269209176301956</v>
+        <v>0.2585192322731018</v>
       </c>
       <c r="P36" t="n">
-        <v>0.07710257917642593</v>
+        <v>0.04107067361474037</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.1908403038978577</v>
+        <v>0.200408086180687</v>
       </c>
       <c r="R36" t="n">
-        <v>0.127028152346611</v>
+        <v>0.08512689173221588</v>
       </c>
       <c r="S36" t="n">
-        <v>0.05645062774419785</v>
+        <v>0.1038889065384865</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Charge‐Spin‐Orbit Modulated Carbon‐Encapsulated FeP/Fe3O4 Heterojunctions for Ultrafast and Stable Conversion of Low‐Concentration Nitrate to Ammonia</t>
+          <t>Why Biden-era clean energy investment policies had limited political returns</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Abstract Electrocatalytic nitrate reduction reaction offers an effective route for ammonia synthesis and actual wastewater treatment. Despite some important achievements, the progress is still low than expected, especially in low‐concentration nitrate, mostly because of slow hydrogenation kinetics and interfering substances. In this work, we presented that, by engineering spin orbital orientation, a carbon‐encapsulated FeP/Fe 3 O 4 heterojunctions (FeP/Fe 3 O 4 @C) enabled ultrafast and stable NH 3 electrosynthesis from low‐concentration nitrate. In‐situ characterization and theoretical calculation confirmed that FeP/Fe 3 O 4 heterojunctions induced spin orbit splitting of Fe, resulting in electron transition from low spin to high spin. The resulted non‐degenerate orbitals caused the energy levels shift up and guided the electron migration from FeP to Fe 3 O 4 , which thus activated additional 3d orbital electron states. This spin orbital orientation further optimized the chemisorption properties of nitrogen‐oxygen intermediates and H* spillover, thus accelerating hydrogenation kinetics for ultrafast NH 3 electrosynthesis. Meanwhile, FeP/Fe 3 O 4 @C electrocatalyst alleviated the phosphate poisoning of active metal sites during industrial wastewater treatment, demonstrating excellent anti‐interference capability and environmental sustainability for real application. This work by modulating the “charge‐spin‐orbit” structure of active sites provided a new strategy for rational design of high‐performance electrocatalysts for various electrocatalytic reactions.</t>
+          <t>The Biden Administration enacted the largest federal policy framework to incentivize clean energy and decarbonization in U.S. history. We examine whether Biden-era green investments produced political returns by affecting public opinion. Using geolocated survey data linked to investment records and a database of company and politician statements, we assess project visibility and credit attribution. People closer to new renewable energy and green manufacturing facilities are more likely to notice these investments but are not more likely to credit the Biden Administration. Instead, the public sees governors as most responsible. This credit allocation pattern aligns with the political message environment: Governors more frequently claim credit than the White House and companies spread recognition broadly across political actors. This fragmented information environment illustrates the limits of using less traceable forms of green spending to generate electoral gains and public support for climate policy.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>https://onlinelibrary.wiley.com/doi/10.1002/anie.202519571?af=R</t>
+          <t>https://www.pnas.org/doi/abs/10.1073/pnas.2526802123?mi=eymic2&amp;af=R&amp;access=on&amp;content=articlesChapters&amp;publication=pnas&amp;sortBy=Earliest&amp;target=default</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6598,57 +6437,57 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.342134952545166</v>
+        <v>0.3420231938362122</v>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="n">
-        <v>0.3023344576358795</v>
+        <v>0.1598720401525497</v>
       </c>
       <c r="K37" t="n">
-        <v>0.2498351782560349</v>
+        <v>0.09095373004674911</v>
       </c>
       <c r="L37" t="n">
-        <v>0.3262722194194794</v>
+        <v>0.05561123788356781</v>
       </c>
       <c r="M37" t="n">
-        <v>0.1736057102680206</v>
+        <v>0.1264538764953613</v>
       </c>
       <c r="N37" t="n">
-        <v>0.342134952545166</v>
+        <v>0.09167083352804184</v>
       </c>
       <c r="O37" t="n">
-        <v>0.2585192322731018</v>
+        <v>0.1250477880239487</v>
       </c>
       <c r="P37" t="n">
-        <v>0.04107067361474037</v>
+        <v>0.1432141810655594</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.200408086180687</v>
+        <v>0.1176950484514236</v>
       </c>
       <c r="R37" t="n">
-        <v>0.08512689173221588</v>
+        <v>0.2728007137775421</v>
       </c>
       <c r="S37" t="n">
-        <v>0.1038889065384865</v>
+        <v>0.3420231938362122</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Why Biden-era clean energy investment policies had limited political returns</t>
+          <t>Molecular‐Level Design of Asphalt‐Derived Hard Carbon with Enhanced Ion/Electron Transport for High‐Rate Sodium‐Ion Batteries</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>The Biden Administration enacted the largest federal policy framework to incentivize clean energy and decarbonization in U.S. history. We examine whether Biden-era green investments produced political returns by affecting public opinion. Using geolocated survey data linked to investment records and a database of company and politician statements, we assess project visibility and credit attribution. People closer to new renewable energy and green manufacturing facilities are more likely to notice these investments but are not more likely to credit the Biden Administration. Instead, the public sees governors as most responsible. This credit allocation pattern aligns with the political message environment: Governors more frequently claim credit than the White House and companies spread recognition broadly across political actors. This fragmented information environment illustrates the limits of using less traceable forms of green spending to generate electoral gains and public support for climate policy.</t>
+          <t>ABSTRACT Asphalt is an attractive precursor for hard carbon anodes in sodium‐ion batteries owing to its low cost and excellent structural consistency. However, conventional oxidative strategies, commonly employed for converting asphalt into hard carbon, inevitably distorts the carbon framework, disrupting electronic continuity and Na⁺ diffusion, thereby limiting rate capability. Herein, an integrated molecular‐level strategy is developed by coupling controlled oxidative crosslinking with simultaneous nitrogen modulation, enabling rapid electron/ion transport and delivering outstanding electrochemical performance, as validated in Ah‐level cylindrical cells. Combined with in situ characterizations and theoretical calculations, we uncover that synergistic graphitic and pyrrolic nitrogen species markedly enhance structural stability and charge transport—with the electronic conductivity reaching 41.9 S cm −1 (1.5 × higher) and ionic conductivity up to 0.87 mS cm −1 (1.4 × higher)—while inducing the formation of a thin, NaF‐rich solid electrolyte interface that collectively promotes ultrafast Na + migration and long‐term stability. As a result, the modulated hard carbon achieves a high capacity of 361.8 mA h g −1 , excellent rate capability (190.3 mA h g −1 at 5.0 A g −1 ), and superior cycling stability. When assembled into 18650 cylindrical cells, it delivers energy density of 106.7 Wh kg −1 , retaining 83.8% capacity after 1000 cycles at 1C/10C, highlighting its strong practical potential.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>https://www.pnas.org/doi/abs/10.1073/pnas.2526802123?mi=eymic2&amp;af=R&amp;access=on&amp;content=articlesChapters&amp;publication=pnas&amp;sortBy=Earliest&amp;target=default</t>
+          <t>https://advanced.onlinelibrary.wiley.com/doi/10.1002/aenm.202506585?af=R</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6657,57 +6496,57 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.3420231938362122</v>
+        <v>0.3404554724693298</v>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="n">
-        <v>0.1598720401525497</v>
+        <v>0.1454907208681107</v>
       </c>
       <c r="K38" t="n">
-        <v>0.09095373004674911</v>
+        <v>0.1244246289134026</v>
       </c>
       <c r="L38" t="n">
-        <v>0.05561123788356781</v>
+        <v>0.3404554724693298</v>
       </c>
       <c r="M38" t="n">
-        <v>0.1264538764953613</v>
+        <v>0.253010481595993</v>
       </c>
       <c r="N38" t="n">
-        <v>0.09167083352804184</v>
+        <v>0.1530074030160904</v>
       </c>
       <c r="O38" t="n">
-        <v>0.1250477880239487</v>
+        <v>0.3237095475196838</v>
       </c>
       <c r="P38" t="n">
-        <v>0.1432141810655594</v>
+        <v>0.1526584923267365</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.1176950484514236</v>
+        <v>0.2227078825235367</v>
       </c>
       <c r="R38" t="n">
-        <v>0.2728007137775421</v>
+        <v>0.1196814402937889</v>
       </c>
       <c r="S38" t="n">
-        <v>0.3420231938362122</v>
+        <v>0.1575845927000046</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Molecular‐Level Design of Asphalt‐Derived Hard Carbon with Enhanced Ion/Electron Transport for High‐Rate Sodium‐Ion Batteries</t>
+          <t>[ASAP] Geminal Cl-Bridged Dual-Fe-Atom Catalyst for Efficient and Stable Oxygen Reduction Reaction</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ABSTRACT Asphalt is an attractive precursor for hard carbon anodes in sodium‐ion batteries owing to its low cost and excellent structural consistency. However, conventional oxidative strategies, commonly employed for converting asphalt into hard carbon, inevitably distorts the carbon framework, disrupting electronic continuity and Na⁺ diffusion, thereby limiting rate capability. Herein, an integrated molecular‐level strategy is developed by coupling controlled oxidative crosslinking with simultaneous nitrogen modulation, enabling rapid electron/ion transport and delivering outstanding electrochemical performance, as validated in Ah‐level cylindrical cells. Combined with in situ characterizations and theoretical calculations, we uncover that synergistic graphitic and pyrrolic nitrogen species markedly enhance structural stability and charge transport—with the electronic conductivity reaching 41.9 S cm −1 (1.5 × higher) and ionic conductivity up to 0.87 mS cm −1 (1.4 × higher)—while inducing the formation of a thin, NaF‐rich solid electrolyte interface that collectively promotes ultrafast Na + migration and long‐term stability. As a result, the modulated hard carbon achieves a high capacity of 361.8 mA h g −1 , excellent rate capability (190.3 mA h g −1 at 5.0 A g −1 ), and superior cycling stability. When assembled into 18650 cylindrical cells, it delivers energy density of 106.7 Wh kg −1 , retaining 83.8% capacity after 1000 cycles at 1C/10C, highlighting its strong practical potential.</t>
+          <t>Atomically dispersed iron-nitrogen-carbon (Fe-N-C) catalysts hold great promise for the oxygen reduction reaction (ORR), yet their structural instability under operational conditions restricts their practical application. In this study, we identify that electrochemical degradation of the Fe-N-C catalyst stems from a dynamic disparity between the Fe-N and Fe-O bonds during ORR, leading to pronounced Fe demetallization. Guided by this mechanistic insight, we synthesize a dual-Fe-atom catalyst featuring a well-defined N3-Fe-Cl-Fe-N3 structure. Combined theoretical and experimental results reveal that the bridging Cl atom induces charge redistribution and downshifts the Fe d-band center, thereby regulating the adsorption and activation of oxygenated intermediates. The electronic energy gained by Fe-O bonding during ORR triggers a dynamic reconfiguration of the N3-Fe-Cl-Fe-N3 moieties, which in turn reinforces structural Fe-N and Fe-Cl bonds while attenuating hyperergic Fe-O interactions. Such a dynamic process enables adaptable coordination and accelerates protonation kinetics, underscoring the cooperativity of metal coordination at dual-Fe centers and thereby ensuring electrochemical robustness. The resulting dual-Fe-atom catalyst demonstrates exceptional ORR stability with minimal Fe leaching (16.4 μg L-1 after 20000 accelerated durability cycles) and retains 88% current over 160 h of operation. This catalyst delivers over 1000 h of stable performance in a zinc-air battery with a negligible overpotential increase. These findings deepen the mechanistic understanding of Fe demetallization in the Fe-N-C catalyst under operando ORR conditions, paving the way for the rational design of robust noble-metal-free ORR electrocatalysts.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>https://advanced.onlinelibrary.wiley.com/doi/10.1002/aenm.202506585?af=R</t>
+          <t>http://dx.doi.org/10.1021/jacs.5c15456</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6716,57 +6555,57 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.3404554724693298</v>
+        <v>0.3379671573638916</v>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="n">
-        <v>0.1454907208681107</v>
+        <v>0.3379671573638916</v>
       </c>
       <c r="K39" t="n">
-        <v>0.1244246289134026</v>
+        <v>0.2304790169000626</v>
       </c>
       <c r="L39" t="n">
-        <v>0.3404554724693298</v>
+        <v>0.29352867603302</v>
       </c>
       <c r="M39" t="n">
-        <v>0.253010481595993</v>
+        <v>0.2087946683168411</v>
       </c>
       <c r="N39" t="n">
-        <v>0.1530074030160904</v>
+        <v>0.2201386839151382</v>
       </c>
       <c r="O39" t="n">
-        <v>0.3237095475196838</v>
+        <v>0.2258867025375366</v>
       </c>
       <c r="P39" t="n">
-        <v>0.1526584923267365</v>
+        <v>0.09975206106901169</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.2227078825235367</v>
+        <v>0.1818326562643051</v>
       </c>
       <c r="R39" t="n">
-        <v>0.1196814402937889</v>
+        <v>0.1384085565805435</v>
       </c>
       <c r="S39" t="n">
-        <v>0.1575845927000046</v>
+        <v>0.1288657635450363</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>[ASAP] Geminal Cl-Bridged Dual-Fe-Atom Catalyst for Efficient and Stable Oxygen Reduction Reaction</t>
+          <t>Regenerable Water Remediation Platform for Ultrafast Capture and Mineralization of Per‐ and Polyfluoroalkyl Substances</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Atomically dispersed iron-nitrogen-carbon (Fe-N-C) catalysts hold great promise for the oxygen reduction reaction (ORR), yet their structural instability under operational conditions restricts their practical application. In this study, we identify that electrochemical degradation of the Fe-N-C catalyst stems from a dynamic disparity between the Fe-N and Fe-O bonds during ORR, leading to pronounced Fe demetallization. Guided by this mechanistic insight, we synthesize a dual-Fe-atom catalyst featuring a well-defined N3-Fe-Cl-Fe-N3 structure. Combined theoretical and experimental results reveal that the bridging Cl atom induces charge redistribution and downshifts the Fe d-band center, thereby regulating the adsorption and activation of oxygenated intermediates. The electronic energy gained by Fe-O bonding during ORR triggers a dynamic reconfiguration of the N3-Fe-Cl-Fe-N3 moieties, which in turn reinforces structural Fe-N and Fe-Cl bonds while attenuating hyperergic Fe-O interactions. Such a dynamic process enables adaptable coordination and accelerates protonation kinetics, underscoring the cooperativity of metal coordination at dual-Fe centers and thereby ensuring electrochemical robustness. The resulting dual-Fe-atom catalyst demonstrates exceptional ORR stability with minimal Fe leaching (16.4 μg L-1 after 20000 accelerated durability cycles) and retains 88% current over 160 h of operation. This catalyst delivers over 1000 h of stable performance in a zinc-air battery with a negligible overpotential increase. These findings deepen the mechanistic understanding of Fe demetallization in the Fe-N-C catalyst under operando ORR conditions, paving the way for the rational design of robust noble-metal-free ORR electrocatalysts.</t>
+          <t>Abstract Concerns about per‐ and polyfluoroalkyl substances (PFAS) arise from their persistence, toxicity, and widespread presence in aquatic environments. Currently, activated carbon and ion exchange resins have been used to remove perfluorooctanoic acid (PFOA), the most commonly studied PFAS, but these methods face challenges like low adsorption capacity and slow kinetics, leading to secondary waste issues. Here, it is observed that a high interlayer crystallinity of nitrate intercalated Cu x Al layered double hydroxides (LDH) (Cu x Al‐NO 3 LDH) enables a boundary‐breaking performance of maximum adsorption capacity (q max ) of PFOA as 1702 mg g −1 at neutral pH and room temperature. The Al‐Al clash within the cationic layers (basal plane disorder) enhances adsorption kinetics (k 1 = 13.2 h −1 ), as determined by a 2 H magic angle spinning (MAS) solid‐state nuclear magnetic resonance (ssNMR) spectroscopy. Furthermore, PFOA‐saturated Cu 2 Al‐NO 3 LDH can be regenerated through its memory effect, achieving ≈54% defluorination of the adsorbed PFOA in the presence of CaCO 3 after the thermal treatment at 773 K (500 °C). Performance in continuous fixed‐bed systems (720 mg g −1 at 0.5 mL min −1 ) and PFOA‐spiked real water matrices indicates the practical application potential of Cu x Al‐NO 3 LDH, suggesting an effective integrated ultrafast capture–thermal destruction–recycling (CTR) process for treating PFAS‐contaminated water.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>http://dx.doi.org/10.1021/jacs.5c15456</t>
+          <t>https://advanced.onlinelibrary.wiley.com/doi/10.1002/adma.202509842?af=R</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6775,57 +6614,57 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.3379671573638916</v>
+        <v>0.3365139663219452</v>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="n">
-        <v>0.3379671573638916</v>
+        <v>0.199079692363739</v>
       </c>
       <c r="K40" t="n">
-        <v>0.2304790169000626</v>
+        <v>0.1806170493364334</v>
       </c>
       <c r="L40" t="n">
-        <v>0.29352867603302</v>
+        <v>0.1848300397396088</v>
       </c>
       <c r="M40" t="n">
-        <v>0.2087946683168411</v>
+        <v>0.2774670422077179</v>
       </c>
       <c r="N40" t="n">
-        <v>0.2201386839151382</v>
+        <v>0.1461724191904068</v>
       </c>
       <c r="O40" t="n">
-        <v>0.2258867025375366</v>
+        <v>0.3365139663219452</v>
       </c>
       <c r="P40" t="n">
-        <v>0.09975206106901169</v>
+        <v>0.1845438480377197</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.1818326562643051</v>
+        <v>0.1621338129043579</v>
       </c>
       <c r="R40" t="n">
-        <v>0.1384085565805435</v>
+        <v>0.1216883584856987</v>
       </c>
       <c r="S40" t="n">
-        <v>0.1288657635450363</v>
+        <v>0.09608981758356094</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Regenerable Water Remediation Platform for Ultrafast Capture and Mineralization of Per‐ and Polyfluoroalkyl Substances</t>
+          <t>Critical transition of urban ozone formation regime in the North China Plain</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Abstract Concerns about per‐ and polyfluoroalkyl substances (PFAS) arise from their persistence, toxicity, and widespread presence in aquatic environments. Currently, activated carbon and ion exchange resins have been used to remove perfluorooctanoic acid (PFOA), the most commonly studied PFAS, but these methods face challenges like low adsorption capacity and slow kinetics, leading to secondary waste issues. Here, it is observed that a high interlayer crystallinity of nitrate intercalated Cu x Al layered double hydroxides (LDH) (Cu x Al‐NO 3 LDH) enables a boundary‐breaking performance of maximum adsorption capacity (q max ) of PFOA as 1702 mg g −1 at neutral pH and room temperature. The Al‐Al clash within the cationic layers (basal plane disorder) enhances adsorption kinetics (k 1 = 13.2 h −1 ), as determined by a 2 H magic angle spinning (MAS) solid‐state nuclear magnetic resonance (ssNMR) spectroscopy. Furthermore, PFOA‐saturated Cu 2 Al‐NO 3 LDH can be regenerated through its memory effect, achieving ≈54% defluorination of the adsorbed PFOA in the presence of CaCO 3 after the thermal treatment at 773 K (500 °C). Performance in continuous fixed‐bed systems (720 mg g −1 at 0.5 mL min −1 ) and PFOA‐spiked real water matrices indicates the practical application potential of Cu x Al‐NO 3 LDH, suggesting an effective integrated ultrafast capture–thermal destruction–recycling (CTR) process for treating PFAS‐contaminated water.</t>
+          <t>Over the past decade, China has achieved remarkable progress in mitigating the aerosol pollution. However, ozone (O3) pollution still shows a worsening trend, implying that China’s control measures may have been less effective in tackling O3 pollution. Herein, we conduct synchronized observations of O3 and its precursors across 37 cities in the heavily polluted North China Plain (NCP) during the summer of 2021 and apply a unified observation-based model to diagnose O3 formation mechanisms. Our results reveal a significant transition in urban O3 formation regime, shifting from primarily VOC-limited to VOC–NOx co-limited across the NCP between 2010s and 2020s. Notably, the primary VOC species, their respective sources, and the optimal VOCs/NOx reduction ratios exhibit remarkable regional consistency. Modeling analyses further indicate that long-term national “Carbon Neutrality” strategy could effectively alleviate O3 pollution, with targeted VOC emission reductions from major anthropogenic sources offering the greatest mitigation potential. These findings underscore the efficacy of China’s endeavors in mitigating O3 pollution, although the effects are not immediately evident from ambient O3 concentrations. O3 pollution control in Chinese cities has reached a critical inflection point, offering considerable flexibility and feasibility in formulating future control policies.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>https://advanced.onlinelibrary.wiley.com/doi/10.1002/adma.202509842?af=R</t>
+          <t>https://academic.oup.com/nsr/advance-article/doi/10.1093/nsr/nwaf596/8408452?rss=1</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6834,57 +6673,53 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.3365139663219452</v>
+        <v>0.3337845206260681</v>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="n">
-        <v>0.199079692363739</v>
+        <v>0.2733720541000366</v>
       </c>
       <c r="K41" t="n">
-        <v>0.1806170493364334</v>
+        <v>0.2186239212751389</v>
       </c>
       <c r="L41" t="n">
-        <v>0.1848300397396088</v>
+        <v>0.1797241121530533</v>
       </c>
       <c r="M41" t="n">
-        <v>0.2774670422077179</v>
+        <v>0.210317924618721</v>
       </c>
       <c r="N41" t="n">
-        <v>0.1461724191904068</v>
+        <v>0.1881285160779953</v>
       </c>
       <c r="O41" t="n">
-        <v>0.3365139663219452</v>
+        <v>0.3337845206260681</v>
       </c>
       <c r="P41" t="n">
-        <v>0.1845438480377197</v>
+        <v>0.2924940586090088</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.1621338129043579</v>
+        <v>0.2110673189163208</v>
       </c>
       <c r="R41" t="n">
-        <v>0.1216883584856987</v>
+        <v>0.3271044492721558</v>
       </c>
       <c r="S41" t="n">
-        <v>0.09608981758356094</v>
+        <v>0.3322280645370483</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Critical transition of urban ozone formation regime in the North China Plain</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Over the past decade, China has achieved remarkable progress in mitigating the aerosol pollution. However, ozone (O3) pollution still shows a worsening trend, implying that China’s control measures may have been less effective in tackling O3 pollution. Herein, we conduct synchronized observations of O3 and its precursors across 37 cities in the heavily polluted North China Plain (NCP) during the summer of 2021 and apply a unified observation-based model to diagnose O3 formation mechanisms. Our results reveal a significant transition in urban O3 formation regime, shifting from primarily VOC-limited to VOC–NOx co-limited across the NCP between 2010s and 2020s. Notably, the primary VOC species, their respective sources, and the optimal VOCs/NOx reduction ratios exhibit remarkable regional consistency. Modeling analyses further indicate that long-term national “Carbon Neutrality” strategy could effectively alleviate O3 pollution, with targeted VOC emission reductions from major anthropogenic sources offering the greatest mitigation potential. These findings underscore the efficacy of China’s endeavors in mitigating O3 pollution, although the effects are not immediately evident from ambient O3 concentrations. O3 pollution control in Chinese cities has reached a critical inflection point, offering considerable flexibility and feasibility in formulating future control policies.</t>
-        </is>
-      </c>
+          <t>A hybrid centralized-distributed green ammonia system for cost-effective decarbonization of China's nitrogen fertilizer production</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr">
         <is>
-          <t>https://academic.oup.com/nsr/advance-article/doi/10.1093/nsr/nwaf596/8408452?rss=1</t>
+          <t>https://www.sciencedirect.com/science/article/pii/S0306261926002369?dgcid=rss_sd_all</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -6893,53 +6728,57 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.3337845206260681</v>
+        <v>0.3335929811000824</v>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="n">
-        <v>0.2733720541000366</v>
+        <v>0.1753991693258286</v>
       </c>
       <c r="K42" t="n">
-        <v>0.2186239212751389</v>
+        <v>0.1875977963209152</v>
       </c>
       <c r="L42" t="n">
-        <v>0.1797241121530533</v>
+        <v>0.141167014837265</v>
       </c>
       <c r="M42" t="n">
-        <v>0.210317924618721</v>
+        <v>0.1247052848339081</v>
       </c>
       <c r="N42" t="n">
-        <v>0.1881285160779953</v>
+        <v>0.2628704011440277</v>
       </c>
       <c r="O42" t="n">
-        <v>0.3337845206260681</v>
+        <v>0.1448095291852951</v>
       </c>
       <c r="P42" t="n">
-        <v>0.2924940586090088</v>
+        <v>0.1240898445248604</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.2110673189163208</v>
+        <v>0.2400254458189011</v>
       </c>
       <c r="R42" t="n">
-        <v>0.3271044492721558</v>
+        <v>0.2779443264007568</v>
       </c>
       <c r="S42" t="n">
-        <v>0.3322280645370483</v>
+        <v>0.3335929811000824</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A hybrid centralized-distributed green ammonia system for cost-effective decarbonization of China's nitrogen fertilizer production</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr"/>
+          <t>Monolayer nanocrystalline graphene synthesized from pyrolyzing a Langmuir monolayer of a polyaromatic hydrocarbon</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Bulk carbon materials can be synthesized through the modulation of precursor structures, stacking mode, and the optimization of pyrolysis conditions. The structure of two-dimensional (2D) carbon materials, however, is mainly driven by the pyrolysis temperature, pressure, and organic gas flow rates. Here, we report the synthesis of a centimeter-sized nanocrystalline graphene monolayer from pyrolyzing a Langmuir monolayer of a hexa(terpyridine)hexaphenylbenzene polyaromatic hydrocarbon (PAH) yielding a 2D carbon material with a thickness of 0.36 ± 0.07 nm. By designing the amphiphilic PAHs and reducing intermolecular π-π stacking interactions, a monolayer of horizontally aligned PAH was obtained at the water-air interface. During the pyrolysis, the monolayer served as a molecularly thin solid carbon source, leading to the controlled preparation of an electrically insulating nanocrystalline graphene monolayer. Our work proposes a 2D carbon material formed from the initial assembly of PAH monolayer at the water-air interface and subsequent pyrolysis and offers a modular strategy for designing nanocrystalline 2D films.</t>
+        </is>
+      </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>https://www.sciencedirect.com/science/article/pii/S0306261926002369?dgcid=rss_sd_all</t>
+          <t>https://www.science.org/doi/abs/10.1126/sciadv.adv1856?af=R</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6948,57 +6787,57 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.3335929811000824</v>
+        <v>0.3331798017024994</v>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="n">
-        <v>0.1753991693258286</v>
+        <v>0.3043299913406372</v>
       </c>
       <c r="K43" t="n">
-        <v>0.1875977963209152</v>
+        <v>0.2660484611988068</v>
       </c>
       <c r="L43" t="n">
-        <v>0.141167014837265</v>
+        <v>0.302857518196106</v>
       </c>
       <c r="M43" t="n">
-        <v>0.1247052848339081</v>
+        <v>0.3265646696090698</v>
       </c>
       <c r="N43" t="n">
-        <v>0.2628704011440277</v>
+        <v>0.1985398977994919</v>
       </c>
       <c r="O43" t="n">
-        <v>0.1448095291852951</v>
+        <v>0.3331798017024994</v>
       </c>
       <c r="P43" t="n">
-        <v>0.1240898445248604</v>
+        <v>0.1387818604707718</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.2400254458189011</v>
+        <v>0.2638175189495087</v>
       </c>
       <c r="R43" t="n">
-        <v>0.2779443264007568</v>
+        <v>0.1568342447280884</v>
       </c>
       <c r="S43" t="n">
-        <v>0.3335929811000824</v>
+        <v>0.1797497868537903</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Monolayer nanocrystalline graphene synthesized from pyrolyzing a Langmuir monolayer of a polyaromatic hydrocarbon</t>
+          <t>Overcoming Hydrophobicity with Water Enables Ultrafast Hydrolysis of Waste Polyethylene Terephthalate at Very Mild Conditions</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Bulk carbon materials can be synthesized through the modulation of precursor structures, stacking mode, and the optimization of pyrolysis conditions. The structure of two-dimensional (2D) carbon materials, however, is mainly driven by the pyrolysis temperature, pressure, and organic gas flow rates. Here, we report the synthesis of a centimeter-sized nanocrystalline graphene monolayer from pyrolyzing a Langmuir monolayer of a hexa(terpyridine)hexaphenylbenzene polyaromatic hydrocarbon (PAH) yielding a 2D carbon material with a thickness of 0.36 ± 0.07 nm. By designing the amphiphilic PAHs and reducing intermolecular π-π stacking interactions, a monolayer of horizontally aligned PAH was obtained at the water-air interface. During the pyrolysis, the monolayer served as a molecularly thin solid carbon source, leading to the controlled preparation of an electrically insulating nanocrystalline graphene monolayer. Our work proposes a 2D carbon material formed from the initial assembly of PAH monolayer at the water-air interface and subsequent pyrolysis and offers a modular strategy for designing nanocrystalline 2D films.</t>
+          <t>Abstract Chemical recycling of plastics holds great promise but remains constrained by sustainability issues, with polyethylene terephthalate (PET) epitomizing this challenge. Herein, we introduce a conceptually novel strategy that overcomes PET's intrinsic hydrophobicity by physically re‐engineering the polymer's microstructure to enable ultrafast alkaline hydrolysis under exceptionally mild conditions. We leverage the ability of propylene carbonate (PC)—an inexpensive, commercial, green solvent—to selectively dissolve PET, to thermally induce phase separation, and subsequently act as a carrier for water insertion between polymer chains. Upon complete PC replacement, the water uptake exceeds twice the polymer mass, preventing chain re‐compaction and establishing an interfacial environment that facilitates hydroxyl ion diffusion to ester bonds and depolymerization with minimal alkali consumption. As a result, water‐swollen PET fully depolymerizes (96% TPA yield) at atmospheric pressure within 5 min at 90 or under 2 h at room temperature, vastly outperforming conventional hydrolysis methods. The process achieves a 20‐fold reduction in energy footprint versus direct PET hydrolysis. It performs robustly on challenging, real‐world feedstocks—including textiles and mixed plastic waste—enabling selective depolymerization unaffected by PET crystallinity. A techno‐economic analysis (TEA) confirms energy efficiency and strong economic feasibility, demonstrating overall competitiveness with existing engineered technologies. Beyond PET, the physical mechanism underpinning the strategy offers a scalable and sustainable platform for recycling a wide range of condensation polymers.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>https://www.science.org/doi/abs/10.1126/sciadv.adv1856?af=R</t>
+          <t>https://onlinelibrary.wiley.com/doi/10.1002/anie.202514136?af=R</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7007,57 +6846,57 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.3331798017024994</v>
+        <v>0.3325088918209076</v>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="n">
-        <v>0.3043299913406372</v>
+        <v>0.1712909042835236</v>
       </c>
       <c r="K44" t="n">
-        <v>0.2660484611988068</v>
+        <v>0.2175843864679337</v>
       </c>
       <c r="L44" t="n">
-        <v>0.302857518196106</v>
+        <v>0.1581297367811203</v>
       </c>
       <c r="M44" t="n">
-        <v>0.3265646696090698</v>
+        <v>0.1314769685268402</v>
       </c>
       <c r="N44" t="n">
-        <v>0.1985398977994919</v>
+        <v>0.1367266327142715</v>
       </c>
       <c r="O44" t="n">
-        <v>0.3331798017024994</v>
+        <v>0.3325088918209076</v>
       </c>
       <c r="P44" t="n">
-        <v>0.1387818604707718</v>
+        <v>0.1015291213989258</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.2638175189495087</v>
+        <v>0.1083123236894608</v>
       </c>
       <c r="R44" t="n">
-        <v>0.1568342447280884</v>
+        <v>0.1065651550889015</v>
       </c>
       <c r="S44" t="n">
-        <v>0.1797497868537903</v>
+        <v>0.1084738224744797</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Overcoming Hydrophobicity with Water Enables Ultrafast Hydrolysis of Waste Polyethylene Terephthalate at Very Mild Conditions</t>
+          <t>Photoredox/Cobalt‐Catalyzed Asymmetric Radical Addition to Imines with Furanosyl 1,4‐Dihydropyridines to Access C‐Glycosyl Amino Esters</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Abstract Chemical recycling of plastics holds great promise but remains constrained by sustainability issues, with polyethylene terephthalate (PET) epitomizing this challenge. Herein, we introduce a conceptually novel strategy that overcomes PET's intrinsic hydrophobicity by physically re‐engineering the polymer's microstructure to enable ultrafast alkaline hydrolysis under exceptionally mild conditions. We leverage the ability of propylene carbonate (PC)—an inexpensive, commercial, green solvent—to selectively dissolve PET, to thermally induce phase separation, and subsequently act as a carrier for water insertion between polymer chains. Upon complete PC replacement, the water uptake exceeds twice the polymer mass, preventing chain re‐compaction and establishing an interfacial environment that facilitates hydroxyl ion diffusion to ester bonds and depolymerization with minimal alkali consumption. As a result, water‐swollen PET fully depolymerizes (96% TPA yield) at atmospheric pressure within 5 min at 90 or under 2 h at room temperature, vastly outperforming conventional hydrolysis methods. The process achieves a 20‐fold reduction in energy footprint versus direct PET hydrolysis. It performs robustly on challenging, real‐world feedstocks—including textiles and mixed plastic waste—enabling selective depolymerization unaffected by PET crystallinity. A techno‐economic analysis (TEA) confirms energy efficiency and strong economic feasibility, demonstrating overall competitiveness with existing engineered technologies. Beyond PET, the physical mechanism underpinning the strategy offers a scalable and sustainable platform for recycling a wide range of condensation polymers.</t>
+          <t>Abstract Chiral oxygen‐containing heterocycles, particularly tetrahydrofuran scaffolds are pivotal structures found in numerous bioactive molecules. Among them, furanoses constitute a highly important class. While C‐glycosylation with furanosyl donors offers a promising route to access these frameworks, methods for simultaneously constructing multiple stereogenic centers remain unknown. Herein, we report a synergistic photoredox/cobalt‐catalyzed enantioselective radical addition strategy to imines that employs bench‐stable furanosyl 1,4‐dihydropyridines (DHPs) as the radical precursors. This redox‐neutral protocol directly forges C‐glycosidic bonds at the challenging non‐anomeric position while concurrently establishing a new tetrasubstituted carbon stereocenter. The chiral cobalt catalyst effectively governs the stereochemistry of both the glycosidic bond and the new tetrasubstituted center, as evidenced by ligand control experiments. Furthermore, the method is generalizable to simple alkyl‐substituted DHPs, providing a versatile and complementary approach to synthesize amino esters and C‐glycosides with multiple stereogenic centers.</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>https://onlinelibrary.wiley.com/doi/10.1002/anie.202514136?af=R</t>
+          <t>https://onlinelibrary.wiley.com/doi/10.1002/anie.202521583?af=R</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7066,57 +6905,57 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.3325088918209076</v>
+        <v>0.328845739364624</v>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="n">
-        <v>0.1712909042835236</v>
+        <v>0.328845739364624</v>
       </c>
       <c r="K45" t="n">
-        <v>0.2175843864679337</v>
+        <v>0.1689878106117249</v>
       </c>
       <c r="L45" t="n">
-        <v>0.1581297367811203</v>
+        <v>0.1796481311321259</v>
       </c>
       <c r="M45" t="n">
-        <v>0.1314769685268402</v>
+        <v>0.1078003495931625</v>
       </c>
       <c r="N45" t="n">
-        <v>0.1367266327142715</v>
+        <v>0.3094960749149323</v>
       </c>
       <c r="O45" t="n">
-        <v>0.3325088918209076</v>
+        <v>0.06778561323881149</v>
       </c>
       <c r="P45" t="n">
-        <v>0.1015291213989258</v>
+        <v>-0.01344203017652035</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.1083123236894608</v>
+        <v>0.03344322741031647</v>
       </c>
       <c r="R45" t="n">
-        <v>0.1065651550889015</v>
+        <v>0.03883992880582809</v>
       </c>
       <c r="S45" t="n">
-        <v>0.1084738224744797</v>
+        <v>0.05023181438446045</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Photoredox/Cobalt‐Catalyzed Asymmetric Radical Addition to Imines with Furanosyl 1,4‐Dihydropyridines to Access C‐Glycosyl Amino Esters</t>
+          <t>One‐ and Two‐Electron Carbon–Halide Bond Activation at a Phosphorus Center</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Abstract Chiral oxygen‐containing heterocycles, particularly tetrahydrofuran scaffolds are pivotal structures found in numerous bioactive molecules. Among them, furanoses constitute a highly important class. While C‐glycosylation with furanosyl donors offers a promising route to access these frameworks, methods for simultaneously constructing multiple stereogenic centers remain unknown. Herein, we report a synergistic photoredox/cobalt‐catalyzed enantioselective radical addition strategy to imines that employs bench‐stable furanosyl 1,4‐dihydropyridines (DHPs) as the radical precursors. This redox‐neutral protocol directly forges C‐glycosidic bonds at the challenging non‐anomeric position while concurrently establishing a new tetrasubstituted carbon stereocenter. The chiral cobalt catalyst effectively governs the stereochemistry of both the glycosidic bond and the new tetrasubstituted center, as evidenced by ligand control experiments. Furthermore, the method is generalizable to simple alkyl‐substituted DHPs, providing a versatile and complementary approach to synthesize amino esters and C‐glycosides with multiple stereogenic centers.</t>
+          <t>Abstract The activation of small molecules by main‐group elements has garnered significant attention as a potential alternative to transition metal catalysis. While transition metals excel in switching between single‐electron (1e) and two‐electron (2e) pathways due to their accessible d‐orbitals, such switchability remains uncommon for main‐group elements. In this work, we report the phosphorus‐centered selective activation of various organohalides by phosphorus‐atom transfer reaction of metallophosphanorcaradiene complex, which presents four distinct modes, S N 2 or S N Ar‐type substitution, E2 elimination, or reductive radical coupling via halogen‐atom transfer. These reactivities selectively show 1e or 2e pathways depending on the substrate, mimicking oxidative addition and radical activation steps traditionally reserved for transition metals. These divergent modes of reactivity are enabled by the substantial orbital interactions between the single phosphorus atom center and [Cp*(Idipp)(CO)Ru] fragment, which can be viewed as a metalloligand, allowing for switchable reactivities between 2e and 1e pathways. Furthermore, this platform enables the modular synthesis of phosphines bearing three different substituents through a “P + 2E + Nu” strategy, establishing a new phosphorus‐atom transfer route to organophosphorus molecules (E = electrophile; Nu = nucleophile).</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>https://onlinelibrary.wiley.com/doi/10.1002/anie.202521583?af=R</t>
+          <t>https://onlinelibrary.wiley.com/doi/10.1002/anie.202521209?af=R</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7125,57 +6964,57 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.328845739364624</v>
+        <v>0.3280811011791229</v>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="n">
-        <v>0.328845739364624</v>
+        <v>0.3280811011791229</v>
       </c>
       <c r="K46" t="n">
-        <v>0.1689878106117249</v>
+        <v>0.2379897385835648</v>
       </c>
       <c r="L46" t="n">
-        <v>0.1796481311321259</v>
+        <v>0.2229756116867065</v>
       </c>
       <c r="M46" t="n">
-        <v>0.1078003495931625</v>
+        <v>0.1256550252437592</v>
       </c>
       <c r="N46" t="n">
-        <v>0.3094960749149323</v>
+        <v>0.2045130133628845</v>
       </c>
       <c r="O46" t="n">
-        <v>0.06778561323881149</v>
+        <v>0.1936225891113281</v>
       </c>
       <c r="P46" t="n">
-        <v>-0.01344203017652035</v>
+        <v>-0.002009965712204576</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.03344322741031647</v>
+        <v>0.1341075748205185</v>
       </c>
       <c r="R46" t="n">
-        <v>0.03883992880582809</v>
+        <v>0.08114277571439743</v>
       </c>
       <c r="S46" t="n">
-        <v>0.05023181438446045</v>
+        <v>0.0946425199508667</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>One‐ and Two‐Electron Carbon–Halide Bond Activation at a Phosphorus Center</t>
+          <t>Host–microbiome mutualism drives urea carbon salvage and acetogenesis during hibernation</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Abstract The activation of small molecules by main‐group elements has garnered significant attention as a potential alternative to transition metal catalysis. While transition metals excel in switching between single‐electron (1e) and two‐electron (2e) pathways due to their accessible d‐orbitals, such switchability remains uncommon for main‐group elements. In this work, we report the phosphorus‐centered selective activation of various organohalides by phosphorus‐atom transfer reaction of metallophosphanorcaradiene complex, which presents four distinct modes, S N 2 or S N Ar‐type substitution, E2 elimination, or reductive radical coupling via halogen‐atom transfer. These reactivities selectively show 1e or 2e pathways depending on the substrate, mimicking oxidative addition and radical activation steps traditionally reserved for transition metals. These divergent modes of reactivity are enabled by the substantial orbital interactions between the single phosphorus atom center and [Cp*(Idipp)(CO)Ru] fragment, which can be viewed as a metalloligand, allowing for switchable reactivities between 2e and 1e pathways. Furthermore, this platform enables the modular synthesis of phosphines bearing three different substituents through a “P + 2E + Nu” strategy, establishing a new phosphorus‐atom transfer route to organophosphorus molecules (E = electrophile; Nu = nucleophile).</t>
+          <t>Hibernation is a seasonal survival strategy employed by certain mammals that, through torpor use, reduces overall energy expenditure and permits long-term fasting. Although fasting solves the challenge of winter food scarcity, it also removes dietary carbon, a critical biomolecular building block. Here, we demonstrate a process of urea carbon salvage (UCS) in hibernating 13-lined ground squirrels, whereby urea carbon is reclaimed through gut microbial ureolysis and used in reductive acetogenesis to produce acetate, a short-chain fatty acid (SCFA) of major value to the host and its gut microbiota. We find that urea carbon incorporation into acetate is more efficient during hibernation than the summer active season and that while both host and gut microbes oxidize acetate for energy supply throughout the year, the host’s ability to absorb and oxidize acetate is highest during hibernation. Metagenomic analysis of the gut microbiome indicates that genes involved in the degradation of gut mucins, an abundant endogenous nutrient, are retained during hibernation. The hydrogen disposal associated with reductive acetogenesis from urea carbon helps facilitate this mucin degradation by providing a luminal environment that sustains fermentation, thereby generating SCFAs and other metabolites usable by both the host and its gut microbes. Our findings introduce UCS as a mechanism that enables hibernating squirrels and their gut microbes to exploit two key endogenous nutrient sources—urea and mucins—in the resource-limited hibernation season.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>https://onlinelibrary.wiley.com/doi/10.1002/anie.202521209?af=R</t>
+          <t>https://www.pnas.org/doi/abs/10.1073/pnas.2518978123?mi=eymic2&amp;af=R&amp;access=on&amp;content=articlesChapters&amp;publication=pnas&amp;sortBy=Earliest&amp;target=default</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7184,57 +7023,53 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.3280811011791229</v>
+        <v>0.327415406703949</v>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="n">
-        <v>0.3280811011791229</v>
+        <v>0.1556333601474762</v>
       </c>
       <c r="K47" t="n">
-        <v>0.2379897385835648</v>
+        <v>0.1453667879104614</v>
       </c>
       <c r="L47" t="n">
-        <v>0.2229756116867065</v>
+        <v>0.1251576840877533</v>
       </c>
       <c r="M47" t="n">
-        <v>0.1256550252437592</v>
+        <v>0.1982937902212143</v>
       </c>
       <c r="N47" t="n">
-        <v>0.2045130133628845</v>
+        <v>0.327415406703949</v>
       </c>
       <c r="O47" t="n">
-        <v>0.1936225891113281</v>
+        <v>0.2512165009975433</v>
       </c>
       <c r="P47" t="n">
-        <v>-0.002009965712204576</v>
+        <v>0.1623225808143616</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.1341075748205185</v>
+        <v>0.1880806535482407</v>
       </c>
       <c r="R47" t="n">
-        <v>0.08114277571439743</v>
+        <v>0.1786568760871887</v>
       </c>
       <c r="S47" t="n">
-        <v>0.0946425199508667</v>
+        <v>0.1768194735050201</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Host–microbiome mutualism drives urea carbon salvage and acetogenesis during hibernation</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Hibernation is a seasonal survival strategy employed by certain mammals that, through torpor use, reduces overall energy expenditure and permits long-term fasting. Although fasting solves the challenge of winter food scarcity, it also removes dietary carbon, a critical biomolecular building block. Here, we demonstrate a process of urea carbon salvage (UCS) in hibernating 13-lined ground squirrels, whereby urea carbon is reclaimed through gut microbial ureolysis and used in reductive acetogenesis to produce acetate, a short-chain fatty acid (SCFA) of major value to the host and its gut microbiota. We find that urea carbon incorporation into acetate is more efficient during hibernation than the summer active season and that while both host and gut microbes oxidize acetate for energy supply throughout the year, the host’s ability to absorb and oxidize acetate is highest during hibernation. Metagenomic analysis of the gut microbiome indicates that genes involved in the degradation of gut mucins, an abundant endogenous nutrient, are retained during hibernation. The hydrogen disposal associated with reductive acetogenesis from urea carbon helps facilitate this mucin degradation by providing a luminal environment that sustains fermentation, thereby generating SCFAs and other metabolites usable by both the host and its gut microbes. Our findings introduce UCS as a mechanism that enables hibernating squirrels and their gut microbes to exploit two key endogenous nutrient sources—urea and mucins—in the resource-limited hibernation season.</t>
-        </is>
-      </c>
+          <t>Divergent paths: A machine learning analysis of post-pandemic decarbonization trajectories and the global climate policy imperative</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
         <is>
-          <t>https://www.pnas.org/doi/abs/10.1073/pnas.2518978123?mi=eymic2&amp;af=R&amp;access=on&amp;content=articlesChapters&amp;publication=pnas&amp;sortBy=Earliest&amp;target=default</t>
+          <t>https://www.sciencedirect.com/science/article/pii/S0301421525005567?dgcid=rss_sd_all</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -7243,53 +7078,57 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.327415406703949</v>
+        <v>0.316833108663559</v>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="n">
-        <v>0.1556333601474762</v>
+        <v>0.126339390873909</v>
       </c>
       <c r="K48" t="n">
-        <v>0.1453667879104614</v>
+        <v>0.2008381932973862</v>
       </c>
       <c r="L48" t="n">
-        <v>0.1251576840877533</v>
+        <v>0.07629304379224777</v>
       </c>
       <c r="M48" t="n">
-        <v>0.1982937902212143</v>
+        <v>0.1396418511867523</v>
       </c>
       <c r="N48" t="n">
-        <v>0.327415406703949</v>
+        <v>0.1200752779841423</v>
       </c>
       <c r="O48" t="n">
-        <v>0.2512165009975433</v>
+        <v>0.125351756811142</v>
       </c>
       <c r="P48" t="n">
-        <v>0.1623225808143616</v>
+        <v>0.1140849590301514</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.1880806535482407</v>
+        <v>0.1305088400840759</v>
       </c>
       <c r="R48" t="n">
-        <v>0.1786568760871887</v>
+        <v>0.3093616962432861</v>
       </c>
       <c r="S48" t="n">
-        <v>0.1768194735050201</v>
+        <v>0.316833108663559</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Divergent paths: A machine learning analysis of post-pandemic decarbonization trajectories and the global climate policy imperative</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr"/>
+          <t>[ASAP] Ultrastable Copper Superatom</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Atomically coinage metal nanoclusters are highly attractive for various applications including catalysis, photochemistry, and energy conversion. While Cu nanoclusters are low cost, their development has lagged behind that of Au and Ag counterparts due to their inherent instability primarily caused by the low Cu(I)/Cu(0) reduction potential. Therefore, the synthesis of stable Cu(0)-containing nanoclusters remains a formidable challenge. Herein, we report the first 6-electron superatomic copper nanocluster, [Cu45H6(C≡CR)18(OAc)15] (Cu45). This cluster has remarkable stability, being resistant to thermal, oxidative, reductive, acidic, and basic treatments. Single-crystal X-ray diffraction analysis and time-dependent DFT calculations reveal that the outstanding stability of Cu45 is attributed to its superatomic electronic configuration (1S21P4) and strong copper-ligand interactions. Furthermore, Cu45 is the first well-defined Cu superatom electrocatalyst used for CO2-to-C2H4 electrocatalysis, which exhibits outstanding performance with a maximum Faradaic efficiency for C2+ products of 81.8% (58% for ethene), surpassing all known copper cluster catalysts. In situ ATR-SEIRAS and theoretical calculations reveal that Cu45 effectively activates CO2 and promotes C-C coupling, thereby facilitating the formation of C2+ products. This work provides new insights into the design of robust Cu nanoclusters for electrocatalytic applications, enabling their broader application in future research and technology development.</t>
+        </is>
+      </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>https://www.sciencedirect.com/science/article/pii/S0301421525005567?dgcid=rss_sd_all</t>
+          <t>http://dx.doi.org/10.1021/jacs.5c17976</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -7298,57 +7137,57 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.316833108663559</v>
+        <v>0.3014475405216217</v>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="n">
-        <v>0.126339390873909</v>
+        <v>0.3014475405216217</v>
       </c>
       <c r="K49" t="n">
-        <v>0.2008381932973862</v>
+        <v>0.1439000964164734</v>
       </c>
       <c r="L49" t="n">
-        <v>0.07629304379224777</v>
+        <v>0.2687362432479858</v>
       </c>
       <c r="M49" t="n">
-        <v>0.1396418511867523</v>
+        <v>0.1815896928310394</v>
       </c>
       <c r="N49" t="n">
-        <v>0.1200752779841423</v>
+        <v>0.1220001950860023</v>
       </c>
       <c r="O49" t="n">
-        <v>0.125351756811142</v>
+        <v>0.1654644161462784</v>
       </c>
       <c r="P49" t="n">
-        <v>0.1140849590301514</v>
+        <v>0.02098527550697327</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.1305088400840759</v>
+        <v>0.1553100347518921</v>
       </c>
       <c r="R49" t="n">
-        <v>0.3093616962432861</v>
+        <v>0.08321194350719452</v>
       </c>
       <c r="S49" t="n">
-        <v>0.316833108663559</v>
+        <v>0.07804631441831589</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>[ASAP] Ultrastable Copper Superatom</t>
+          <t>[ASAP] Collective Total Synthesis of 12 C4-Oxygenated Cladiellins and Structure Elucidation of Cladieunicellin D and Cladielloides A/C</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Atomically coinage metal nanoclusters are highly attractive for various applications including catalysis, photochemistry, and energy conversion. While Cu nanoclusters are low cost, their development has lagged behind that of Au and Ag counterparts due to their inherent instability primarily caused by the low Cu(I)/Cu(0) reduction potential. Therefore, the synthesis of stable Cu(0)-containing nanoclusters remains a formidable challenge. Herein, we report the first 6-electron superatomic copper nanocluster, [Cu45H6(C≡CR)18(OAc)15] (Cu45). This cluster has remarkable stability, being resistant to thermal, oxidative, reductive, acidic, and basic treatments. Single-crystal X-ray diffraction analysis and time-dependent DFT calculations reveal that the outstanding stability of Cu45 is attributed to its superatomic electronic configuration (1S21P4) and strong copper-ligand interactions. Furthermore, Cu45 is the first well-defined Cu superatom electrocatalyst used for CO2-to-C2H4 electrocatalysis, which exhibits outstanding performance with a maximum Faradaic efficiency for C2+ products of 81.8% (58% for ethene), surpassing all known copper cluster catalysts. In situ ATR-SEIRAS and theoretical calculations reveal that Cu45 effectively activates CO2 and promotes C-C coupling, thereby facilitating the formation of C2+ products. This work provides new insights into the design of robust Cu nanoclusters for electrocatalytic applications, enabling their broader application in future research and technology development.</t>
+          <t>Cladiellins are a group of marine natural products found in octocorals inhabiting Indo-Pacific reefs, and some members exhibit medically relevant biological activity. The 6/5/9-membered tricyclic ring skeleton of cladiellins comprises hydroisobenzofuran and oxonane moieties, and possesses three one-carbon branches and one three-carbon branch. Unsaturation and oxygenation at various positions endow structural diversity to this family; however, C4-oxygenated cladiellins are rare. Among these unusual structural features, the conformationally variable 9-membered ring presents an uncommon and formidable challenge for both NMR-based structure determination and chemical synthesis. Herein, we report the collective total synthesis of 12 structurally diverse C4-oxygenated cladiellins, 10 of which were chemically constructed for the first time. In addition, we revised the proposed structures of cladieunicellin D and cladielloide A, and established the previously unknown stereochemistry of cladielloides A/C. To accomplish this multifaceted endeavor, the project was divided into three parts. In the first part, we deduced the most likely stereoisomers of the three structurally ambiguous cladiellins from DP4+ probability analyses. In the second part, a common tricycle was assembled by a radical-polar crossover reaction of α-alkoxyacyl telluride with a 6-membered ring and an aldehyde, a reductive etherification reaction of a 5-membered ring, and a ring-closing metathesis reaction of a 9-membered ring. In the third part, the tricycle was systematically derivatized into 12 cladiellins by devising a series of selective transformations. The described results underscore the importance of designing an advanced common intermediate for collective total synthesis and combining density functional theory (DFT) calculations and syntheses for efficient structure elucidation.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>http://dx.doi.org/10.1021/jacs.5c17976</t>
+          <t>http://dx.doi.org/10.1021/jacs.5c19112</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -7357,57 +7196,53 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.3014475405216217</v>
+        <v>0.2980359792709351</v>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="n">
-        <v>0.3014475405216217</v>
+        <v>0.1948529034852982</v>
       </c>
       <c r="K50" t="n">
-        <v>0.1439000964164734</v>
+        <v>0.1972333639860153</v>
       </c>
       <c r="L50" t="n">
-        <v>0.2687362432479858</v>
+        <v>0.2132568359375</v>
       </c>
       <c r="M50" t="n">
-        <v>0.1815896928310394</v>
+        <v>0.2337729334831238</v>
       </c>
       <c r="N50" t="n">
-        <v>0.1220001950860023</v>
+        <v>0.2980359792709351</v>
       </c>
       <c r="O50" t="n">
-        <v>0.1654644161462784</v>
+        <v>0.162337452173233</v>
       </c>
       <c r="P50" t="n">
-        <v>0.02098527550697327</v>
+        <v>0.2206272184848785</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.1553100347518921</v>
+        <v>0.1676791906356812</v>
       </c>
       <c r="R50" t="n">
-        <v>0.08321194350719452</v>
+        <v>0.1100441142916679</v>
       </c>
       <c r="S50" t="n">
-        <v>0.07804631441831589</v>
+        <v>0.07230668514966965</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>[ASAP] Collective Total Synthesis of 12 C4-Oxygenated Cladiellins and Structure Elucidation of Cladieunicellin D and Cladielloides A/C</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Cladiellins are a group of marine natural products found in octocorals inhabiting Indo-Pacific reefs, and some members exhibit medically relevant biological activity. The 6/5/9-membered tricyclic ring skeleton of cladiellins comprises hydroisobenzofuran and oxonane moieties, and possesses three one-carbon branches and one three-carbon branch. Unsaturation and oxygenation at various positions endow structural diversity to this family; however, C4-oxygenated cladiellins are rare. Among these unusual structural features, the conformationally variable 9-membered ring presents an uncommon and formidable challenge for both NMR-based structure determination and chemical synthesis. Herein, we report the collective total synthesis of 12 structurally diverse C4-oxygenated cladiellins, 10 of which were chemically constructed for the first time. In addition, we revised the proposed structures of cladieunicellin D and cladielloide A, and established the previously unknown stereochemistry of cladielloides A/C. To accomplish this multifaceted endeavor, the project was divided into three parts. In the first part, we deduced the most likely stereoisomers of the three structurally ambiguous cladiellins from DP4+ probability analyses. In the second part, a common tricycle was assembled by a radical-polar crossover reaction of α-alkoxyacyl telluride with a 6-membered ring and an aldehyde, a reductive etherification reaction of a 5-membered ring, and a ring-closing metathesis reaction of a 9-membered ring. In the third part, the tricycle was systematically derivatized into 12 cladiellins by devising a series of selective transformations. The described results underscore the importance of designing an advanced common intermediate for collective total synthesis and combining density functional theory (DFT) calculations and syntheses for efficient structure elucidation.</t>
-        </is>
-      </c>
+          <t>Mixture-of-experts based multi-critic deep reinforcement learning for sustainable management of data center microgrids</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr">
         <is>
-          <t>http://dx.doi.org/10.1021/jacs.5c19112</t>
+          <t>https://www.sciencedirect.com/science/article/pii/S0306261926002138?dgcid=rss_sd_all</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -7416,53 +7251,57 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.2980359792709351</v>
+        <v>0.2955213189125061</v>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="n">
-        <v>0.1948529034852982</v>
+        <v>0.1320846974849701</v>
       </c>
       <c r="K51" t="n">
-        <v>0.1972333639860153</v>
+        <v>0.0546480193734169</v>
       </c>
       <c r="L51" t="n">
-        <v>0.2132568359375</v>
+        <v>0.06301382184028625</v>
       </c>
       <c r="M51" t="n">
-        <v>0.2337729334831238</v>
+        <v>0.1090811342000961</v>
       </c>
       <c r="N51" t="n">
-        <v>0.2980359792709351</v>
+        <v>0.1548383831977844</v>
       </c>
       <c r="O51" t="n">
-        <v>0.162337452173233</v>
+        <v>0.0354066900908947</v>
       </c>
       <c r="P51" t="n">
-        <v>0.2206272184848785</v>
+        <v>0.1329715251922607</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.1676791906356812</v>
+        <v>0.2019860595464706</v>
       </c>
       <c r="R51" t="n">
-        <v>0.1100441142916679</v>
+        <v>0.2537469565868378</v>
       </c>
       <c r="S51" t="n">
-        <v>0.07230668514966965</v>
+        <v>0.2955213189125061</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Mixture-of-experts based multi-critic deep reinforcement learning for sustainable management of data center microgrids</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr"/>
+          <t>Gene duplication, horizontal gene transfer, and trait trade-offs drive evolution of postfire resource acquisition in pyrophilous fungi</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Wildfires significantly alter soil carbon (C) and nitrogen (N), reducing microbial richness and biomass, while selecting for “fire-loving” pyrophilous microbes that drive postfire nutrient cycling. However, the genomic strategies and functional trade-offs (balancing gains in one trait with costs in another) underlying the traits that enable pyrophilous microbes to survive and thrive postfire are virtually unknown. We hypothesized that pyrophilous fungi employ specialized genomic adaptations for C and N cycling, with evolutionary trade-offs between traits governing aromatic C degradation, N acquisition pathways, and rapid growth. To test these hypotheses, we performed complementary comparative genomics, transcriptomics after pyrogenic organic matter amendment, and growth rate bioassays for 18 pyrophilous fungi from five Ascomycota (Eurotiales, Pleosporales, Sordariales, Coniochaetales, and Pezizales) and three Basidiomycota (Agaricales, Holtermanniales, and Geminibasidiales) orders isolated from burned soils. We found a dramatic trait trade-off between fast growth and number of genes responsible for aromatic C degradation, implying burned environments select for metabolically costly genes despite their evolutionary cost. We used the comparative genomics framework to evaluate genomic signatures of evolution and found that either gene duplication and somatic mutation, or recombination via sexual reproduction, were the primary drivers of fungal genomic variation in aromatic C degradation and N acquisition genes. Finally, we identified cross-kingdom bacterial to fungal horizontal gene transfer (HGT) as a secondary strategy producing novel aromatic C degradation genes. Overall, we found that trait trade-offs and genome evolutionary strategies are key drivers that may predict the persistence and contribution of pyrophilous fungi to global C and N cycling.</t>
+        </is>
+      </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>https://www.sciencedirect.com/science/article/pii/S0306261926002138?dgcid=rss_sd_all</t>
+          <t>https://www.pnas.org/doi/abs/10.1073/pnas.2519152123?mi=eymic2&amp;af=R&amp;access=on&amp;content=articlesChapters&amp;publication=pnas&amp;sortBy=Earliest&amp;target=default</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7471,57 +7310,57 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.2955213189125061</v>
+        <v>0.2952836751937866</v>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="n">
-        <v>0.1320846974849701</v>
+        <v>0.05537516996264458</v>
       </c>
       <c r="K52" t="n">
-        <v>0.0546480193734169</v>
+        <v>0.1593573391437531</v>
       </c>
       <c r="L52" t="n">
-        <v>0.06301382184028625</v>
+        <v>0.03107214905321598</v>
       </c>
       <c r="M52" t="n">
-        <v>0.1090811342000961</v>
+        <v>0.1691121757030487</v>
       </c>
       <c r="N52" t="n">
-        <v>0.1548383831977844</v>
+        <v>0.2952836751937866</v>
       </c>
       <c r="O52" t="n">
-        <v>0.0354066900908947</v>
+        <v>0.1660727858543396</v>
       </c>
       <c r="P52" t="n">
-        <v>0.1329715251922607</v>
+        <v>0.1485943496227264</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.2019860595464706</v>
+        <v>0.08055032789707184</v>
       </c>
       <c r="R52" t="n">
-        <v>0.2537469565868378</v>
+        <v>0.2016826122999191</v>
       </c>
       <c r="S52" t="n">
-        <v>0.2955213189125061</v>
+        <v>0.1886787116527557</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Gene duplication, horizontal gene transfer, and trait trade-offs drive evolution of postfire resource acquisition in pyrophilous fungi</t>
+          <t>Bioactive bioplastic films incorporating waste-derived carbon dots and starch for sustainable packaging</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Wildfires significantly alter soil carbon (C) and nitrogen (N), reducing microbial richness and biomass, while selecting for “fire-loving” pyrophilous microbes that drive postfire nutrient cycling. However, the genomic strategies and functional trade-offs (balancing gains in one trait with costs in another) underlying the traits that enable pyrophilous microbes to survive and thrive postfire are virtually unknown. We hypothesized that pyrophilous fungi employ specialized genomic adaptations for C and N cycling, with evolutionary trade-offs between traits governing aromatic C degradation, N acquisition pathways, and rapid growth. To test these hypotheses, we performed complementary comparative genomics, transcriptomics after pyrogenic organic matter amendment, and growth rate bioassays for 18 pyrophilous fungi from five Ascomycota (Eurotiales, Pleosporales, Sordariales, Coniochaetales, and Pezizales) and three Basidiomycota (Agaricales, Holtermanniales, and Geminibasidiales) orders isolated from burned soils. We found a dramatic trait trade-off between fast growth and number of genes responsible for aromatic C degradation, implying burned environments select for metabolically costly genes despite their evolutionary cost. We used the comparative genomics framework to evaluate genomic signatures of evolution and found that either gene duplication and somatic mutation, or recombination via sexual reproduction, were the primary drivers of fungal genomic variation in aromatic C degradation and N acquisition genes. Finally, we identified cross-kingdom bacterial to fungal horizontal gene transfer (HGT) as a secondary strategy producing novel aromatic C degradation genes. Overall, we found that trait trade-offs and genome evolutionary strategies are key drivers that may predict the persistence and contribution of pyrophilous fungi to global C and N cycling.</t>
+          <t>Carbon dots (CDs) derived from avocado peel waste were incorporated into a starch-based biopolymer from stale bread, producing sustainable, multifunctional films. Uniform CD dispersion improved mechanical properties, barrier performance, and bioactivity, including antioxidant and antibacterial effects. This circular strategy transforms food waste into high-value packaging materials, providing a scalable, eco-friendly approach for biodegradable bioplastics with potential applications beyond food packaging, including biomedical and environmental uses.</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>https://www.pnas.org/doi/abs/10.1073/pnas.2519152123?mi=eymic2&amp;af=R&amp;access=on&amp;content=articlesChapters&amp;publication=pnas&amp;sortBy=Earliest&amp;target=default</t>
+          <t>https://www.cell.com/matter/fulltext/S2590-2385(25)00663-0?rss=yes</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7530,57 +7369,57 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.2952836751937866</v>
+        <v>0.2906905114650726</v>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="n">
-        <v>0.05537516996264458</v>
+        <v>0.2059457898139954</v>
       </c>
       <c r="K53" t="n">
-        <v>0.1593573391437531</v>
+        <v>0.1276386678218842</v>
       </c>
       <c r="L53" t="n">
-        <v>0.03107214905321598</v>
+        <v>0.2352531999349594</v>
       </c>
       <c r="M53" t="n">
-        <v>0.1691121757030487</v>
+        <v>0.2451967298984528</v>
       </c>
       <c r="N53" t="n">
-        <v>0.2952836751937866</v>
+        <v>0.237490639090538</v>
       </c>
       <c r="O53" t="n">
-        <v>0.1660727858543396</v>
+        <v>0.2906905114650726</v>
       </c>
       <c r="P53" t="n">
-        <v>0.1485943496227264</v>
+        <v>0.2133183479309082</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.08055032789707184</v>
+        <v>0.2155252248048782</v>
       </c>
       <c r="R53" t="n">
-        <v>0.2016826122999191</v>
+        <v>0.1810484528541565</v>
       </c>
       <c r="S53" t="n">
-        <v>0.1886787116527557</v>
+        <v>0.2439803332090378</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Bioactive bioplastic films incorporating waste-derived carbon dots and starch for sustainable packaging</t>
+          <t>Acinetobacter baumannii α2–6‐Legionaminyltransferase‐Catalyzed Synthesis Reveals Legionaminic Acid Form Selectivity by Antibodies in Pooled Human IgGs</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Carbon dots (CDs) derived from avocado peel waste were incorporated into a starch-based biopolymer from stale bread, producing sustainable, multifunctional films. Uniform CD dispersion improved mechanical properties, barrier performance, and bioactivity, including antioxidant and antibacterial effects. This circular strategy transforms food waste into high-value packaging materials, providing a scalable, eco-friendly approach for biodegradable bioplastics with potential applications beyond food packaging, including biomedical and environmental uses.</t>
+          <t>Abstract Legionaminic acids (Legs) are prokaryote‐specific nine‐carbon acidic monosaccharides belonging to the nonulosonic acid (NulO) family. Various Leg forms are found in the polysaccharides or glycoproteins produced by numerous pathogenic bacteria, including capsular polysaccharides of carbapenem‐resistant Acinetobacter baumannii . Hypothetic legionaminyltransferases have been predicted from gene sequences but none has been biochemically validated. In this study we report the first biochemical characterization of a legionaminyltransferase. We demonstrate that AbGtr18 from an A. baumannii K8 strain is a donor promiscuous α2–6‐legionaminyltransferase selective for α‐ N ‐acetylgalactosamine‐glycoside (GalNAcαOR) acceptors. In addition, streamlined chemical synthetic routes, including regio‐selective triflylation and azide substitution processes, were developed to prepare precursors or chemoenzymatic synthons of various forms of Legs. Applying the novel α2–6‐legionaminyltransferase AbGtr18 in one‐pot multienzyme (OPME) synthesis with or without additional chemical derivatization enabled rapid construction of a focused library of NulO‐glycosides (NulOα2–6GalNAcαOR) containing nine NulO forms. Binding and inhibition studies with these compounds revealed selective Leg forms recognized by the antibodies in the pooled human immunoglobulin (IgGs), reflecting natural occurrence of these Leg forms and indicating their prior encounters by human immune systems. AbGtr18 thus emerges as both a potential target for antibiotic development and a powerful biocatalyst for accessing synthetically challenging NulO‐glycosides with therapeutical potentials.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>https://www.cell.com/matter/fulltext/S2590-2385(25)00663-0?rss=yes</t>
+          <t>https://onlinelibrary.wiley.com/doi/10.1002/anie.202519750?af=R</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7589,57 +7428,53 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.2906905114650726</v>
+        <v>0.2903682291507721</v>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="n">
-        <v>0.2059457898139954</v>
+        <v>0.1000539809465408</v>
       </c>
       <c r="K54" t="n">
-        <v>0.1276386678218842</v>
+        <v>0.1729098856449127</v>
       </c>
       <c r="L54" t="n">
-        <v>0.2352531999349594</v>
+        <v>0.1197004392743111</v>
       </c>
       <c r="M54" t="n">
-        <v>0.2451967298984528</v>
+        <v>0.07498285174369812</v>
       </c>
       <c r="N54" t="n">
-        <v>0.237490639090538</v>
+        <v>0.2903682291507721</v>
       </c>
       <c r="O54" t="n">
-        <v>0.2906905114650726</v>
+        <v>0.1628508865833282</v>
       </c>
       <c r="P54" t="n">
-        <v>0.2133183479309082</v>
+        <v>-0.001646480639465153</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.2155252248048782</v>
+        <v>0.1464489847421646</v>
       </c>
       <c r="R54" t="n">
-        <v>0.1810484528541565</v>
+        <v>0.1931858956813812</v>
       </c>
       <c r="S54" t="n">
-        <v>0.2439803332090378</v>
+        <v>0.07857769727706909</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Acinetobacter baumannii α2–6‐Legionaminyltransferase‐Catalyzed Synthesis Reveals Legionaminic Acid Form Selectivity by Antibodies in Pooled Human IgGs</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Abstract Legionaminic acids (Legs) are prokaryote‐specific nine‐carbon acidic monosaccharides belonging to the nonulosonic acid (NulO) family. Various Leg forms are found in the polysaccharides or glycoproteins produced by numerous pathogenic bacteria, including capsular polysaccharides of carbapenem‐resistant Acinetobacter baumannii . Hypothetic legionaminyltransferases have been predicted from gene sequences but none has been biochemically validated. In this study we report the first biochemical characterization of a legionaminyltransferase. We demonstrate that AbGtr18 from an A. baumannii K8 strain is a donor promiscuous α2–6‐legionaminyltransferase selective for α‐ N ‐acetylgalactosamine‐glycoside (GalNAcαOR) acceptors. In addition, streamlined chemical synthetic routes, including regio‐selective triflylation and azide substitution processes, were developed to prepare precursors or chemoenzymatic synthons of various forms of Legs. Applying the novel α2–6‐legionaminyltransferase AbGtr18 in one‐pot multienzyme (OPME) synthesis with or without additional chemical derivatization enabled rapid construction of a focused library of NulO‐glycosides (NulOα2–6GalNAcαOR) containing nine NulO forms. Binding and inhibition studies with these compounds revealed selective Leg forms recognized by the antibodies in the pooled human immunoglobulin (IgGs), reflecting natural occurrence of these Leg forms and indicating their prior encounters by human immune systems. AbGtr18 thus emerges as both a potential target for antibiotic development and a powerful biocatalyst for accessing synthetically challenging NulO‐glycosides with therapeutical potentials.</t>
-        </is>
-      </c>
+          <t>Numerical optimization of aviation decarbonization scenarios: balancing traffic and emissions with maturing energy carriers and aircraft technology</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr">
         <is>
-          <t>https://onlinelibrary.wiley.com/doi/10.1002/anie.202519750?af=R</t>
+          <t>https://www.sciencedirect.com/science/article/pii/S0306261926002837?dgcid=rss_sd_all</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7648,53 +7483,57 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.2903682291507721</v>
+        <v>0.2873866856098175</v>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="n">
-        <v>0.1000539809465408</v>
+        <v>0.07692227512598038</v>
       </c>
       <c r="K55" t="n">
-        <v>0.1729098856449127</v>
+        <v>0.1143270060420036</v>
       </c>
       <c r="L55" t="n">
-        <v>0.1197004392743111</v>
+        <v>0.1134346500039101</v>
       </c>
       <c r="M55" t="n">
-        <v>0.07498285174369812</v>
+        <v>0.0649527832865715</v>
       </c>
       <c r="N55" t="n">
-        <v>0.2903682291507721</v>
+        <v>0.08872009813785553</v>
       </c>
       <c r="O55" t="n">
-        <v>0.1628508865833282</v>
+        <v>0.1465215384960175</v>
       </c>
       <c r="P55" t="n">
-        <v>-0.001646480639465153</v>
+        <v>0.1163707301020622</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.1464489847421646</v>
+        <v>0.2558110654354095</v>
       </c>
       <c r="R55" t="n">
-        <v>0.1931858956813812</v>
+        <v>0.2873866856098175</v>
       </c>
       <c r="S55" t="n">
-        <v>0.07857769727706909</v>
+        <v>0.2831022143363953</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Numerical optimization of aviation decarbonization scenarios: balancing traffic and emissions with maturing energy carriers and aircraft technology</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr"/>
+          <t>[ASAP] Using Mechanochemistry to Activate Poly(vinyl chloride) as a Mechanotunable Brønsted-Acid-Releasing Reagent for Organic Synthesis</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Mechanical force has the potential to activate thermodynamically and chemically stable molecules, enabling unique reactions to proceed with lower activation energies compared to those of conventional thermal activation pathways. However, the practical utility of such force-driven transformations in synthetic chemistry remains to be demonstrated. In this study, we developed a mechanochemical strategy for the facile activation of poly(vinyl chloride) (PVC), a stable plastic material, as a convenient and practical hydrochloric acid (HCl)-releasing reagent. Although HCl can be generated from PVC via thermal decomposition processes, elevated temperatures (&gt;250 °C) are required, which restrict their practical applications in chemical synthesis. In contrast, our mechanochemical approach leverages the mechanical energy generated via ball milling to induce the homolytic cleavage of the polymer chains, producing HCl under mild conditions. Preliminary calculations support that our proposed force-induced mechanoradical-related mechanism generates HCl with lower activation energies than thermal activation. Inspired by this finding, we demonstrate the applicability of PVC as a mechanotunable Brønsted-acid-releasing reagent to facilitate direct SN1-type substitution reactions of allylic and benzylic alcohols with electron-rich (hetero)aromatics, amines, and alcohols as nucleophiles under mild, solvent-free, and moisture-tolerant mechanochemical conditions. Moreover, these reactions proceeded efficiently using PVC-based plastic waste, such as PVC tubing. Beyond the immediate utility of this protocol, this work can be expected to inspire the development of mechanochemical approaches to activate stable, abundant commodity plastic materials for their valorization as chemical reagents in the synthesis of high-value molecules.</t>
+        </is>
+      </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>https://www.sciencedirect.com/science/article/pii/S0306261926002837?dgcid=rss_sd_all</t>
+          <t>http://dx.doi.org/10.1021/jacs.5c20376</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7703,57 +7542,57 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.2873866856098175</v>
+        <v>0.2870927751064301</v>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="n">
-        <v>0.07692227512598038</v>
+        <v>0.2788200080394745</v>
       </c>
       <c r="K56" t="n">
-        <v>0.1143270060420036</v>
+        <v>0.2870927751064301</v>
       </c>
       <c r="L56" t="n">
-        <v>0.1134346500039101</v>
+        <v>0.1826436072587967</v>
       </c>
       <c r="M56" t="n">
-        <v>0.0649527832865715</v>
+        <v>0.1879710704088211</v>
       </c>
       <c r="N56" t="n">
-        <v>0.08872009813785553</v>
+        <v>0.1798471659421921</v>
       </c>
       <c r="O56" t="n">
-        <v>0.1465215384960175</v>
+        <v>0.165313333272934</v>
       </c>
       <c r="P56" t="n">
-        <v>0.1163707301020622</v>
+        <v>0.03754387423396111</v>
       </c>
       <c r="Q56" t="n">
-        <v>0.2558110654354095</v>
+        <v>0.1182014420628548</v>
       </c>
       <c r="R56" t="n">
-        <v>0.2873866856098175</v>
+        <v>0.09191808849573135</v>
       </c>
       <c r="S56" t="n">
-        <v>0.2831022143363953</v>
+        <v>0.05527111142873764</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>[ASAP] Using Mechanochemistry to Activate Poly(vinyl chloride) as a Mechanotunable Brønsted-Acid-Releasing Reagent for Organic Synthesis</t>
+          <t>Direct Recycling of Degraded LiFePO4 Cathode Material via Natural Electron Donors Healing and Targeted Surface Reconstruction</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Mechanical force has the potential to activate thermodynamically and chemically stable molecules, enabling unique reactions to proceed with lower activation energies compared to those of conventional thermal activation pathways. However, the practical utility of such force-driven transformations in synthetic chemistry remains to be demonstrated. In this study, we developed a mechanochemical strategy for the facile activation of poly(vinyl chloride) (PVC), a stable plastic material, as a convenient and practical hydrochloric acid (HCl)-releasing reagent. Although HCl can be generated from PVC via thermal decomposition processes, elevated temperatures (&gt;250 °C) are required, which restrict their practical applications in chemical synthesis. In contrast, our mechanochemical approach leverages the mechanical energy generated via ball milling to induce the homolytic cleavage of the polymer chains, producing HCl under mild conditions. Preliminary calculations support that our proposed force-induced mechanoradical-related mechanism generates HCl with lower activation energies than thermal activation. Inspired by this finding, we demonstrate the applicability of PVC as a mechanotunable Brønsted-acid-releasing reagent to facilitate direct SN1-type substitution reactions of allylic and benzylic alcohols with electron-rich (hetero)aromatics, amines, and alcohols as nucleophiles under mild, solvent-free, and moisture-tolerant mechanochemical conditions. Moreover, these reactions proceeded efficiently using PVC-based plastic waste, such as PVC tubing. Beyond the immediate utility of this protocol, this work can be expected to inspire the development of mechanochemical approaches to activate stable, abundant commodity plastic materials for their valorization as chemical reagents in the synthesis of high-value molecules.</t>
+          <t>Abstract Direct regeneration of spent cathode materials is crucial for the sustainable development of the new energy vehicle industry. However, owing to the lack of targeted surface repair strategies, the regenerated LiFePO 4 (LFP) always faces some issues, such as Fe ions re‐migration and sluggish Li + diffusion, or a serious trade‐off between restored specific capacity and stability. Herein, an integrated bulk and surface restoration strategy is proposed to regenerate spent LFP (S‐LFP) via using natural tea polyphenols as electron donors to reduce Fe (III) phase and heal anti‐site defects in the bulk, and introducing a hybrid AlPO 4 /Li 3 PO 4 (AP/LP) patching coating at the fracture of carbon layer on LFP for targeted surface reconstruction, accompanied by Al doping into the bulk LFP. Theoretical calculations reveal that AP/LP patching coating forms a dual electron‐ and ion‐conducting layer with the residual carbon layer, coupling with strengthened Fe─O bonding by Al doping, to improve kinetics and stability of LFP during cycling. The optimized regenerated LFP cathode exhibits a capacity of 124.3 mAh g −1 after 400 cycles at 2C with a capacity retention of 92.1%. This scalable healing and stabilizing strategy have large potential to strike a balance between specific capacity repairing and stability improvement in the regeneration process.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>http://dx.doi.org/10.1021/jacs.5c20376</t>
+          <t>https://advanced.onlinelibrary.wiley.com/doi/10.1002/adma.202511246?af=R</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7762,57 +7601,57 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.2870927751064301</v>
+        <v>0.2777232229709625</v>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="n">
-        <v>0.2788200080394745</v>
+        <v>0.2387418299913406</v>
       </c>
       <c r="K57" t="n">
-        <v>0.2870927751064301</v>
+        <v>0.120968408882618</v>
       </c>
       <c r="L57" t="n">
-        <v>0.1826436072587967</v>
+        <v>0.2283995151519775</v>
       </c>
       <c r="M57" t="n">
-        <v>0.1879710704088211</v>
+        <v>0.2777232229709625</v>
       </c>
       <c r="N57" t="n">
-        <v>0.1798471659421921</v>
+        <v>0.112954393029213</v>
       </c>
       <c r="O57" t="n">
-        <v>0.165313333272934</v>
+        <v>0.2384909242391586</v>
       </c>
       <c r="P57" t="n">
-        <v>0.03754387423396111</v>
+        <v>0.1430681347846985</v>
       </c>
       <c r="Q57" t="n">
-        <v>0.1182014420628548</v>
+        <v>0.211382120847702</v>
       </c>
       <c r="R57" t="n">
-        <v>0.09191808849573135</v>
+        <v>0.1867611855268478</v>
       </c>
       <c r="S57" t="n">
-        <v>0.05527111142873764</v>
+        <v>0.1552674770355225</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Direct Recycling of Degraded LiFePO4 Cathode Material via Natural Electron Donors Healing and Targeted Surface Reconstruction</t>
+          <t>[ASAP] Electrochemically Initiated Depolymerization of Poly(Methyl Methacrylate)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Abstract Direct regeneration of spent cathode materials is crucial for the sustainable development of the new energy vehicle industry. However, owing to the lack of targeted surface repair strategies, the regenerated LiFePO 4 (LFP) always faces some issues, such as Fe ions re‐migration and sluggish Li + diffusion, or a serious trade‐off between restored specific capacity and stability. Herein, an integrated bulk and surface restoration strategy is proposed to regenerate spent LFP (S‐LFP) via using natural tea polyphenols as electron donors to reduce Fe (III) phase and heal anti‐site defects in the bulk, and introducing a hybrid AlPO 4 /Li 3 PO 4 (AP/LP) patching coating at the fracture of carbon layer on LFP for targeted surface reconstruction, accompanied by Al doping into the bulk LFP. Theoretical calculations reveal that AP/LP patching coating forms a dual electron‐ and ion‐conducting layer with the residual carbon layer, coupling with strengthened Fe─O bonding by Al doping, to improve kinetics and stability of LFP during cycling. The optimized regenerated LFP cathode exhibits a capacity of 124.3 mAh g −1 after 400 cycles at 2C with a capacity retention of 92.1%. This scalable healing and stabilizing strategy have large potential to strike a balance between specific capacity repairing and stability improvement in the regeneration process.</t>
+          <t>Efficient depolymerization of polymers with all-carbon backbones under mild conditions would be valuable in chemically recycling commodity plastics. Poly(methyl methacrylate) (PMMA) is a commodity thermoplastic that is currently depolymerized at temperatures in excess of 400 °C. Herein, we lower the temperatures needed to depolymerize PMMA by performing radical generation and depropagation with orthogonal stimuli. This first demonstration of electrochemically initiated PMMA depolymerization relies on reduction of phthalimide esters that, upon subsequent decarboxylation, generate polymer-centered radicals. These radicals then spontaneously unzip the polymer back to its monomeric constituents at temperatures as low as 105 °C. We studied the mechanism and efficiency of this transformation as a function of phthalimide ester placement, incorporation density, and polymer molecular weight. We found that chain-end activation is effective for modest molecular weights but suffers diminished efficiency at higher degrees of polymerization. In contrast, pendent-group activation is more effective for depolymerizing higher molecular weight species. Integrating higher molar amounts of phthalimide ester pendants leads to more effective depolymerization, with &gt;95% depolymerization in copolymers with 5 mol % phthalimide ester incorporation. We leveraged this understanding to create a custom electro-distillation apparatus that allowed us to simultaneously electrochemically depolymerize PMMA and directly distill methyl methacrylate, which could ultimately be repolymerized. These findings establish electrochemistry as a versatile and orthogonal stimulus for vinyl polymer depolymerization and provide a foundation for closed-loop electrochemical recycling of widely used plastics.</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>https://advanced.onlinelibrary.wiley.com/doi/10.1002/adma.202511246?af=R</t>
+          <t>http://dx.doi.org/10.1021/jacs.5c17930</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7821,57 +7660,57 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.2777232229709625</v>
+        <v>0.2772755324840546</v>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="n">
-        <v>0.2387418299913406</v>
+        <v>0.2211088687181473</v>
       </c>
       <c r="K58" t="n">
-        <v>0.120968408882618</v>
+        <v>0.2642519474029541</v>
       </c>
       <c r="L58" t="n">
-        <v>0.2283995151519775</v>
+        <v>0.2772755324840546</v>
       </c>
       <c r="M58" t="n">
-        <v>0.2777232229709625</v>
+        <v>0.1686611622571945</v>
       </c>
       <c r="N58" t="n">
-        <v>0.112954393029213</v>
+        <v>0.185700386762619</v>
       </c>
       <c r="O58" t="n">
-        <v>0.2384909242391586</v>
+        <v>0.2430597543716431</v>
       </c>
       <c r="P58" t="n">
-        <v>0.1430681347846985</v>
+        <v>0.002998330630362034</v>
       </c>
       <c r="Q58" t="n">
-        <v>0.211382120847702</v>
+        <v>0.243688702583313</v>
       </c>
       <c r="R58" t="n">
-        <v>0.1867611855268478</v>
+        <v>0.0692962184548378</v>
       </c>
       <c r="S58" t="n">
-        <v>0.1552674770355225</v>
+        <v>0.1256504654884338</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>[ASAP] Electrochemically Initiated Depolymerization of Poly(Methyl Methacrylate)</t>
+          <t>Aqua‐Oxidation of Polyethylene Into Carboxylic Acids Under Mild Conditions: A Catalyst‐Free Upcycling Strategy for Nonpolar Plastics</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Efficient depolymerization of polymers with all-carbon backbones under mild conditions would be valuable in chemically recycling commodity plastics. Poly(methyl methacrylate) (PMMA) is a commodity thermoplastic that is currently depolymerized at temperatures in excess of 400 °C. Herein, we lower the temperatures needed to depolymerize PMMA by performing radical generation and depropagation with orthogonal stimuli. This first demonstration of electrochemically initiated PMMA depolymerization relies on reduction of phthalimide esters that, upon subsequent decarboxylation, generate polymer-centered radicals. These radicals then spontaneously unzip the polymer back to its monomeric constituents at temperatures as low as 105 °C. We studied the mechanism and efficiency of this transformation as a function of phthalimide ester placement, incorporation density, and polymer molecular weight. We found that chain-end activation is effective for modest molecular weights but suffers diminished efficiency at higher degrees of polymerization. In contrast, pendent-group activation is more effective for depolymerizing higher molecular weight species. Integrating higher molar amounts of phthalimide ester pendants leads to more effective depolymerization, with &gt;95% depolymerization in copolymers with 5 mol % phthalimide ester incorporation. We leveraged this understanding to create a custom electro-distillation apparatus that allowed us to simultaneously electrochemically depolymerize PMMA and directly distill methyl methacrylate, which could ultimately be repolymerized. These findings establish electrochemistry as a versatile and orthogonal stimulus for vinyl polymer depolymerization and provide a foundation for closed-loop electrochemical recycling of widely used plastics.</t>
+          <t>ABSTRACT Noncatalytic polyolefin upcycling offers distinct advantages in eliminating catalyst costs and enhancing operational stability, yet it remains highly challenging under mild conditions. Herein, we develop an aqua‐oxidation strategy that converts polyethylene into carboxylic acids at 160°C without using any catalysts or organic solvents. The mass yield of carboxylic acid is up to 97.8 wt%, of which 72.1% is comprised by C 4 –C 10 dicarboxylic acids. The roles of H 2 O and O 2 play in aqua‐oxidation were further investigated in an in situ liquid‐phase spectroscopic reactor filled with isotope‐labeled D 2 O. It reveals that O 2 governs the effective initiation and oxidation of polyethylene. Whereas H 2 O serves as a key medium to intensify oxygen–polyethylene interaction uniformly and inhibit localized oxidation, promoting selective upcycling to narrow‐distributed acids. Moreover, this strategy allows for upcycling diverse commercial polyolefins with additives. This study presents a breakthrough in the noncatalytic upcycling of polyolefins under mild conditions and demonstrates the potential of this eco‐friendly and streamlined strategy for advancing plastic circularity.</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>http://dx.doi.org/10.1021/jacs.5c17930</t>
+          <t>https://onlinelibrary.wiley.com/doi/10.1002/anie.202523067?af=R</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7880,57 +7719,57 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.2772755324840546</v>
+        <v>0.2751191854476929</v>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="n">
-        <v>0.2211088687181473</v>
+        <v>0.2287163138389587</v>
       </c>
       <c r="K59" t="n">
-        <v>0.2642519474029541</v>
+        <v>0.2613732814788818</v>
       </c>
       <c r="L59" t="n">
-        <v>0.2772755324840546</v>
+        <v>0.2751191854476929</v>
       </c>
       <c r="M59" t="n">
-        <v>0.1686611622571945</v>
+        <v>0.1538543403148651</v>
       </c>
       <c r="N59" t="n">
-        <v>0.185700386762619</v>
+        <v>0.1966850906610489</v>
       </c>
       <c r="O59" t="n">
-        <v>0.2430597543716431</v>
+        <v>0.225330263376236</v>
       </c>
       <c r="P59" t="n">
-        <v>0.002998330630362034</v>
+        <v>0.09106028079986572</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.243688702583313</v>
+        <v>0.1382820159196854</v>
       </c>
       <c r="R59" t="n">
-        <v>0.0692962184548378</v>
+        <v>0.1519626528024673</v>
       </c>
       <c r="S59" t="n">
-        <v>0.1256504654884338</v>
+        <v>0.117667131125927</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Aqua‐Oxidation of Polyethylene Into Carboxylic Acids Under Mild Conditions: A Catalyst‐Free Upcycling Strategy for Nonpolar Plastics</t>
+          <t>[ASAP] All-Hydrocarbon Polymers with Chemical Recyclability via a Catalyst-Free and Solvent-Free Method</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ABSTRACT Noncatalytic polyolefin upcycling offers distinct advantages in eliminating catalyst costs and enhancing operational stability, yet it remains highly challenging under mild conditions. Herein, we develop an aqua‐oxidation strategy that converts polyethylene into carboxylic acids at 160°C without using any catalysts or organic solvents. The mass yield of carboxylic acid is up to 97.8 wt%, of which 72.1% is comprised by C 4 –C 10 dicarboxylic acids. The roles of H 2 O and O 2 play in aqua‐oxidation were further investigated in an in situ liquid‐phase spectroscopic reactor filled with isotope‐labeled D 2 O. It reveals that O 2 governs the effective initiation and oxidation of polyethylene. Whereas H 2 O serves as a key medium to intensify oxygen–polyethylene interaction uniformly and inhibit localized oxidation, promoting selective upcycling to narrow‐distributed acids. Moreover, this strategy allows for upcycling diverse commercial polyolefins with additives. This study presents a breakthrough in the noncatalytic upcycling of polyolefins under mild conditions and demonstrates the potential of this eco‐friendly and streamlined strategy for advancing plastic circularity.</t>
+          <t>Chemically recyclable polymers are at the forefront of synthetic chemistry and sustainable chemistry, in which the unique recycling process is enabled by the installation of a cleavable C-X (X = heteroatom) unit. Developing chemically recyclable all-hydrocarbon polymers without heteroatoms remains challenging due to the difficulty in the design and installation of a reversible C-C unit. In this study, we utilize the dynamic covalent chemistry of the Diels-Alder cyclopentadienyl (Cp) unit, report the chemically recyclable all-hydrocarbon polymer, and propose the "macromonomer-all-hydrocarbon polymer-macromonomer" recycling loop. Through the design of A2-type Cp2-terminated monomers bearing desired alkyl or aryl spacers, all-hydrocarbon homopolymers, random copolymers, and block copolymers are synthesized at 100 °C respectively via an A2 + A2 Diels-Alder step-growth polycondensation. These all-hydrocarbon polymers have high molecular weights of up to 245.3 kDa and a wide glass transition temperature range from -20 to 133 °C, offering programmable thermomechanical properties, excellent optical properties, extremely low water absorption, and impressive shape memory function. Depolymerization of an all-hydrocarbon polymer via a retro-Diels-Alder mechanism occurs at 250 °C to generate a Cp2-terminated oligomer (A2-type macromonomer), which again repolymerizes at 100 °C to yield the parent all-hydrocarbon polymer with preserved properties. This recycling process is thermo-driven, catalyst-free, solvent-free, and quantitative, indicating a 100% atom economy. These merits enable all-hydrocarbon polymers to be a unique member of an all-carbon-backbone polymer, establishing a new circular polymer.</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>https://onlinelibrary.wiley.com/doi/10.1002/anie.202523067?af=R</t>
+          <t>http://dx.doi.org/10.1021/jacs.5c21514</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7939,57 +7778,53 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.2751191854476929</v>
+        <v>0.2726980149745941</v>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="n">
-        <v>0.2287163138389587</v>
+        <v>0.2572852373123169</v>
       </c>
       <c r="K60" t="n">
-        <v>0.2613732814788818</v>
+        <v>0.2182574570178986</v>
       </c>
       <c r="L60" t="n">
-        <v>0.2751191854476929</v>
+        <v>0.2726980149745941</v>
       </c>
       <c r="M60" t="n">
-        <v>0.1538543403148651</v>
+        <v>0.1355155557394028</v>
       </c>
       <c r="N60" t="n">
-        <v>0.1966850906610489</v>
+        <v>0.1549653112888336</v>
       </c>
       <c r="O60" t="n">
-        <v>0.225330263376236</v>
+        <v>0.1995649039745331</v>
       </c>
       <c r="P60" t="n">
-        <v>0.09106028079986572</v>
+        <v>0.06945084780454636</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.1382820159196854</v>
+        <v>0.1428640335798264</v>
       </c>
       <c r="R60" t="n">
-        <v>0.1519626528024673</v>
+        <v>0.1473093181848526</v>
       </c>
       <c r="S60" t="n">
-        <v>0.117667131125927</v>
+        <v>0.1593245416879654</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>[ASAP] All-Hydrocarbon Polymers with Chemical Recyclability via a Catalyst-Free and Solvent-Free Method</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Chemically recyclable polymers are at the forefront of synthetic chemistry and sustainable chemistry, in which the unique recycling process is enabled by the installation of a cleavable C-X (X = heteroatom) unit. Developing chemically recyclable all-hydrocarbon polymers without heteroatoms remains challenging due to the difficulty in the design and installation of a reversible C-C unit. In this study, we utilize the dynamic covalent chemistry of the Diels-Alder cyclopentadienyl (Cp) unit, report the chemically recyclable all-hydrocarbon polymer, and propose the "macromonomer-all-hydrocarbon polymer-macromonomer" recycling loop. Through the design of A2-type Cp2-terminated monomers bearing desired alkyl or aryl spacers, all-hydrocarbon homopolymers, random copolymers, and block copolymers are synthesized at 100 °C respectively via an A2 + A2 Diels-Alder step-growth polycondensation. These all-hydrocarbon polymers have high molecular weights of up to 245.3 kDa and a wide glass transition temperature range from -20 to 133 °C, offering programmable thermomechanical properties, excellent optical properties, extremely low water absorption, and impressive shape memory function. Depolymerization of an all-hydrocarbon polymer via a retro-Diels-Alder mechanism occurs at 250 °C to generate a Cp2-terminated oligomer (A2-type macromonomer), which again repolymerizes at 100 °C to yield the parent all-hydrocarbon polymer with preserved properties. This recycling process is thermo-driven, catalyst-free, solvent-free, and quantitative, indicating a 100% atom economy. These merits enable all-hydrocarbon polymers to be a unique member of an all-carbon-backbone polymer, establishing a new circular polymer.</t>
-        </is>
-      </c>
+          <t>A transfer learning approach to energy-efficient control of small and medium-sized commercial buildings</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr">
         <is>
-          <t>http://dx.doi.org/10.1021/jacs.5c21514</t>
+          <t>https://www.sciencedirect.com/science/article/pii/S0306261926003971?dgcid=rss_sd_all</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7998,53 +7833,53 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.2726980149745941</v>
+        <v>0.2724075317382812</v>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="n">
-        <v>0.2572852373123169</v>
+        <v>0.1451131701469421</v>
       </c>
       <c r="K61" t="n">
-        <v>0.2182574570178986</v>
+        <v>0.08153136819601059</v>
       </c>
       <c r="L61" t="n">
-        <v>0.2726980149745941</v>
+        <v>0.003589640604332089</v>
       </c>
       <c r="M61" t="n">
-        <v>0.1355155557394028</v>
+        <v>0.02894102223217487</v>
       </c>
       <c r="N61" t="n">
-        <v>0.1549653112888336</v>
+        <v>0.04612055048346519</v>
       </c>
       <c r="O61" t="n">
-        <v>0.1995649039745331</v>
+        <v>0.09494907408952713</v>
       </c>
       <c r="P61" t="n">
-        <v>0.06945084780454636</v>
+        <v>0.07084192335605621</v>
       </c>
       <c r="Q61" t="n">
-        <v>0.1428640335798264</v>
+        <v>0.1834046393632889</v>
       </c>
       <c r="R61" t="n">
-        <v>0.1473093181848526</v>
+        <v>0.2724075317382812</v>
       </c>
       <c r="S61" t="n">
-        <v>0.1593245416879654</v>
+        <v>0.1834460943937302</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A transfer learning approach to energy-efficient control of small and medium-sized commercial buildings</t>
+          <t>Deep-sea robots will search for source of mysterious ‘dark oxygen’</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr">
         <is>
-          <t>https://www.sciencedirect.com/science/article/pii/S0306261926003971?dgcid=rss_sd_all</t>
+          <t>https://www.nature.com/articles/d41586-026-00266-9</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8053,53 +7888,57 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.2724075317382812</v>
+        <v>0.2684940695762634</v>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="n">
-        <v>0.1451131701469421</v>
+        <v>0.2067472040653229</v>
       </c>
       <c r="K62" t="n">
-        <v>0.08153136819601059</v>
+        <v>0.1219362244009972</v>
       </c>
       <c r="L62" t="n">
-        <v>0.003589640604332089</v>
+        <v>0.1156096160411835</v>
       </c>
       <c r="M62" t="n">
-        <v>0.02894102223217487</v>
+        <v>0.1710654944181442</v>
       </c>
       <c r="N62" t="n">
-        <v>0.04612055048346519</v>
+        <v>0.1996285021305084</v>
       </c>
       <c r="O62" t="n">
-        <v>0.09494907408952713</v>
+        <v>0.1506830155849457</v>
       </c>
       <c r="P62" t="n">
-        <v>0.07084192335605621</v>
+        <v>0.2684940695762634</v>
       </c>
       <c r="Q62" t="n">
-        <v>0.1834046393632889</v>
+        <v>0.02911666221916676</v>
       </c>
       <c r="R62" t="n">
-        <v>0.2724075317382812</v>
+        <v>0.03752194344997406</v>
       </c>
       <c r="S62" t="n">
-        <v>0.1834460943937302</v>
+        <v>0.09072794765233994</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Deep-sea robots will search for source of mysterious ‘dark oxygen’</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr"/>
+          <t>[ASAP] Total Synthesis of (±)-Dhilirolide U</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>We report the first total synthesis of (±)-dhilirolide U, a highly oxidized meroterpenoid featuring a densely functionalized 6/6/6/5/5-pentacyclic skeleton. Central to the strategy are a MnIII-mediated cyclization sequence and a Payne-type rearrangement cascade, which together forge a bicyclo[3.2.1]octane fused to a γ-lactone─the defining motif of the dhilirolide natural product family. Both transformations proceed in high yields and with excellent diastereocontrol. Intramolecular Ni-catalyzed conjugate addition was leveraged to install the vicinal quaternary carbon centers. This transformation set the stage for construction of the tetrahydroisochromenone subunit and completion of (±)-dhilirolide U. The reported route to the highly decorated bicyclo[3.2.1]octane provides a blueprint to access the diverse family that are the complex dhilirolide meroterpenoids.</t>
+        </is>
+      </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>https://www.nature.com/articles/d41586-026-00266-9</t>
+          <t>http://dx.doi.org/10.1021/jacs.5c22734</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8108,57 +7947,57 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.2684940695762634</v>
+        <v>0.2681883871555328</v>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="n">
-        <v>0.2067472040653229</v>
+        <v>0.2681883871555328</v>
       </c>
       <c r="K63" t="n">
-        <v>0.1219362244009972</v>
+        <v>0.225828543305397</v>
       </c>
       <c r="L63" t="n">
-        <v>0.1156096160411835</v>
+        <v>0.2163107395172119</v>
       </c>
       <c r="M63" t="n">
-        <v>0.1710654944181442</v>
+        <v>0.1787129640579224</v>
       </c>
       <c r="N63" t="n">
-        <v>0.1996285021305084</v>
+        <v>0.2291835397481918</v>
       </c>
       <c r="O63" t="n">
-        <v>0.1506830155849457</v>
+        <v>0.1577159613370895</v>
       </c>
       <c r="P63" t="n">
-        <v>0.2684940695762634</v>
+        <v>0.09241563081741333</v>
       </c>
       <c r="Q63" t="n">
-        <v>0.02911666221916676</v>
+        <v>0.08195406198501587</v>
       </c>
       <c r="R63" t="n">
-        <v>0.03752194344997406</v>
+        <v>0.08518280833959579</v>
       </c>
       <c r="S63" t="n">
-        <v>0.09072794765233994</v>
+        <v>0.126571461558342</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>[ASAP] Total Synthesis of (±)-Dhilirolide U</t>
+          <t>Structure‐Tunable Fluorinated Polyester Electrolytes with Enhanced Interfacial Stability for Recyclable Solid‐State Lithium Metal Batteries</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>We report the first total synthesis of (±)-dhilirolide U, a highly oxidized meroterpenoid featuring a densely functionalized 6/6/6/5/5-pentacyclic skeleton. Central to the strategy are a MnIII-mediated cyclization sequence and a Payne-type rearrangement cascade, which together forge a bicyclo[3.2.1]octane fused to a γ-lactone─the defining motif of the dhilirolide natural product family. Both transformations proceed in high yields and with excellent diastereocontrol. Intramolecular Ni-catalyzed conjugate addition was leveraged to install the vicinal quaternary carbon centers. This transformation set the stage for construction of the tetrahydroisochromenone subunit and completion of (±)-dhilirolide U. The reported route to the highly decorated bicyclo[3.2.1]octane provides a blueprint to access the diverse family that are the complex dhilirolide meroterpenoids.</t>
+          <t>Abstract Polyesters, with their tunable chemical structures and environmental sustainability, have drawn growing attention as solid polymer electrolytes for next‐generation solid‐state lithium metal batteries (SSLMBs). Through a comprehensive experimental and theoretical study involving the systematic variation of carbon chain lengths in the flexible (diol) and coordinating (diacid) segments, along with selective fluorination at distinct positions along the polymer backbone, 18 types of polyester are fabricated and demonstrate that fluorination at the coordinating segment significantly enhances ionic conductivity by suppressing crystallinity. In contrast, fluorination at the flexible segment reduces ionic migration barriers by providing more homogeneous coordinating sites, thereby improving the lithium‐ion transference number, despite increasing chain rigidity and a reduction in overall ionic conductivity. The optimized fluorinated polyesters exhibit excellent interfacial stability with lithium metal by facilitating the formation of a LiF‐rich solid electrolyte interphase, as supported by experimental and theoretical simulation analysis. More importantly, to enhance cost‐effectiveness and sustainability, a solvent‐based recycling route has been developed, achieving substantial recovery yields and notable environmental benefits. This work provides a versatile molecular design and closed‐loop recovery strategy for fluorinated polyester electrolytes, advancing their practical application in high‐energy and sustainable SSLMBs.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>http://dx.doi.org/10.1021/jacs.5c22734</t>
+          <t>https://advanced.onlinelibrary.wiley.com/doi/10.1002/adma.202511556?af=R</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8167,57 +8006,57 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.2681883871555328</v>
+        <v>0.2681316435337067</v>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="n">
-        <v>0.2681883871555328</v>
+        <v>0.1076240763068199</v>
       </c>
       <c r="K64" t="n">
-        <v>0.225828543305397</v>
+        <v>0.1064996868371964</v>
       </c>
       <c r="L64" t="n">
-        <v>0.2163107395172119</v>
+        <v>0.2558870017528534</v>
       </c>
       <c r="M64" t="n">
-        <v>0.1787129640579224</v>
+        <v>0.201895996928215</v>
       </c>
       <c r="N64" t="n">
-        <v>0.2291835397481918</v>
+        <v>0.1100730374455452</v>
       </c>
       <c r="O64" t="n">
-        <v>0.1577159613370895</v>
+        <v>0.2681316435337067</v>
       </c>
       <c r="P64" t="n">
-        <v>0.09241563081741333</v>
+        <v>0.1236226856708527</v>
       </c>
       <c r="Q64" t="n">
-        <v>0.08195406198501587</v>
+        <v>0.1597414165735245</v>
       </c>
       <c r="R64" t="n">
-        <v>0.08518280833959579</v>
+        <v>0.1657723933458328</v>
       </c>
       <c r="S64" t="n">
-        <v>0.126571461558342</v>
+        <v>0.133614793419838</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Structure‐Tunable Fluorinated Polyester Electrolytes with Enhanced Interfacial Stability for Recyclable Solid‐State Lithium Metal Batteries</t>
+          <t>A Cathepsin B‐Triggered CO‐Releasing Molecule with a Non‐Toxic Metal Core for Targeted Tumor Delivery</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Abstract Polyesters, with their tunable chemical structures and environmental sustainability, have drawn growing attention as solid polymer electrolytes for next‐generation solid‐state lithium metal batteries (SSLMBs). Through a comprehensive experimental and theoretical study involving the systematic variation of carbon chain lengths in the flexible (diol) and coordinating (diacid) segments, along with selective fluorination at distinct positions along the polymer backbone, 18 types of polyester are fabricated and demonstrate that fluorination at the coordinating segment significantly enhances ionic conductivity by suppressing crystallinity. In contrast, fluorination at the flexible segment reduces ionic migration barriers by providing more homogeneous coordinating sites, thereby improving the lithium‐ion transference number, despite increasing chain rigidity and a reduction in overall ionic conductivity. The optimized fluorinated polyesters exhibit excellent interfacial stability with lithium metal by facilitating the formation of a LiF‐rich solid electrolyte interphase, as supported by experimental and theoretical simulation analysis. More importantly, to enhance cost‐effectiveness and sustainability, a solvent‐based recycling route has been developed, achieving substantial recovery yields and notable environmental benefits. This work provides a versatile molecular design and closed‐loop recovery strategy for fluorinated polyester electrolytes, advancing their practical application in high‐energy and sustainable SSLMBs.</t>
+          <t>Abstract Carbon monoxide (CO) has shown therapeutic potential across various diseases, including cancer. To enable controlled delivery, many CO‐releasing molecules (CORMs) have been developed. However, their clinical translation has been limited due to concerns about stability, potential toxicity, and insufficient targeting ability. In this study, we report the synthesis and characterization of an enzyme‐triggered CO‐releasing molecule ( ET‐CORM ) that can be site‐specifically conjugated to antibodies. This novel ET‐CORM is built on a biocompatible iron core, and releases CO upon cleavage by the cancer‐associated protease cathepsin B (CatB). The incorporation of a bioorthogonal handle into ET‐CORM enabled its efficient and site‐specific conjugation to the clinically used antibody trastuzumab via the interchain disulfide bonds. The resulting ET‐CORM–antibody conjugate ( ET‐CORM‐Ab ) exhibited an average drug‐to‐antibody ratio (DAR) of 6.8, corresponding to approximately 20 CO molecules per conjugate. This construct allowed for selective intracellular CO delivery to HER2‐overexpressing and CatB‐expressing cells in vitro. This study represents a metal‐based CORM–antibody conjugate activated by a tumor‐associated enzymatic trigger, opening new avenues for investigating CO‐mediated effects and advancing CO‐based cancer therapies to the clinics.</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>https://advanced.onlinelibrary.wiley.com/doi/10.1002/adma.202511556?af=R</t>
+          <t>https://onlinelibrary.wiley.com/doi/10.1002/anie.202513808?af=R</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8226,57 +8065,53 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.2681316435337067</v>
+        <v>0.2617363333702087</v>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="n">
-        <v>0.1076240763068199</v>
+        <v>0.2065532505512238</v>
       </c>
       <c r="K65" t="n">
-        <v>0.1064996868371964</v>
+        <v>0.2413516938686371</v>
       </c>
       <c r="L65" t="n">
-        <v>0.2558870017528534</v>
+        <v>0.1578679978847504</v>
       </c>
       <c r="M65" t="n">
-        <v>0.201895996928215</v>
+        <v>0.1585894227027893</v>
       </c>
       <c r="N65" t="n">
-        <v>0.1100730374455452</v>
+        <v>0.2617363333702087</v>
       </c>
       <c r="O65" t="n">
-        <v>0.2681316435337067</v>
+        <v>0.1974778026342392</v>
       </c>
       <c r="P65" t="n">
-        <v>0.1236226856708527</v>
+        <v>0.08843986690044403</v>
       </c>
       <c r="Q65" t="n">
-        <v>0.1597414165735245</v>
+        <v>0.1336179375648499</v>
       </c>
       <c r="R65" t="n">
-        <v>0.1657723933458328</v>
+        <v>0.08414635807275772</v>
       </c>
       <c r="S65" t="n">
-        <v>0.133614793419838</v>
+        <v>0.0791228711605072</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A Cathepsin B‐Triggered CO‐Releasing Molecule with a Non‐Toxic Metal Core for Targeted Tumor Delivery</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Abstract Carbon monoxide (CO) has shown therapeutic potential across various diseases, including cancer. To enable controlled delivery, many CO‐releasing molecules (CORMs) have been developed. However, their clinical translation has been limited due to concerns about stability, potential toxicity, and insufficient targeting ability. In this study, we report the synthesis and characterization of an enzyme‐triggered CO‐releasing molecule ( ET‐CORM ) that can be site‐specifically conjugated to antibodies. This novel ET‐CORM is built on a biocompatible iron core, and releases CO upon cleavage by the cancer‐associated protease cathepsin B (CatB). The incorporation of a bioorthogonal handle into ET‐CORM enabled its efficient and site‐specific conjugation to the clinically used antibody trastuzumab via the interchain disulfide bonds. The resulting ET‐CORM–antibody conjugate ( ET‐CORM‐Ab ) exhibited an average drug‐to‐antibody ratio (DAR) of 6.8, corresponding to approximately 20 CO molecules per conjugate. This construct allowed for selective intracellular CO delivery to HER2‐overexpressing and CatB‐expressing cells in vitro. This study represents a metal‐based CORM–antibody conjugate activated by a tumor‐associated enzymatic trigger, opening new avenues for investigating CO‐mediated effects and advancing CO‐based cancer therapies to the clinics.</t>
-        </is>
-      </c>
+          <t>Decarbonizing construction machinery: Data-driven lifecycle assessment of a hydraulic excavator using electrified and alternative-fuel hybrid power systems</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr">
         <is>
-          <t>https://onlinelibrary.wiley.com/doi/10.1002/anie.202513808?af=R</t>
+          <t>https://www.sciencedirect.com/science/article/pii/S030626192600293X?dgcid=rss_sd_all</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8285,53 +8120,57 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.2617363333702087</v>
+        <v>0.2613231837749481</v>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="n">
-        <v>0.2065532505512238</v>
+        <v>0.01176231261342764</v>
       </c>
       <c r="K66" t="n">
-        <v>0.2413516938686371</v>
+        <v>0.07589057832956314</v>
       </c>
       <c r="L66" t="n">
-        <v>0.1578679978847504</v>
+        <v>0.1036296933889389</v>
       </c>
       <c r="M66" t="n">
-        <v>0.1585894227027893</v>
+        <v>0.1414066851139069</v>
       </c>
       <c r="N66" t="n">
-        <v>0.2617363333702087</v>
+        <v>0.04448666051030159</v>
       </c>
       <c r="O66" t="n">
-        <v>0.1974778026342392</v>
+        <v>0.07163386046886444</v>
       </c>
       <c r="P66" t="n">
-        <v>0.08843986690044403</v>
+        <v>0.2321275770664215</v>
       </c>
       <c r="Q66" t="n">
-        <v>0.1336179375648499</v>
+        <v>0.2010591626167297</v>
       </c>
       <c r="R66" t="n">
-        <v>0.08414635807275772</v>
+        <v>0.2613231837749481</v>
       </c>
       <c r="S66" t="n">
-        <v>0.0791228711605072</v>
+        <v>0.1967612951993942</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Decarbonizing construction machinery: Data-driven lifecycle assessment of a hydraulic excavator using electrified and alternative-fuel hybrid power systems</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr"/>
+          <t>Grazer exclusion is associated with higher fast-cycling carbon pools but lower slow-cycling mineral-associated carbon across grasslands</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>The removal of livestock grazers from historically grazed grasslands is widely proposed as a key strategy for the enhancement of soil organic carbon (SOC) for climate mitigation. Yet, accurate assessments of how grazer exclusion impacts SOC pools of differing stability are lacking, with most studies focusing on total SOC rather than the distribution of SOC within fast and more stable, slow-cycling pools. Here, we used 12 historically grazed grassland sites along an 800 km south-north gradient across the United Kingdom to test how particulate (POC) and mineral-associated organic carbon (MAOC) pools were linked to long-term (&gt;10 y) exclusion of large domesticated grazers. We found that grazer exclusion was associated with relatively higher fast-cycling C pools, including plant and litter C, and to a lesser extent POC, but lower more stable, slow-cycling MAOC pools compared to grazed controls. Grazer exclusion was also associated with a marked shift in vegetation composition, with greater cover of ericoid mycorrhizal (ErM) shrubs over arbuscular mycorrhizal (AM) graminoids. This vegetation shift likely played a dual role in regulating SOC, contributing to higher POC via both the input of recalcitrant litter and by the enhancement of soil moisture and lower MAOC due to priming and decreased mineral protection of SOC. Our findings provide evidence that while the exclusion of grazers tends to favor fast-cycling C pools, it coincides with lower SOC persistence, potentially increasing the vulnerability of grassland SOC stocks to future climate change.</t>
+        </is>
+      </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>https://www.sciencedirect.com/science/article/pii/S030626192600293X?dgcid=rss_sd_all</t>
+          <t>https://www.pnas.org/doi/abs/10.1073/pnas.2512048123?mi=eymic2&amp;af=R&amp;access=on&amp;content=articlesChapters&amp;publication=pnas&amp;sortBy=Earliest&amp;target=default</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8340,53 +8179,57 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.2613231837749481</v>
+        <v>0.2479619979858398</v>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="n">
-        <v>0.01176231261342764</v>
+        <v>0.2240615338087082</v>
       </c>
       <c r="K67" t="n">
-        <v>0.07589057832956314</v>
+        <v>0.1174910515546799</v>
       </c>
       <c r="L67" t="n">
-        <v>0.1036296933889389</v>
+        <v>0.07263962179422379</v>
       </c>
       <c r="M67" t="n">
-        <v>0.1414066851139069</v>
+        <v>0.2479619979858398</v>
       </c>
       <c r="N67" t="n">
-        <v>0.04448666051030159</v>
+        <v>0.237274244427681</v>
       </c>
       <c r="O67" t="n">
-        <v>0.07163386046886444</v>
+        <v>0.2292270362377167</v>
       </c>
       <c r="P67" t="n">
-        <v>0.2321275770664215</v>
+        <v>0.2212507724761963</v>
       </c>
       <c r="Q67" t="n">
-        <v>0.2010591626167297</v>
+        <v>0.1832579076290131</v>
       </c>
       <c r="R67" t="n">
-        <v>0.2613231837749481</v>
+        <v>0.1869437247514725</v>
       </c>
       <c r="S67" t="n">
-        <v>0.1967612951993942</v>
+        <v>0.2383932918310165</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Svante Advances New BECCS Project At US Paper Mill</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr"/>
+          <t>Electron‐Rich Niobium Oxide Sub‐Nanoclusters Boosting Charge Transfer for Highly Reversible Sodium–Sulfur Batteries</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Abstract Ether‐based room‐temperature sodium–sulfur (RT Na─S) batteries are a promising energy‐storage system, yet hindered by the unregulated sulfur redox pathway, severe polysulfide shuttling and rapid capacity fading. Herein, highly unsaturated niobium‐oxide sub‐nanoclusters (≈0.7 nm) anchored on defective carbon black (NbO x ‐DCB) as a dynamic sulfur‐conversion catalyst are introduced. The delocalized Nb d‐electrons in the sub‐nanocluster configuration create a mixed Nb 4+ /Nb 5+ valence state that functions as a bidirectional electron reservoir, thereby enabling a distinct d ‐band‐center self‐regulation mechanism. The strong d – p orbital coupling enabled by a Nb 4+ ‐rich surface effectively captures sodium polysulfides and accelerates sulfur conversion kinetics during discharge, while a Nb 5+ ‐rich surface promotes facile solid‐polysulfide decomposition during charging. Consequently, the NbO x ‐DCB/S cathode delivers a reversible capacity of 1184 mAh g S −1 at 0.1 A g −1 after 100 cycles and retains 547 mAh g S −1 after 3000 cycles at 2 A g −1 , corresponding to a decay rate of 0.0027% per cycle. The general applicability of this approach is validated by high‐performance tungsten and vanadium oxide sub‐nanocluster‐based sulfur cathodes. These findings highlight sub‐nanoscale metal‐oxide engineering as a versatile route to high‐performance RT Na–S batteries.</t>
+        </is>
+      </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>https://carbonherald.com/svante-advances-new-beccs-project-at-us-paper-mill/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=svante-advances-new-beccs-project-at-us-paper-mill</t>
+          <t>https://advanced.onlinelibrary.wiley.com/doi/10.1002/adma.202509954?af=R</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8395,57 +8238,57 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.2523589730262756</v>
+        <v>0.2443980723619461</v>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="n">
-        <v>0.1363866776227951</v>
+        <v>0.2443980723619461</v>
       </c>
       <c r="K68" t="n">
-        <v>0.1195920631289482</v>
+        <v>0.1639363020658493</v>
       </c>
       <c r="L68" t="n">
-        <v>0.08029191941022873</v>
+        <v>0.2091448158025742</v>
       </c>
       <c r="M68" t="n">
-        <v>0.1071798205375671</v>
+        <v>0.1646253615617752</v>
       </c>
       <c r="N68" t="n">
-        <v>0.05936072021722794</v>
+        <v>0.08216958492994308</v>
       </c>
       <c r="O68" t="n">
-        <v>0.09031722694635391</v>
+        <v>0.1491861492395401</v>
       </c>
       <c r="P68" t="n">
-        <v>0.1902538985013962</v>
+        <v>0.1201169565320015</v>
       </c>
       <c r="Q68" t="n">
-        <v>0.224038302898407</v>
+        <v>0.1355596035718918</v>
       </c>
       <c r="R68" t="n">
-        <v>0.1854538172483444</v>
+        <v>0.1085072904825211</v>
       </c>
       <c r="S68" t="n">
-        <v>0.2523589730262756</v>
+        <v>0.1758030503988266</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Grazer exclusion is associated with higher fast-cycling carbon pools but lower slow-cycling mineral-associated carbon across grasslands</t>
+          <t>(Poly)Borylated Species as Modern Reactive Groups toward Unusual Synthetic Applications</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>The removal of livestock grazers from historically grazed grasslands is widely proposed as a key strategy for the enhancement of soil organic carbon (SOC) for climate mitigation. Yet, accurate assessments of how grazer exclusion impacts SOC pools of differing stability are lacking, with most studies focusing on total SOC rather than the distribution of SOC within fast and more stable, slow-cycling pools. Here, we used 12 historically grazed grassland sites along an 800 km south-north gradient across the United Kingdom to test how particulate (POC) and mineral-associated organic carbon (MAOC) pools were linked to long-term (&gt;10 y) exclusion of large domesticated grazers. We found that grazer exclusion was associated with relatively higher fast-cycling C pools, including plant and litter C, and to a lesser extent POC, but lower more stable, slow-cycling MAOC pools compared to grazed controls. Grazer exclusion was also associated with a marked shift in vegetation composition, with greater cover of ericoid mycorrhizal (ErM) shrubs over arbuscular mycorrhizal (AM) graminoids. This vegetation shift likely played a dual role in regulating SOC, contributing to higher POC via both the input of recalcitrant litter and by the enhancement of soil moisture and lower MAOC due to priming and decreased mineral protection of SOC. Our findings provide evidence that while the exclusion of grazers tends to favor fast-cycling C pools, it coincides with lower SOC persistence, potentially increasing the vulnerability of grassland SOC stocks to future climate change.</t>
+          <t>Abstract (Poly)borylated species, molecules bearing multiple carbon–boron groups, have emerged as powerful building blocks in modern synthetic chemistry owing to their rich, tunable reactivity. Their distinctive steric and electronic properties, together with their ability to participate in both ionic and radical pathways, make them uniquely versatile synthons for the selective construction of carbon─carbon and carbon─heteroatom bonds. These frameworks provide strategic opportunities for late‐stage functionalization and the assembly of architecturally complex molecules. This review highlights recent advances in the chemistry of (poly)borylated compounds, particularly molecules bearing multiple boron substituents on a single carbon site, with emphasis on their anionic, cationic, radical, alkene, 1,2‐diradical, and carbene‐based variants. It underscores the synergistic behavior of these multiple boron‐substituted reactive carbon‐centered intermediates and the diverse functionalization of C─metalloid bonds. Key reactivity modes are examined across structural classes such as gem ‐diborylalkanes, gem ‐diborylalkenes, 1,1,2‐polyborylated systems, and emerging tri‐ and tetra‐borylated frameworks. Central transformations include transition‐metal‐catalyzed cross‐couplings, stereoselective transmetalation and functionalizations, addition reactions, and polymerizations, along with boron‐masking, boron‐retentive, and boron‐eliminative strategies. Furthermore, alkylations, radical‐mediated reactions, and energy‐transfer photocatalysis pathways are critically discussed. By elucidating the mechanistic principles and synthetic potential of (poly)borylated species, this review aims to provide a unified framework to better understand their reactivity and to highlight the significant advances made since 2019 at the interface of organoboron chemistry, catalysis, and advanced materials science.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>https://www.pnas.org/doi/abs/10.1073/pnas.2512048123?mi=eymic2&amp;af=R&amp;access=on&amp;content=articlesChapters&amp;publication=pnas&amp;sortBy=Earliest&amp;target=default</t>
+          <t>https://onlinelibrary.wiley.com/doi/10.1002/anie.202520748?af=R</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8454,57 +8297,57 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.2479619979858398</v>
+        <v>0.2437034994363785</v>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="n">
-        <v>0.2240615338087082</v>
+        <v>0.2437034994363785</v>
       </c>
       <c r="K69" t="n">
-        <v>0.1174910515546799</v>
+        <v>0.2182867079973221</v>
       </c>
       <c r="L69" t="n">
-        <v>0.07263962179422379</v>
+        <v>0.2335806041955948</v>
       </c>
       <c r="M69" t="n">
-        <v>0.2479619979858398</v>
+        <v>0.2138469666242599</v>
       </c>
       <c r="N69" t="n">
-        <v>0.237274244427681</v>
+        <v>0.1445961743593216</v>
       </c>
       <c r="O69" t="n">
-        <v>0.2292270362377167</v>
+        <v>0.1756410300731659</v>
       </c>
       <c r="P69" t="n">
-        <v>0.2212507724761963</v>
+        <v>0.1099963188171387</v>
       </c>
       <c r="Q69" t="n">
-        <v>0.1832579076290131</v>
+        <v>0.1334860026836395</v>
       </c>
       <c r="R69" t="n">
-        <v>0.1869437247514725</v>
+        <v>0.1143390610814095</v>
       </c>
       <c r="S69" t="n">
-        <v>0.2383932918310165</v>
+        <v>0.1250109970569611</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Electron‐Rich Niobium Oxide Sub‐Nanoclusters Boosting Charge Transfer for Highly Reversible Sodium–Sulfur Batteries</t>
+          <t>Hierarchical, Template‐Controlled Self‐Assembly of Two Different Organometallic Capsules from a Tetrakisimidazolium Salt</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Abstract Ether‐based room‐temperature sodium–sulfur (RT Na─S) batteries are a promising energy‐storage system, yet hindered by the unregulated sulfur redox pathway, severe polysulfide shuttling and rapid capacity fading. Herein, highly unsaturated niobium‐oxide sub‐nanoclusters (≈0.7 nm) anchored on defective carbon black (NbO x ‐DCB) as a dynamic sulfur‐conversion catalyst are introduced. The delocalized Nb d‐electrons in the sub‐nanocluster configuration create a mixed Nb 4+ /Nb 5+ valence state that functions as a bidirectional electron reservoir, thereby enabling a distinct d ‐band‐center self‐regulation mechanism. The strong d – p orbital coupling enabled by a Nb 4+ ‐rich surface effectively captures sodium polysulfides and accelerates sulfur conversion kinetics during discharge, while a Nb 5+ ‐rich surface promotes facile solid‐polysulfide decomposition during charging. Consequently, the NbO x ‐DCB/S cathode delivers a reversible capacity of 1184 mAh g S −1 at 0.1 A g −1 after 100 cycles and retains 547 mAh g S −1 after 3000 cycles at 2 A g −1 , corresponding to a decay rate of 0.0027% per cycle. The general applicability of this approach is validated by high‐performance tungsten and vanadium oxide sub‐nanocluster‐based sulfur cathodes. These findings highlight sub‐nanoscale metal‐oxide engineering as a versatile route to high‐performance RT Na–S batteries.</t>
+          <t>Abstract Controlling the assembly of molecular nanocapsules through metal‐carbon bonds constitutes a major challenge in the field of supramolecular organometallic chemistry. Here, we demonstrate the construction of two nanosized dodecanuclear organometallic capsules, [{Ag(CH 3 CN) 4 (BF 4 ) 8 }⊂Ag 12 ( 1 ) 6 ](BF 4 ) 5 and [(CF 3 SO 3 ) 8 ⊂Ag 12 ( 1 ) 6 ](CF 3 SO 3 ) 4 from the calix[4]resorcinarene‐based tetrakisimidazolium salts H 4 ‐ 1 (X) 4 and Ag I ions employing the metal‐carbene directed self‐assembly and hierarchical template strategies. An [Ag(CH 3 CH) 4 (BF 4 ) 8 ] 7− anion or eight triflate anions served as templates. The dodecanuclear capsules are the largest poly‐NHC‐derived assemblies known so far. Salt H 4 ‐ 1 (SbF 6 ) 4 reacts with Ag 2 O to give the tetranuclear assembly [(SbF 6 )⊂Ag 4 ( 1 ) 2 ](SbF 6 ) 3 featuring an encapsulated SbF 6 − anion. Transmetalation of the tetra‐NHC ligands from silver to gold yielded in all cases tetranuclear assemblies of type [Au 4 ( 1 ) 2 ]X 4 .</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>https://advanced.onlinelibrary.wiley.com/doi/10.1002/adma.202509954?af=R</t>
+          <t>https://onlinelibrary.wiley.com/doi/10.1002/anie.202520814?af=R</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8513,57 +8356,57 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.2443980723619461</v>
+        <v>0.2402537167072296</v>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="n">
-        <v>0.2443980723619461</v>
+        <v>0.1607654243707657</v>
       </c>
       <c r="K70" t="n">
-        <v>0.1639363020658493</v>
+        <v>0.148959681391716</v>
       </c>
       <c r="L70" t="n">
-        <v>0.2091448158025742</v>
+        <v>0.1769839525222778</v>
       </c>
       <c r="M70" t="n">
-        <v>0.1646253615617752</v>
+        <v>0.1177339851856232</v>
       </c>
       <c r="N70" t="n">
-        <v>0.08216958492994308</v>
+        <v>0.1253965944051743</v>
       </c>
       <c r="O70" t="n">
-        <v>0.1491861492395401</v>
+        <v>0.2402537167072296</v>
       </c>
       <c r="P70" t="n">
-        <v>0.1201169565320015</v>
+        <v>0.07715091109275818</v>
       </c>
       <c r="Q70" t="n">
-        <v>0.1355596035718918</v>
+        <v>0.09613330662250519</v>
       </c>
       <c r="R70" t="n">
-        <v>0.1085072904825211</v>
+        <v>0.04252269491553307</v>
       </c>
       <c r="S70" t="n">
-        <v>0.1758030503988266</v>
+        <v>0.0432797446846962</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>(Poly)Borylated Species as Modern Reactive Groups toward Unusual Synthetic Applications</t>
+          <t>Sequential Heterolytic Carbon‐Halide and Carbon–Carbon Bond Activation in Unactivated Piperidines</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Abstract (Poly)borylated species, molecules bearing multiple carbon–boron groups, have emerged as powerful building blocks in modern synthetic chemistry owing to their rich, tunable reactivity. Their distinctive steric and electronic properties, together with their ability to participate in both ionic and radical pathways, make them uniquely versatile synthons for the selective construction of carbon─carbon and carbon─heteroatom bonds. These frameworks provide strategic opportunities for late‐stage functionalization and the assembly of architecturally complex molecules. This review highlights recent advances in the chemistry of (poly)borylated compounds, particularly molecules bearing multiple boron substituents on a single carbon site, with emphasis on their anionic, cationic, radical, alkene, 1,2‐diradical, and carbene‐based variants. It underscores the synergistic behavior of these multiple boron‐substituted reactive carbon‐centered intermediates and the diverse functionalization of C─metalloid bonds. Key reactivity modes are examined across structural classes such as gem ‐diborylalkanes, gem ‐diborylalkenes, 1,1,2‐polyborylated systems, and emerging tri‐ and tetra‐borylated frameworks. Central transformations include transition‐metal‐catalyzed cross‐couplings, stereoselective transmetalation and functionalizations, addition reactions, and polymerizations, along with boron‐masking, boron‐retentive, and boron‐eliminative strategies. Furthermore, alkylations, radical‐mediated reactions, and energy‐transfer photocatalysis pathways are critically discussed. By elucidating the mechanistic principles and synthetic potential of (poly)borylated species, this review aims to provide a unified framework to better understand their reactivity and to highlight the significant advances made since 2019 at the interface of organoboron chemistry, catalysis, and advanced materials science.</t>
+          <t>Abstract The thermodynamic stability of unactivated Csp 3 ─F and Csp 3 ─Csp 3 bonds remains a major challenge in organic synthesis as methods that achieve effective cleavage and high‐yielding functionalization under mild conditions are rare. Herein, we introduce a cascade reaction involving heterolytic activation of 4‐halopiperidines with organoaluminum reagents which is followed by fast ring opening toward a thermodynamically favored iminium ion that undergoes C─C bond formation via aryl or alkyl transfer from a concomitantly generated fluoroaluminate counteranion. Fluoropiperidines were found to be more reactive than other halides and are smoothly transformed into tertiary homoallyl amines with good to excellent yields. This reaction occurs at room temperature with high functional group tolerance and without noticeable by‐product formation. Similarly, Csp 3 ─F bond scission is observed with 4,4‐difluoropiperidines, giving rise to monofluorinated alkene products as the Csp 2 ─F bond generated during this process does not react. X‐ray crystallographic analysis of two cationic reaction intermediates simultaneously isolated in a single crystal provides a snapshot of the ring‐opening process and together with chemical trapping and control experiments is in agreement with an ionic mechanism and a three‐step reaction sequence. By contrast, defluorinative halide exchange leaving the piperidinyl ring intact prevails when 4‐fluoro‐ and 4,4‐difluoropiperidines are treated with aluminum trihalide Lewis acids.</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>https://onlinelibrary.wiley.com/doi/10.1002/anie.202520748?af=R</t>
+          <t>https://onlinelibrary.wiley.com/doi/10.1002/anie.202512579?af=R</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8572,57 +8415,53 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.2437034994363785</v>
+        <v>0.2349510788917542</v>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="n">
-        <v>0.2437034994363785</v>
+        <v>0.2091465592384338</v>
       </c>
       <c r="K71" t="n">
-        <v>0.2182867079973221</v>
+        <v>0.2109045386314392</v>
       </c>
       <c r="L71" t="n">
-        <v>0.2335806041955948</v>
+        <v>0.1739977896213531</v>
       </c>
       <c r="M71" t="n">
-        <v>0.2138469666242599</v>
+        <v>0.1897228062152863</v>
       </c>
       <c r="N71" t="n">
-        <v>0.1445961743593216</v>
+        <v>0.2349510788917542</v>
       </c>
       <c r="O71" t="n">
-        <v>0.1756410300731659</v>
+        <v>0.1924907267093658</v>
       </c>
       <c r="P71" t="n">
-        <v>0.1099963188171387</v>
+        <v>0.06132102012634277</v>
       </c>
       <c r="Q71" t="n">
-        <v>0.1334860026836395</v>
+        <v>0.1255578994750977</v>
       </c>
       <c r="R71" t="n">
-        <v>0.1143390610814095</v>
+        <v>0.1464055478572845</v>
       </c>
       <c r="S71" t="n">
-        <v>0.1250109970569611</v>
+        <v>0.1269901245832443</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Hierarchical, Template‐Controlled Self‐Assembly of Two Different Organometallic Capsules from a Tetrakisimidazolium Salt</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Abstract Controlling the assembly of molecular nanocapsules through metal‐carbon bonds constitutes a major challenge in the field of supramolecular organometallic chemistry. Here, we demonstrate the construction of two nanosized dodecanuclear organometallic capsules, [{Ag(CH 3 CN) 4 (BF 4 ) 8 }⊂Ag 12 ( 1 ) 6 ](BF 4 ) 5 and [(CF 3 SO 3 ) 8 ⊂Ag 12 ( 1 ) 6 ](CF 3 SO 3 ) 4 from the calix[4]resorcinarene‐based tetrakisimidazolium salts H 4 ‐ 1 (X) 4 and Ag I ions employing the metal‐carbene directed self‐assembly and hierarchical template strategies. An [Ag(CH 3 CH) 4 (BF 4 ) 8 ] 7− anion or eight triflate anions served as templates. The dodecanuclear capsules are the largest poly‐NHC‐derived assemblies known so far. Salt H 4 ‐ 1 (SbF 6 ) 4 reacts with Ag 2 O to give the tetranuclear assembly [(SbF 6 )⊂Ag 4 ( 1 ) 2 ](SbF 6 ) 3 featuring an encapsulated SbF 6 − anion. Transmetalation of the tetra‐NHC ligands from silver to gold yielded in all cases tetranuclear assemblies of type [Au 4 ( 1 ) 2 ]X 4 .</t>
-        </is>
-      </c>
+          <t>Volatility modeling in energy commodity markets: A review of responses to shocks and the path towards resiliency and sustainability</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr">
         <is>
-          <t>https://onlinelibrary.wiley.com/doi/10.1002/anie.202520814?af=R</t>
+          <t>https://www.sciencedirect.com/science/article/pii/S0306261926002114?dgcid=rss_sd_all</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8631,57 +8470,57 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.2402537167072296</v>
+        <v>0.2336919009685516</v>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="n">
-        <v>0.1607654243707657</v>
+        <v>0.06262164562940598</v>
       </c>
       <c r="K72" t="n">
-        <v>0.148959681391716</v>
+        <v>0.07224398106336594</v>
       </c>
       <c r="L72" t="n">
-        <v>0.1769839525222778</v>
+        <v>0.1314468383789062</v>
       </c>
       <c r="M72" t="n">
-        <v>0.1177339851856232</v>
+        <v>0.1139631271362305</v>
       </c>
       <c r="N72" t="n">
-        <v>0.1253965944051743</v>
+        <v>0.04860568791627884</v>
       </c>
       <c r="O72" t="n">
-        <v>0.2402537167072296</v>
+        <v>0.03298217430710793</v>
       </c>
       <c r="P72" t="n">
-        <v>0.07715091109275818</v>
+        <v>0.09166080504655838</v>
       </c>
       <c r="Q72" t="n">
-        <v>0.09613330662250519</v>
+        <v>0.06152238696813583</v>
       </c>
       <c r="R72" t="n">
-        <v>0.04252269491553307</v>
+        <v>0.1941447854042053</v>
       </c>
       <c r="S72" t="n">
-        <v>0.0432797446846962</v>
+        <v>0.2336919009685516</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sequential Heterolytic Carbon‐Halide and Carbon–Carbon Bond Activation in Unactivated Piperidines</t>
+          <t>Chiral Single‐Atom Nanozymes‐Enabled ROS Catalysis and Metal Transport Regulation Cooperatively Induce Ferroptosis to Treat Bacterial Infections</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Abstract The thermodynamic stability of unactivated Csp 3 ─F and Csp 3 ─Csp 3 bonds remains a major challenge in organic synthesis as methods that achieve effective cleavage and high‐yielding functionalization under mild conditions are rare. Herein, we introduce a cascade reaction involving heterolytic activation of 4‐halopiperidines with organoaluminum reagents which is followed by fast ring opening toward a thermodynamically favored iminium ion that undergoes C─C bond formation via aryl or alkyl transfer from a concomitantly generated fluoroaluminate counteranion. Fluoropiperidines were found to be more reactive than other halides and are smoothly transformed into tertiary homoallyl amines with good to excellent yields. This reaction occurs at room temperature with high functional group tolerance and without noticeable by‐product formation. Similarly, Csp 3 ─F bond scission is observed with 4,4‐difluoropiperidines, giving rise to monofluorinated alkene products as the Csp 2 ─F bond generated during this process does not react. X‐ray crystallographic analysis of two cationic reaction intermediates simultaneously isolated in a single crystal provides a snapshot of the ring‐opening process and together with chemical trapping and control experiments is in agreement with an ionic mechanism and a three‐step reaction sequence. By contrast, defluorinative halide exchange leaving the piperidinyl ring intact prevails when 4‐fluoro‐ and 4,4‐difluoropiperidines are treated with aluminum trihalide Lewis acids.</t>
+          <t>ABSTRACT Nanozyme‐driven ferroptosis provides a promising therapeutic strategy against drug‐resistant bacterial infections by inducing iron overload and oxidative stress. However, bacterial metal transport proteins (MTP) and antioxidant systems can reduce iron accumulation and lipid peroxidation, limiting the efficacy of ferroptosis‐based therapies and promoting resistance. Single‐atom and chiral nanozymes, with their high atomic utilization and catalytic specificity, may provide an effective approach to overcoming bacterial defense mechanisms, which has been not exploited. In this study, we report D‐chiral single‐atom iron–carbon dot nanozymes (DFe‐NSC) for effective bacterial infection treatment. Compared to L‐chiral form (LFe‐NSC), DFe‐NSC exhibits significantly higher peroxidase (POD)‐like and glutathione peroxidase (GPx)‐like activities. The enhanced catalytic activity promotes reactive oxygen species (ROS) generation and glutathione depletion, disrupting bacterial redox homeostasis. More intriguingly, DFe‐NSC more effectively modulates the expression and iron‐regulatory function of MTP (including Fur and FtnA) than LFe‐NSC. This will induce substantial accumulation of Fe 2 ⁺ intracellularly and thereafter lipid peroxidation, thereby facilitating the bactericidal effects of ferroptosis‐like cell death. Resultantly, DFe‐NSC exhibit markedly enhanced antibacterial and antibiofilm activities in diabetic infected wound and osteomyelitis models. This study introduces a chiral catalysis–MTP regulation strategy to induce bacterial ferroptosis‐like death, providing a promising alternative for drug‐resistant infection treatment.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>https://onlinelibrary.wiley.com/doi/10.1002/anie.202512579?af=R</t>
+          <t>https://advanced.onlinelibrary.wiley.com/doi/10.1002/adma.202518810?af=R</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -8690,53 +8529,57 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.2349510788917542</v>
+        <v>0.232131227850914</v>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="n">
-        <v>0.2091465592384338</v>
+        <v>0.1189228147268295</v>
       </c>
       <c r="K73" t="n">
-        <v>0.2109045386314392</v>
+        <v>0.05307762324810028</v>
       </c>
       <c r="L73" t="n">
-        <v>0.1739977896213531</v>
+        <v>0.08560404181480408</v>
       </c>
       <c r="M73" t="n">
-        <v>0.1897228062152863</v>
+        <v>0.07256678491830826</v>
       </c>
       <c r="N73" t="n">
-        <v>0.2349510788917542</v>
+        <v>0.232131227850914</v>
       </c>
       <c r="O73" t="n">
-        <v>0.1924907267093658</v>
+        <v>0.1086617112159729</v>
       </c>
       <c r="P73" t="n">
-        <v>0.06132102012634277</v>
+        <v>0.06126600503921509</v>
       </c>
       <c r="Q73" t="n">
-        <v>0.1255578994750977</v>
+        <v>0.04488996788859367</v>
       </c>
       <c r="R73" t="n">
-        <v>0.1464055478572845</v>
+        <v>0.01588337309658527</v>
       </c>
       <c r="S73" t="n">
-        <v>0.1269901245832443</v>
+        <v>0.07512816041707993</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Volatility modeling in energy commodity markets: A review of responses to shocks and the path towards resiliency and sustainability</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr"/>
+          <t>[ASAP] Covalent Adaptable Networks: Reprocessable Cross-Linked Polymers</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Thermoset polymers have desirable properties, such as excellent thermal and mechanical stability, but their covalent cross-links typically prevent repair or recycling. By enabling and controlling dynamic exchange reactions within polymer networks, their covalent bonds rearrange and allow the polymer to be reshaped. These viscoelastic polymer networks, now known as covalent adaptable networks (CANs), are an important frontier for improving plastic circularity, as well as for designing valuable stimuli-responsive materials. This Review describes the history of CANs, dating back to the early days of polymer science, and the evolution of their classification and nomenclature. A comprehensive survey of dynamic reactions and linkage chemistries is provided, as well as methods to characterize and reprocess CANs. Beyond straightforward reprocessing, many advanced applications of CANs and their composites are now emerging. Finally, we provide perspective on how the development of new chemistries, strategies to control stimuli-responsive bond exchange and mechanical properties, and a deep understanding of exchange reactions will advance this field toward scalable, sustainable, and high-value materials.</t>
+        </is>
+      </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>https://www.sciencedirect.com/science/article/pii/S0306261926002114?dgcid=rss_sd_all</t>
+          <t>http://dx.doi.org/10.1021/acs.chemrev.4c00994</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -8745,57 +8588,57 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.2336919009685516</v>
+        <v>0.2263173758983612</v>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="n">
-        <v>0.06262164562940598</v>
+        <v>0.1838305741548538</v>
       </c>
       <c r="K74" t="n">
-        <v>0.07224398106336594</v>
+        <v>0.2020614594221115</v>
       </c>
       <c r="L74" t="n">
-        <v>0.1314468383789062</v>
+        <v>0.2263173758983612</v>
       </c>
       <c r="M74" t="n">
-        <v>0.1139631271362305</v>
+        <v>0.1354841440916061</v>
       </c>
       <c r="N74" t="n">
-        <v>0.04860568791627884</v>
+        <v>0.1411776840686798</v>
       </c>
       <c r="O74" t="n">
-        <v>0.03298217430710793</v>
+        <v>0.1861944496631622</v>
       </c>
       <c r="P74" t="n">
-        <v>0.09166080504655838</v>
+        <v>0.08763619512319565</v>
       </c>
       <c r="Q74" t="n">
-        <v>0.06152238696813583</v>
+        <v>0.1530071049928665</v>
       </c>
       <c r="R74" t="n">
-        <v>0.1941447854042053</v>
+        <v>0.1291109025478363</v>
       </c>
       <c r="S74" t="n">
-        <v>0.2336919009685516</v>
+        <v>0.05065755918622017</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Chiral Single‐Atom Nanozymes‐Enabled ROS Catalysis and Metal Transport Regulation Cooperatively Induce Ferroptosis to Treat Bacterial Infections</t>
+          <t>Solubility‐pKa Coupling Effect Tailored Nanoporous Nylon Aerogel Family with Multiple Thermomechanical Processes</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>ABSTRACT Nanozyme‐driven ferroptosis provides a promising therapeutic strategy against drug‐resistant bacterial infections by inducing iron overload and oxidative stress. However, bacterial metal transport proteins (MTP) and antioxidant systems can reduce iron accumulation and lipid peroxidation, limiting the efficacy of ferroptosis‐based therapies and promoting resistance. Single‐atom and chiral nanozymes, with their high atomic utilization and catalytic specificity, may provide an effective approach to overcoming bacterial defense mechanisms, which has been not exploited. In this study, we report D‐chiral single‐atom iron–carbon dot nanozymes (DFe‐NSC) for effective bacterial infection treatment. Compared to L‐chiral form (LFe‐NSC), DFe‐NSC exhibits significantly higher peroxidase (POD)‐like and glutathione peroxidase (GPx)‐like activities. The enhanced catalytic activity promotes reactive oxygen species (ROS) generation and glutathione depletion, disrupting bacterial redox homeostasis. More intriguingly, DFe‐NSC more effectively modulates the expression and iron‐regulatory function of MTP (including Fur and FtnA) than LFe‐NSC. This will induce substantial accumulation of Fe 2 ⁺ intracellularly and thereafter lipid peroxidation, thereby facilitating the bactericidal effects of ferroptosis‐like cell death. Resultantly, DFe‐NSC exhibit markedly enhanced antibacterial and antibiofilm activities in diabetic infected wound and osteomyelitis models. This study introduces a chiral catalysis–MTP regulation strategy to induce bacterial ferroptosis‐like death, providing a promising alternative for drug‐resistant infection treatment.</t>
+          <t>Abstract Despite significant advancements in aerogels science, the fabrication of high‐performance aerogels with their plastic processability remains unexplored owing to their inherent trade‐off between skeletal rigidity and transformable processability. Herein, a universal solubility‐pKa coupling‐effect to engineer high‐performance thermoplastic nylon aerogel family with excellent thermomechanical processing performance is proposed. By modulating solubility parameters and acid dissociation constants in nylon‐solvent systems, it is precisely control crystallization to assemble interlaced 1D nanofiber skeletons, yielding nylon aerogels that integrate a high specific surface area (226 m 2 g −1 ), exceptional compressive modulus (12.6 MPa), and ultralow thermal conductivity (0.034 W m −1 K −1 ). Notably, beyond achieving performance comparable to aramid and other high‐performance aerogels, these nylon aerogels uniquely incorporate thermoplastic properties enabling multiple thermomechanical processing for aerogel functionalization, including protective barrier via thermal encapsulating, reassembly of aerogel unmanned aerial vehicle through thermal cutting and welding, and biomimetic hydrophobic surfaces with lotus and petal effects through precise thermal imprinting. Surprisingly, thermomechanical processing also induces fluorescence of aerogels, suggesting applications in thermal‐recording, anti‐counterfeiting, etc. This research overcomes the critical skeletal rigidity‐transformable processability trade‐off in aerogels, enabling novel manufacturing approaches and broader engineering applications.</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>https://advanced.onlinelibrary.wiley.com/doi/10.1002/adma.202518810?af=R</t>
+          <t>https://advanced.onlinelibrary.wiley.com/doi/10.1002/adma.202510031?af=R</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -8804,57 +8647,57 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.232131227850914</v>
+        <v>0.221360370516777</v>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="n">
-        <v>0.1189228147268295</v>
+        <v>0.1213804483413696</v>
       </c>
       <c r="K75" t="n">
-        <v>0.05307762324810028</v>
+        <v>0.1846737265586853</v>
       </c>
       <c r="L75" t="n">
-        <v>0.08560404181480408</v>
+        <v>0.06936901062726974</v>
       </c>
       <c r="M75" t="n">
-        <v>0.07256678491830826</v>
+        <v>0.1352435797452927</v>
       </c>
       <c r="N75" t="n">
-        <v>0.232131227850914</v>
+        <v>0.08894670754671097</v>
       </c>
       <c r="O75" t="n">
-        <v>0.1086617112159729</v>
+        <v>0.221360370516777</v>
       </c>
       <c r="P75" t="n">
-        <v>0.06126600503921509</v>
+        <v>-0.02459887228906155</v>
       </c>
       <c r="Q75" t="n">
-        <v>0.04488996788859367</v>
+        <v>0.1448809653520584</v>
       </c>
       <c r="R75" t="n">
-        <v>0.01588337309658527</v>
+        <v>0.03167451918125153</v>
       </c>
       <c r="S75" t="n">
-        <v>0.07512816041707993</v>
+        <v>0.0706821084022522</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>[ASAP] Covalent Adaptable Networks: Reprocessable Cross-Linked Polymers</t>
+          <t>Symmetry‐Breaking in Carbon Nanohoops Enables Room‐Temperature Ternary Single‐Molecule Switching</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Thermoset polymers have desirable properties, such as excellent thermal and mechanical stability, but their covalent cross-links typically prevent repair or recycling. By enabling and controlling dynamic exchange reactions within polymer networks, their covalent bonds rearrange and allow the polymer to be reshaped. These viscoelastic polymer networks, now known as covalent adaptable networks (CANs), are an important frontier for improving plastic circularity, as well as for designing valuable stimuli-responsive materials. This Review describes the history of CANs, dating back to the early days of polymer science, and the evolution of their classification and nomenclature. A comprehensive survey of dynamic reactions and linkage chemistries is provided, as well as methods to characterize and reprocess CANs. Beyond straightforward reprocessing, many advanced applications of CANs and their composites are now emerging. Finally, we provide perspective on how the development of new chemistries, strategies to control stimuli-responsive bond exchange and mechanical properties, and a deep understanding of exchange reactions will advance this field toward scalable, sustainable, and high-value materials.</t>
+          <t>Abstract Single‐molecule electronics offers chemically encoded routes to ultra‐dense information processing, yet room‐temperature operation is often limited to binary conductance states due to thermal broadening and electronic averaging. Here we demonstrate robust ternary switching at room temperature using symmetry‐engineered carbon nanohoops. Embedding a pyrene unit into the [12]cycloparaphenylene backbone via a symmetry‐breaking 1,6‐linkage disrupts the electronic equivalence of π –segments and localizes frontier orbitals. Under controlled mechanical elongation in single–molecule junctions, the molecule exhibits three well‐resolved conductance plateaus, each separated by ∼one order of magnitude, affording unambiguous and reproducible readout. First‐principles transport calculations reveal that symmetry‐breaking–induced orbital localization discretizes coherent tunneling pathways, accounting for the observed plateaus. These findings establish molecular symmetry control as a general design principle for room‐temperature multistate charge transport in conjugated macrocycles, opening a pathway to high‐density single‐molecule logic architectures.</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>http://dx.doi.org/10.1021/acs.chemrev.4c00994</t>
+          <t>https://onlinelibrary.wiley.com/doi/10.1002/anie.202519695?af=R</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -8863,57 +8706,57 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0.2263173758983612</v>
+        <v>0.2095107883214951</v>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="n">
-        <v>0.1838305741548538</v>
+        <v>0.2095107883214951</v>
       </c>
       <c r="K76" t="n">
-        <v>0.2020614594221115</v>
+        <v>0.1518478095531464</v>
       </c>
       <c r="L76" t="n">
-        <v>0.2263173758983612</v>
+        <v>0.1606944799423218</v>
       </c>
       <c r="M76" t="n">
-        <v>0.1354841440916061</v>
+        <v>0.07633987814188004</v>
       </c>
       <c r="N76" t="n">
-        <v>0.1411776840686798</v>
+        <v>0.1159767881035805</v>
       </c>
       <c r="O76" t="n">
-        <v>0.1861944496631622</v>
+        <v>0.1451735198497772</v>
       </c>
       <c r="P76" t="n">
-        <v>0.08763619512319565</v>
+        <v>0.1271640807390213</v>
       </c>
       <c r="Q76" t="n">
-        <v>0.1530071049928665</v>
+        <v>0.1401804089546204</v>
       </c>
       <c r="R76" t="n">
-        <v>0.1291109025478363</v>
+        <v>0.1098811328411102</v>
       </c>
       <c r="S76" t="n">
-        <v>0.05065755918622017</v>
+        <v>0.07377591729164124</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Solubility‐pKa Coupling Effect Tailored Nanoporous Nylon Aerogel Family with Multiple Thermomechanical Processes</t>
+          <t>Diverse polymers with chemical recyclability via regioirregular polymerization of a single monomer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Abstract Despite significant advancements in aerogels science, the fabrication of high‐performance aerogels with their plastic processability remains unexplored owing to their inherent trade‐off between skeletal rigidity and transformable processability. Herein, a universal solubility‐pKa coupling‐effect to engineer high‐performance thermoplastic nylon aerogel family with excellent thermomechanical processing performance is proposed. By modulating solubility parameters and acid dissociation constants in nylon‐solvent systems, it is precisely control crystallization to assemble interlaced 1D nanofiber skeletons, yielding nylon aerogels that integrate a high specific surface area (226 m 2 g −1 ), exceptional compressive modulus (12.6 MPa), and ultralow thermal conductivity (0.034 W m −1 K −1 ). Notably, beyond achieving performance comparable to aramid and other high‐performance aerogels, these nylon aerogels uniquely incorporate thermoplastic properties enabling multiple thermomechanical processing for aerogel functionalization, including protective barrier via thermal encapsulating, reassembly of aerogel unmanned aerial vehicle through thermal cutting and welding, and biomimetic hydrophobic surfaces with lotus and petal effects through precise thermal imprinting. Surprisingly, thermomechanical processing also induces fluorescence of aerogels, suggesting applications in thermal‐recording, anti‐counterfeiting, etc. This research overcomes the critical skeletal rigidity‐transformable processability trade‐off in aerogels, enabling novel manufacturing approaches and broader engineering applications.</t>
+          <t>The development of polymer products with a circular economy lifecycle represents a path to alleviate the growing plastic waste and energy crisis. However, long-standing challenges include synthesis scalability, tunable material performance and the feasibility of chemical recycling from mixed products. Here we developed a facile regioirregular polymerization strategy to access diverse polymer structures from a single monomer via regioselectivity and dynamic covalent bond exchange. We were able to synthesize polyurethanes (PUx, where x represents the percentage of urethane linkages in the polymer) with tailored urethane contents by modulating the reaction time for the regioirregular polymerization of tetramethylene urethane. The resulting PUx products showcase remarkable composition-dependent material performance, illustrating high strength, toughness and gas barriers comparable with commercial plastics. In particular, PU57 exhibits superior adhesive strength, outperforming commercial glues. Notably, these diverse PUx products could be converted back to a single monomer, representing a proof-of-concept process for a ‘single monomer ↔ multiple polymers’ closed loop.</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>https://advanced.onlinelibrary.wiley.com/doi/10.1002/adma.202510031?af=R</t>
+          <t>https://www.nature.com/articles/s41563-026-02498-6</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -8922,57 +8765,57 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>0.221360370516777</v>
+        <v>0.1911968737840652</v>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="n">
-        <v>0.1213804483413696</v>
+        <v>0.1911968737840652</v>
       </c>
       <c r="K77" t="n">
-        <v>0.1846737265586853</v>
+        <v>0.1347317397594452</v>
       </c>
       <c r="L77" t="n">
-        <v>0.06936901062726974</v>
+        <v>0.1896294206380844</v>
       </c>
       <c r="M77" t="n">
-        <v>0.1352435797452927</v>
+        <v>0.08985760062932968</v>
       </c>
       <c r="N77" t="n">
-        <v>0.08894670754671097</v>
+        <v>0.114510290324688</v>
       </c>
       <c r="O77" t="n">
-        <v>0.221360370516777</v>
+        <v>0.1655153334140778</v>
       </c>
       <c r="P77" t="n">
-        <v>-0.02459887228906155</v>
+        <v>0.07993254810571671</v>
       </c>
       <c r="Q77" t="n">
-        <v>0.1448809653520584</v>
+        <v>0.1289712935686111</v>
       </c>
       <c r="R77" t="n">
-        <v>0.03167451918125153</v>
+        <v>0.09573771804571152</v>
       </c>
       <c r="S77" t="n">
-        <v>0.0706821084022522</v>
+        <v>0.1300274133682251</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Symmetry‐Breaking in Carbon Nanohoops Enables Room‐Temperature Ternary Single‐Molecule Switching</t>
+          <t>title</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Abstract Single‐molecule electronics offers chemically encoded routes to ultra‐dense information processing, yet room‐temperature operation is often limited to binary conductance states due to thermal broadening and electronic averaging. Here we demonstrate robust ternary switching at room temperature using symmetry‐engineered carbon nanohoops. Embedding a pyrene unit into the [12]cycloparaphenylene backbone via a symmetry‐breaking 1,6‐linkage disrupts the electronic equivalence of π –segments and localizes frontier orbitals. Under controlled mechanical elongation in single–molecule junctions, the molecule exhibits three well‐resolved conductance plateaus, each separated by ∼one order of magnitude, affording unambiguous and reproducible readout. First‐principles transport calculations reveal that symmetry‐breaking–induced orbital localization discretizes coherent tunneling pathways, accounting for the observed plateaus. These findings establish molecular symmetry control as a general design principle for room‐temperature multistate charge transport in conjugated macrocycles, opening a pathway to high‐density single‐molecule logic architectures.</t>
+          <t>abstract</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>https://onlinelibrary.wiley.com/doi/10.1002/anie.202519695?af=R</t>
+          <t>link</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -8981,57 +8824,57 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.2095107883214951</v>
+        <v>0.1837555319070816</v>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr"/>
       <c r="J78" t="n">
-        <v>0.2095107883214951</v>
+        <v>0.1781131774187088</v>
       </c>
       <c r="K78" t="n">
-        <v>0.1518478095531464</v>
+        <v>0.1837555319070816</v>
       </c>
       <c r="L78" t="n">
-        <v>0.1606944799423218</v>
+        <v>0.1252067536115646</v>
       </c>
       <c r="M78" t="n">
-        <v>0.07633987814188004</v>
+        <v>0.1760801523923874</v>
       </c>
       <c r="N78" t="n">
-        <v>0.1159767881035805</v>
+        <v>0.1714162528514862</v>
       </c>
       <c r="O78" t="n">
-        <v>0.1451735198497772</v>
+        <v>0.1782511025667191</v>
       </c>
       <c r="P78" t="n">
-        <v>0.1271640807390213</v>
+        <v>0.1769502013921738</v>
       </c>
       <c r="Q78" t="n">
-        <v>0.1401804089546204</v>
+        <v>0.1222339496016502</v>
       </c>
       <c r="R78" t="n">
-        <v>0.1098811328411102</v>
+        <v>0.07555164396762848</v>
       </c>
       <c r="S78" t="n">
-        <v>0.07377591729164124</v>
+        <v>0.1570891588926315</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Diverse polymers with chemical recyclability via regioirregular polymerization of a single monomer</t>
+          <t>A Solid State Zwitterionic Plastic Crystal With High Static Dielectric Constant</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>The development of polymer products with a circular economy lifecycle represents a path to alleviate the growing plastic waste and energy crisis. However, long-standing challenges include synthesis scalability, tunable material performance and the feasibility of chemical recycling from mixed products. Here we developed a facile regioirregular polymerization strategy to access diverse polymer structures from a single monomer via regioselectivity and dynamic covalent bond exchange. We were able to synthesize polyurethanes (PUx, where x represents the percentage of urethane linkages in the polymer) with tailored urethane contents by modulating the reaction time for the regioirregular polymerization of tetramethylene urethane. The resulting PUx products showcase remarkable composition-dependent material performance, illustrating high strength, toughness and gas barriers comparable with commercial plastics. In particular, PU57 exhibits superior adhesive strength, outperforming commercial glues. Notably, these diverse PUx products could be converted back to a single monomer, representing a proof-of-concept process for a ‘single monomer ↔ multiple polymers’ closed loop.</t>
+          <t>ABSTRACT Solid materials with a high dielectric constant have a wide range of applications in the energy storage field. In this research, an imidazolium‐based zwitterion is designed, synthesized, and confirmed to have a plastic crystal phase based on the following experimental and computational evidence: (i) the presence of long‐range order with weak intermolecular forces and competing attractive‐repulsive interactions along different crystallographic directions; (ii) the observation of more than one endotherm on heating including a solid‐solid phase transition at T s‐s = −26 °C and melting of the plastic crystal at T m = 72°C; (iii) a low entropy of fusion at melting (2.1 JK −1 mol −1 ); (iv) a strongly anisotropic morphology; (v) relatively fast dynamics originating from short‐range degrees of freedom. Furthermore, it exhibits a very high dielectric constant in the plastic crystal solid state (147 at −10°C and 103 at 70°C) due to the rotational degrees of freedom of plastic crystals that arise from weak net intermolecular interactions of zwitterions due to only having two carbons between the anion and cation. This material conveniently remains in the plastic crystal phase within 50 K of ambient temperature. This discovery opens new opportunities in the search for solid‐state high dielectric constant materials.</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>https://www.nature.com/articles/s41563-026-02498-6</t>
+          <t>https://advanced.onlinelibrary.wiley.com/doi/10.1002/adma.202517774?af=R</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9040,57 +8883,57 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0.1911968737840652</v>
+        <v>0.1816605478525162</v>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
       <c r="J79" t="n">
-        <v>0.1911968737840652</v>
+        <v>0.1806739717721939</v>
       </c>
       <c r="K79" t="n">
-        <v>0.1347317397594452</v>
+        <v>0.1816605478525162</v>
       </c>
       <c r="L79" t="n">
-        <v>0.1896294206380844</v>
+        <v>0.1180452182888985</v>
       </c>
       <c r="M79" t="n">
-        <v>0.08985760062932968</v>
+        <v>0.1047593057155609</v>
       </c>
       <c r="N79" t="n">
-        <v>0.114510290324688</v>
+        <v>0.05048955604434013</v>
       </c>
       <c r="O79" t="n">
-        <v>0.1655153334140778</v>
+        <v>0.1089991182088852</v>
       </c>
       <c r="P79" t="n">
-        <v>0.07993254810571671</v>
+        <v>0.04414737597107887</v>
       </c>
       <c r="Q79" t="n">
-        <v>0.1289712935686111</v>
+        <v>0.1078207120299339</v>
       </c>
       <c r="R79" t="n">
-        <v>0.09573771804571152</v>
+        <v>0.0985962450504303</v>
       </c>
       <c r="S79" t="n">
-        <v>0.1300274133682251</v>
+        <v>0.0409858450293541</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>[ASAP] C–H Insertion Functionalization of Polyolefins for Versatile Polyolefin-Polyester Compatibilization</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>abstract</t>
+          <t>The effective recycling of commingled plastic waste blends remains a major challenge due to the immiscibility of commonly used polymers like polyethylene terephthalate (PET) with polyolefins, including high- or low-density polyethylene (HDPE, LDPE) and isotactic polypropylene (iPP). This immiscibility causes phase separation of the polymers in the blend, compromising the mechanical properties of these mixtures. Herein, we report a versatile and robust strategy to synthesize polar-group pendant polyolefins via C-H insertion from preexisting polymers, which can subsequently act as compatibilizers for blends of PET with different polyolefins. The addition of 0.5-1.0 wt % of these functionalized polyolefins to blends of PET with HDPE, LDPE, or iPP significantly improved the elongation at break, effectively restoring their material properties. This approach can be applied to prepare a compatibilizer from postconsumer HDPE bottlecaps. The waste derived compatibilizer effectively compatibilized postconsumer PET/HDPE blends, demonstrating the versatility of this method as a low-cost, efficient, and adaptable solution for restoring PET/polyolefin blend properties.</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>link</t>
+          <t>http://dx.doi.org/10.1021/jacs.5c20245</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9099,57 +8942,57 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.1837555319070816</v>
+        <v>0.1761684268712997</v>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="n">
-        <v>0.1781131774187088</v>
+        <v>0.1268492788076401</v>
       </c>
       <c r="K80" t="n">
-        <v>0.1837555319070816</v>
+        <v>0.1376067101955414</v>
       </c>
       <c r="L80" t="n">
-        <v>0.1252067536115646</v>
+        <v>0.1359664052724838</v>
       </c>
       <c r="M80" t="n">
-        <v>0.1760801523923874</v>
+        <v>0.0707365944981575</v>
       </c>
       <c r="N80" t="n">
-        <v>0.1714162528514862</v>
+        <v>0.0990336686372757</v>
       </c>
       <c r="O80" t="n">
-        <v>0.1782511025667191</v>
+        <v>0.1761684268712997</v>
       </c>
       <c r="P80" t="n">
-        <v>0.1769502013921738</v>
+        <v>0.03177925571799278</v>
       </c>
       <c r="Q80" t="n">
-        <v>0.1222339496016502</v>
+        <v>0.1589659452438354</v>
       </c>
       <c r="R80" t="n">
-        <v>0.07555164396762848</v>
+        <v>0.06546182930469513</v>
       </c>
       <c r="S80" t="n">
-        <v>0.1570891588926315</v>
+        <v>0.09014496207237244</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A Solid State Zwitterionic Plastic Crystal With High Static Dielectric Constant</t>
+          <t>Exploring the interplay between protein conformational changes and phosphorylation in a pancreatic cancer cell and stellate cell coculture system</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>ABSTRACT Solid materials with a high dielectric constant have a wide range of applications in the energy storage field. In this research, an imidazolium‐based zwitterion is designed, synthesized, and confirmed to have a plastic crystal phase based on the following experimental and computational evidence: (i) the presence of long‐range order with weak intermolecular forces and competing attractive‐repulsive interactions along different crystallographic directions; (ii) the observation of more than one endotherm on heating including a solid‐solid phase transition at T s‐s = −26 °C and melting of the plastic crystal at T m = 72°C; (iii) a low entropy of fusion at melting (2.1 JK −1 mol −1 ); (iv) a strongly anisotropic morphology; (v) relatively fast dynamics originating from short‐range degrees of freedom. Furthermore, it exhibits a very high dielectric constant in the plastic crystal solid state (147 at −10°C and 103 at 70°C) due to the rotational degrees of freedom of plastic crystals that arise from weak net intermolecular interactions of zwitterions due to only having two carbons between the anion and cation. This material conveniently remains in the plastic crystal phase within 50 K of ambient temperature. This discovery opens new opportunities in the search for solid‐state high dielectric constant materials.</t>
+          <t>A global exploration of the complex interplay between protein conformational changes and phosphorylation events in cell–cell interactions is crucial for understanding the dynamic nature of protein modifications. This understanding is essential for developing novel targeted therapies for pancreatic cancer, particularly in the context of interactions between pancreatic cancer cells (PCCs) and pancreatic stellate cells (PSCs). However, protein conformational changes that occur during PCCs–PSCs interactions remain poorly studied, and the relationship between these changes and phosphorylation is not well understood. Here, we present a comprehensive mass spectrometry–based study investigating the interplay between protein conformational alterations and phosphorylation in a coculture system of pancreatic ductal adenocarcinoma cells (PANC-1) and PSCs. Our results demonstrate that 435 proteins exhibiting conformational changes were detected during the coculture of PANC-1 with PSCs, primarily involving proteins associated with the tricarboxylic acid (TCA) cycle, glycolysis/gluconeogenesis, and carbon metabolism. Our findings also highlight a potential association between phosphorylation and protein conformational changes. Moreover, we identified five potential conformational targets, including ACLY, ACO1, ACO2, IDH1, and OGDH, which may provide valuable insights into the molecular pathways underlying gemcitabine resistance in pancreatic cancer. Overall, these results offer insights into protein conformational changes and their potential link to phosphorylation in the context of cancer-stromal cell interactions, paving the way for structure-based, targeted therapeutic strategies for pancreatic cancer treatment.</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>https://advanced.onlinelibrary.wiley.com/doi/10.1002/adma.202517774?af=R</t>
+          <t>https://www.pnas.org/doi/abs/10.1073/pnas.2511839122?mi=eymic2&amp;af=R&amp;access=on&amp;content=articlesChapters&amp;publication=pnas&amp;sortBy=Earliest&amp;target=default</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -9158,57 +9001,57 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.1816605478525162</v>
+        <v>0.161895290017128</v>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr"/>
       <c r="J81" t="n">
-        <v>0.1806739717721939</v>
+        <v>0.05211120471358299</v>
       </c>
       <c r="K81" t="n">
-        <v>0.1816605478525162</v>
+        <v>0.07579249143600464</v>
       </c>
       <c r="L81" t="n">
-        <v>0.1180452182888985</v>
+        <v>0.02999443002045155</v>
       </c>
       <c r="M81" t="n">
-        <v>0.1047593057155609</v>
+        <v>0.08000466972589493</v>
       </c>
       <c r="N81" t="n">
-        <v>0.05048955604434013</v>
+        <v>0.161895290017128</v>
       </c>
       <c r="O81" t="n">
-        <v>0.1089991182088852</v>
+        <v>0.02042846940457821</v>
       </c>
       <c r="P81" t="n">
-        <v>0.04414737597107887</v>
+        <v>0.04339658468961716</v>
       </c>
       <c r="Q81" t="n">
-        <v>0.1078207120299339</v>
+        <v>0.06656236201524734</v>
       </c>
       <c r="R81" t="n">
-        <v>0.0985962450504303</v>
+        <v>0.1232341155409813</v>
       </c>
       <c r="S81" t="n">
-        <v>0.0409858450293541</v>
+        <v>0.02215532213449478</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>[ASAP] C–H Insertion Functionalization of Polyolefins for Versatile Polyolefin-Polyester Compatibilization</t>
+          <t>Dislocation‐Enhanced Pyroelectricity in Barium Titanate</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>The effective recycling of commingled plastic waste blends remains a major challenge due to the immiscibility of commonly used polymers like polyethylene terephthalate (PET) with polyolefins, including high- or low-density polyethylene (HDPE, LDPE) and isotactic polypropylene (iPP). This immiscibility causes phase separation of the polymers in the blend, compromising the mechanical properties of these mixtures. Herein, we report a versatile and robust strategy to synthesize polar-group pendant polyolefins via C-H insertion from preexisting polymers, which can subsequently act as compatibilizers for blends of PET with different polyolefins. The addition of 0.5-1.0 wt % of these functionalized polyolefins to blends of PET with HDPE, LDPE, or iPP significantly improved the elongation at break, effectively restoring their material properties. This approach can be applied to prepare a compatibilizer from postconsumer HDPE bottlecaps. The waste derived compatibilizer effectively compatibilized postconsumer PET/HDPE blends, demonstrating the versatility of this method as a low-cost, efficient, and adaptable solution for restoring PET/polyolefin blend properties.</t>
+          <t>ABSTRACT Pyroelectric materials hold significant promise for thermal sensing, imaging, and energy harvesting, with the pyroelectric coefficient serving as the key figure of merit. While intrinsic lattice optimization, particularly through zero‐dimensional point defects, has improved pyroelectric properties, extrinsic contributions from mobile ferroelectric domain walls have remained underexplored. Here, a dislocation‐based one‐dimensional mechanical doping strategy is proposed to enhance the pyroelectric response of classical ferroelectric BaTiO 3 single crystals. By employing high‐temperature plastic deformation, anisotropic dislocation networks are produced that introduce localized stress concentrations and thermal expansion/contraction effects, which amplify domain‐wall motion. These directional strain fields, combined with phonon–dislocation interactions, lead to an anisotropic coupling of thermal and electrical fields. While the enhanced phonon scattering reduces thermal conductivity, the strong dislocation–domain‐wall coupling leads to an increase in the temperature sensitivity of polarization and accelerates domain switching, effectively compensating for the reduced heat transport. As a result, the maximum pyroelectric coefficient exceeds 600 nC cm − 2 K − 1 , representing a 38‐fold increase compared to the undeformed counterpart. Structural evolution is revealed by synchrotron scanning X‐ray diffraction microscopy and transmission electron microscopy, while multiscale phase‐field simulations corroborate the underlying mechanism. Our work establishes dislocation engineering as an effective new pathway towards domain‐wall‐mediated enhancement of pyroelectric functionality.</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>http://dx.doi.org/10.1021/jacs.5c20245</t>
+          <t>https://advanced.onlinelibrary.wiley.com/doi/10.1002/adma.202515988?af=R</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -9217,57 +9060,57 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>0.1761684268712997</v>
+        <v>0.1534859538078308</v>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="n">
-        <v>0.1268492788076401</v>
+        <v>0.1534859538078308</v>
       </c>
       <c r="K82" t="n">
-        <v>0.1376067101955414</v>
+        <v>0.09580280631780624</v>
       </c>
       <c r="L82" t="n">
-        <v>0.1359664052724838</v>
+        <v>0.06433564424514771</v>
       </c>
       <c r="M82" t="n">
-        <v>0.0707365944981575</v>
+        <v>0.1444400697946548</v>
       </c>
       <c r="N82" t="n">
-        <v>0.0990336686372757</v>
+        <v>-0.03753555938601494</v>
       </c>
       <c r="O82" t="n">
-        <v>0.1761684268712997</v>
+        <v>0.06979785859584808</v>
       </c>
       <c r="P82" t="n">
-        <v>0.03177925571799278</v>
+        <v>0.06430640071630478</v>
       </c>
       <c r="Q82" t="n">
-        <v>0.1589659452438354</v>
+        <v>-0.02559760399162769</v>
       </c>
       <c r="R82" t="n">
-        <v>0.06546182930469513</v>
+        <v>0.08169527351856232</v>
       </c>
       <c r="S82" t="n">
-        <v>0.09014496207237244</v>
+        <v>-0.003024180885404348</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Exploring the interplay between protein conformational changes and phosphorylation in a pancreatic cancer cell and stellate cell coculture system</t>
+          <t>One Collision – Two Heteroatoms: Gas‐Phase Preparation of Azasilabenzenes</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>A global exploration of the complex interplay between protein conformational changes and phosphorylation events in cell–cell interactions is crucial for understanding the dynamic nature of protein modifications. This understanding is essential for developing novel targeted therapies for pancreatic cancer, particularly in the context of interactions between pancreatic cancer cells (PCCs) and pancreatic stellate cells (PSCs). However, protein conformational changes that occur during PCCs–PSCs interactions remain poorly studied, and the relationship between these changes and phosphorylation is not well understood. Here, we present a comprehensive mass spectrometry–based study investigating the interplay between protein conformational alterations and phosphorylation in a coculture system of pancreatic ductal adenocarcinoma cells (PANC-1) and PSCs. Our results demonstrate that 435 proteins exhibiting conformational changes were detected during the coculture of PANC-1 with PSCs, primarily involving proteins associated with the tricarboxylic acid (TCA) cycle, glycolysis/gluconeogenesis, and carbon metabolism. Our findings also highlight a potential association between phosphorylation and protein conformational changes. Moreover, we identified five potential conformational targets, including ACLY, ACO1, ACO2, IDH1, and OGDH, which may provide valuable insights into the molecular pathways underlying gemcitabine resistance in pancreatic cancer. Overall, these results offer insights into protein conformational changes and their potential link to phosphorylation in the context of cancer-stromal cell interactions, paving the way for structure-based, targeted therapeutic strategies for pancreatic cancer treatment.</t>
+          <t>Abstract Nature has long favored cyclic, particularly heterocyclic, molecules in the synthesis of key biomolecules. Silicon‐substituted hydrocarbons have gained increasing attention due to their unique chemical bonding and electronic structure compared to their iso‐valent carbon counterparts. However, the synthesis of silicon‐containing heterocyclic molecules remains a significant challenge. In this work, we investigate the reaction mechanism leading to a sparsely explored class of silicon‐ and nitrogen‐containing aromatic heterocycles, in which silicon and nitrogen atoms are positioned adjacently within an aromatic, six‐membered ring: azasilabenzenes. This is achieved through the reaction of the silicon nitride (SiN) radical with 1,3‐butadiene (C 4 H 6 ) via single collision conditions, exploiting a crossed molecular beam experiment combined with electronic structure calculations and statistical analysis. Our results reveal the formation of two novel cyclic products: 1‐aza‐2‐silacyclohexa‐3,5‐dien‐2‐ylidene and 1‐aza‐2‐silabenzene. Interestingly, this reaction contrasts with the iso‐valent system involving the cyano radical (CN) and 1,3‐butadiene (C 4 H 6 ), which predominantly yields an acyclic product (1‐cyano‐1,3‐butadiene) via a simple addition–elimination pathway. In addition to elucidating the reaction pathways, this study also provides insights into the nature of bonding and atomic interactions in the resulting products, offering a deeper understanding of structure–stability relationships in silicon–nitrogen heterocycles and the counterintuitive concept of iso‐valency.</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>https://www.pnas.org/doi/abs/10.1073/pnas.2511839122?mi=eymic2&amp;af=R&amp;access=on&amp;content=articlesChapters&amp;publication=pnas&amp;sortBy=Earliest&amp;target=default</t>
+          <t>https://onlinelibrary.wiley.com/doi/10.1002/anie.202517656?af=R</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -9276,57 +9119,57 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0.161895290017128</v>
+        <v>0.1487667560577393</v>
       </c>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="n">
-        <v>0.05211120471358299</v>
+        <v>0.1487667560577393</v>
       </c>
       <c r="K83" t="n">
-        <v>0.07579249143600464</v>
+        <v>0.1213658154010773</v>
       </c>
       <c r="L83" t="n">
-        <v>0.02999443002045155</v>
+        <v>0.1148499995470047</v>
       </c>
       <c r="M83" t="n">
-        <v>0.08000466972589493</v>
+        <v>0.04759219288825989</v>
       </c>
       <c r="N83" t="n">
-        <v>0.161895290017128</v>
+        <v>0.1115637347102165</v>
       </c>
       <c r="O83" t="n">
-        <v>0.02042846940457821</v>
+        <v>0.04522985592484474</v>
       </c>
       <c r="P83" t="n">
-        <v>0.04339658468961716</v>
+        <v>0.03295443579554558</v>
       </c>
       <c r="Q83" t="n">
-        <v>0.06656236201524734</v>
+        <v>0.1272771954536438</v>
       </c>
       <c r="R83" t="n">
-        <v>0.1232341155409813</v>
+        <v>0.09581301361322403</v>
       </c>
       <c r="S83" t="n">
-        <v>0.02215532213449478</v>
+        <v>0.002023812150582671</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Dislocation‐Enhanced Pyroelectricity in Barium Titanate</t>
+          <t>[ASAP] Mapping the Undirected Borylation of C(sp3)–H Bonds in Strained Rings</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>ABSTRACT Pyroelectric materials hold significant promise for thermal sensing, imaging, and energy harvesting, with the pyroelectric coefficient serving as the key figure of merit. While intrinsic lattice optimization, particularly through zero‐dimensional point defects, has improved pyroelectric properties, extrinsic contributions from mobile ferroelectric domain walls have remained underexplored. Here, a dislocation‐based one‐dimensional mechanical doping strategy is proposed to enhance the pyroelectric response of classical ferroelectric BaTiO 3 single crystals. By employing high‐temperature plastic deformation, anisotropic dislocation networks are produced that introduce localized stress concentrations and thermal expansion/contraction effects, which amplify domain‐wall motion. These directional strain fields, combined with phonon–dislocation interactions, lead to an anisotropic coupling of thermal and electrical fields. While the enhanced phonon scattering reduces thermal conductivity, the strong dislocation–domain‐wall coupling leads to an increase in the temperature sensitivity of polarization and accelerates domain switching, effectively compensating for the reduced heat transport. As a result, the maximum pyroelectric coefficient exceeds 600 nC cm − 2 K − 1 , representing a 38‐fold increase compared to the undeformed counterpart. Structural evolution is revealed by synchrotron scanning X‐ray diffraction microscopy and transmission electron microscopy, while multiscale phase‐field simulations corroborate the underlying mechanism. Our work establishes dislocation engineering as an effective new pathway towards domain‐wall‐mediated enhancement of pyroelectric functionality.</t>
+          <t>Aliphatic small saturated carbocycles and azacycles are increasingly used as bioisosteres and structural cores in medicinally active compounds due to the beneficial pharmacological and physicochemical properties they can impart. Therefore, a need exists to modify these motifs and to install groups that enable their incorporation into organic structures; these goals can be accomplished by introducing functional groups at the position of the C-H bonds on the rings. However, functionalization of secondary C-H bonds in strained rings, such as cyclopropanes and cyclobutanes, confronts several challenges, including the greater strength of these bonds than those in unstrained rings. Although catalytic, undirected borylation has been reported to functionalize the C-H bonds of selected strained rings, the examples of such reactions in earlier studies are limited in scope, principally involving rings with a small number and size of substituents. We report the borylation of fused, spirocyclic, and polysubstituted cyclopropanes, cyclobutanes, azetidines, and β-lactams with high diastereoselectivity with the most recent generation of catalysts for the borylation of alkyl C-H bonds. Important for the formation of more complex structures, reactions occur, unlike reactions of larger rings, with steric hindrance on adjacent carbon atoms. The stoichiometry of the diboron reagent, the s-character of the C-H bond, and the disposition of substituents influence reactivity and product distribution in ways charted by our results. With these advances, the borylation of C-H bonds becomes a viable approach for the modification and incorporation of these ring systems into pharmaceutically active structures.</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>https://advanced.onlinelibrary.wiley.com/doi/10.1002/adma.202515988?af=R</t>
+          <t>http://dx.doi.org/10.1021/jacs.5c18839</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -9335,57 +9178,57 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0.1534859538078308</v>
+        <v>0.1273094713687897</v>
       </c>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="n">
-        <v>0.1534859538078308</v>
+        <v>0.1263929158449173</v>
       </c>
       <c r="K84" t="n">
-        <v>0.09580280631780624</v>
+        <v>0.1154774278402328</v>
       </c>
       <c r="L84" t="n">
-        <v>0.06433564424514771</v>
+        <v>0.1072105765342712</v>
       </c>
       <c r="M84" t="n">
-        <v>0.1444400697946548</v>
+        <v>0.06887877732515335</v>
       </c>
       <c r="N84" t="n">
-        <v>-0.03753555938601494</v>
+        <v>0.1273094713687897</v>
       </c>
       <c r="O84" t="n">
-        <v>0.06979785859584808</v>
+        <v>0.1087315306067467</v>
       </c>
       <c r="P84" t="n">
-        <v>0.06430640071630478</v>
+        <v>0.02979258447885513</v>
       </c>
       <c r="Q84" t="n">
-        <v>-0.02559760399162769</v>
+        <v>0.0494120679795742</v>
       </c>
       <c r="R84" t="n">
-        <v>0.08169527351856232</v>
+        <v>0.08654410392045975</v>
       </c>
       <c r="S84" t="n">
-        <v>-0.003024180885404348</v>
+        <v>0.07190725207328796</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>One Collision – Two Heteroatoms: Gas‐Phase Preparation of Azasilabenzenes</t>
+          <t>Dietary folic acid prevents peripheral neuropathy in mouse models of neural tube defects and type 2 diabetes</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Abstract Nature has long favored cyclic, particularly heterocyclic, molecules in the synthesis of key biomolecules. Silicon‐substituted hydrocarbons have gained increasing attention due to their unique chemical bonding and electronic structure compared to their iso‐valent carbon counterparts. However, the synthesis of silicon‐containing heterocyclic molecules remains a significant challenge. In this work, we investigate the reaction mechanism leading to a sparsely explored class of silicon‐ and nitrogen‐containing aromatic heterocycles, in which silicon and nitrogen atoms are positioned adjacently within an aromatic, six‐membered ring: azasilabenzenes. This is achieved through the reaction of the silicon nitride (SiN) radical with 1,3‐butadiene (C 4 H 6 ) via single collision conditions, exploiting a crossed molecular beam experiment combined with electronic structure calculations and statistical analysis. Our results reveal the formation of two novel cyclic products: 1‐aza‐2‐silacyclohexa‐3,5‐dien‐2‐ylidene and 1‐aza‐2‐silabenzene. Interestingly, this reaction contrasts with the iso‐valent system involving the cyano radical (CN) and 1,3‐butadiene (C 4 H 6 ), which predominantly yields an acyclic product (1‐cyano‐1,3‐butadiene) via a simple addition–elimination pathway. In addition to elucidating the reaction pathways, this study also provides insights into the nature of bonding and atomic interactions in the resulting products, offering a deeper understanding of structure–stability relationships in silicon–nitrogen heterocycles and the counterintuitive concept of iso‐valency.</t>
+          <t>Folate-mediated one-carbon metabolism is implicated in several pathologies including neural tube defects (NTDs), cancer, and neurodegenerative disorders, whereas diabetes is associated with NTDs and peripheral neuropathy (PN). The development of peripheral neuropathy was assessed in Shmt1 +/− and Shmt1 −/− mice, which are models of human folic acid–responsive NTDs, and diabetic ( Lepr db ) mice to determine whether NTDs and PN have a shared etiology. From 6 wk of age, male and female mice with reduced Shmt1 expression exhibited PN, with greater severity in females compared to males. The neuropathic progression was distinct from diabetic peripheral neuropathy (DPN) observed in Lepr db mice. Excess dietary folic acid prevented PN in both Shmt1 −/− and Lepr db/db mice, whereas dietary uridine caused demyelinating PN in mice independent of genotype and folate status. The transcriptome from L3-L5 dorsal root ganglia (DRG) exhibited distinct sex-specific differences in glial cell gene expression when comparing Shmt1 +/+ and Shmt1 −/− mice. DRG sensory neurons exhibited changes in the expression of solute carriers and ion channels involved in nociception, neurotransmission, and structural support. We conclude that reduced thymidylate synthesis causes folic acid–responsive NTDs and PN in mice and that diabetes sensitizes mice to folic acid–responsive PN. Diabetes induces a special nutritional requirement for high intake of folic acid to prevent PN.</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>https://onlinelibrary.wiley.com/doi/10.1002/anie.202517656?af=R</t>
+          <t>https://www.pnas.org/doi/abs/10.1073/pnas.2528095123?mi=eymic2&amp;af=R&amp;access=on&amp;content=articlesChapters&amp;publication=pnas&amp;sortBy=Earliest&amp;target=default</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -9394,57 +9237,57 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0.1487667560577393</v>
+        <v>0.120154120028019</v>
       </c>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="n">
-        <v>0.1487667560577393</v>
+        <v>-0.02468348853290081</v>
       </c>
       <c r="K85" t="n">
-        <v>0.1213658154010773</v>
+        <v>-0.01601581647992134</v>
       </c>
       <c r="L85" t="n">
-        <v>0.1148499995470047</v>
+        <v>0.04772863537073135</v>
       </c>
       <c r="M85" t="n">
-        <v>0.04759219288825989</v>
+        <v>-0.04878760129213333</v>
       </c>
       <c r="N85" t="n">
-        <v>0.1115637347102165</v>
+        <v>0.1006942018866539</v>
       </c>
       <c r="O85" t="n">
-        <v>0.04522985592484474</v>
+        <v>0.07521982491016388</v>
       </c>
       <c r="P85" t="n">
-        <v>0.03295443579554558</v>
+        <v>-0.004685353022068739</v>
       </c>
       <c r="Q85" t="n">
-        <v>0.1272771954536438</v>
+        <v>0.06158514320850372</v>
       </c>
       <c r="R85" t="n">
-        <v>0.09581301361322403</v>
+        <v>0.120154120028019</v>
       </c>
       <c r="S85" t="n">
-        <v>0.002023812150582671</v>
+        <v>-0.04305624961853027</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>[ASAP] Mapping the Undirected Borylation of C(sp3)–H Bonds in Strained Rings</t>
+          <t>Localized Gradient Conductivity Enabled Ultrasensitive Flexible Tactile Sensors with Ultrawide Linearity Range</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Aliphatic small saturated carbocycles and azacycles are increasingly used as bioisosteres and structural cores in medicinally active compounds due to the beneficial pharmacological and physicochemical properties they can impart. Therefore, a need exists to modify these motifs and to install groups that enable their incorporation into organic structures; these goals can be accomplished by introducing functional groups at the position of the C-H bonds on the rings. However, functionalization of secondary C-H bonds in strained rings, such as cyclopropanes and cyclobutanes, confronts several challenges, including the greater strength of these bonds than those in unstrained rings. Although catalytic, undirected borylation has been reported to functionalize the C-H bonds of selected strained rings, the examples of such reactions in earlier studies are limited in scope, principally involving rings with a small number and size of substituents. We report the borylation of fused, spirocyclic, and polysubstituted cyclopropanes, cyclobutanes, azetidines, and β-lactams with high diastereoselectivity with the most recent generation of catalysts for the borylation of alkyl C-H bonds. Important for the formation of more complex structures, reactions occur, unlike reactions of larger rings, with steric hindrance on adjacent carbon atoms. The stoichiometry of the diboron reagent, the s-character of the C-H bond, and the disposition of substituents influence reactivity and product distribution in ways charted by our results. With these advances, the borylation of C-H bonds becomes a viable approach for the modification and incorporation of these ring systems into pharmaceutically active structures.</t>
+          <t>Abstract The high sensitivity and wide linearity are crucial for flexible tactile sensors in adapting to diverse application scenarios with high accuracy and reliability. However, conventional optimization strategies of constructing microstructures suffer from the mutual restriction between the high sensitivity and wide linearity. Herein, a novel design of localized gradient conductivity (LGC) with partly covered low‐conductivity (low‐ σ ) carbon/Polydimethylsiloxane layer on high‐conductivity (high‐ σ ) silver nanowires film upon the micro‐dome structure is proposed. The LGC configuration enables a unique pressure‐motivated series‐parallel switching to allow the low‐ σ and high‐ σ components to separately take dominant effects in different pressure ranges. The ultrawide linearity can thus be realized by customizing the segmented linear current variation via the rationally associated coverage degree and conductivity gradient of the low‐ σ and high‐ σ components. Moreover, the ultrahigh sensitivity can be originally endowed by the conductivity difference between the low‐ σ and high‐ σ components without compromising linearity. The optimized sensor exhibits an ultrahigh sensitivity of 1546.35 kPa −1 within an ultrabroad linear sensing range of 0–3000 kPa, which is first reported. With such an excellent sensing performance, the potential applications, e.g., reliable healthcare monitoring, convenient smart home control, and ground detection of intelligent vehicles, are successfully demonstrated.</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>http://dx.doi.org/10.1021/jacs.5c18839</t>
+          <t>https://advanced.onlinelibrary.wiley.com/doi/10.1002/adma.202511275?af=R</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -9453,158 +9296,40 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>0.1273094713687897</v>
+        <v>0.1064260080456734</v>
       </c>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="n">
-        <v>0.1263929158449173</v>
+        <v>0.0242091566324234</v>
       </c>
       <c r="K86" t="n">
-        <v>0.1154774278402328</v>
+        <v>-0.05577149614691734</v>
       </c>
       <c r="L86" t="n">
-        <v>0.1072105765342712</v>
+        <v>0.04980719834566116</v>
       </c>
       <c r="M86" t="n">
-        <v>0.06887877732515335</v>
+        <v>-0.08281034231185913</v>
       </c>
       <c r="N86" t="n">
-        <v>0.1273094713687897</v>
+        <v>-0.02618293277919292</v>
       </c>
       <c r="O86" t="n">
-        <v>0.1087315306067467</v>
+        <v>0.0585050918161869</v>
       </c>
       <c r="P86" t="n">
-        <v>0.02979258447885513</v>
+        <v>0.04823269322514534</v>
       </c>
       <c r="Q86" t="n">
-        <v>0.0494120679795742</v>
+        <v>0.1064260080456734</v>
       </c>
       <c r="R86" t="n">
-        <v>0.08654410392045975</v>
+        <v>0.04569581896066666</v>
       </c>
       <c r="S86" t="n">
-        <v>0.07190725207328796</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Dietary folic acid prevents peripheral neuropathy in mouse models of neural tube defects and type 2 diabetes</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Folate-mediated one-carbon metabolism is implicated in several pathologies including neural tube defects (NTDs), cancer, and neurodegenerative disorders, whereas diabetes is associated with NTDs and peripheral neuropathy (PN). The development of peripheral neuropathy was assessed in Shmt1 +/− and Shmt1 −/− mice, which are models of human folic acid–responsive NTDs, and diabetic ( Lepr db ) mice to determine whether NTDs and PN have a shared etiology. From 6 wk of age, male and female mice with reduced Shmt1 expression exhibited PN, with greater severity in females compared to males. The neuropathic progression was distinct from diabetic peripheral neuropathy (DPN) observed in Lepr db mice. Excess dietary folic acid prevented PN in both Shmt1 −/− and Lepr db/db mice, whereas dietary uridine caused demyelinating PN in mice independent of genotype and folate status. The transcriptome from L3-L5 dorsal root ganglia (DRG) exhibited distinct sex-specific differences in glial cell gene expression when comparing Shmt1 +/+ and Shmt1 −/− mice. DRG sensory neurons exhibited changes in the expression of solute carriers and ion channels involved in nociception, neurotransmission, and structural support. We conclude that reduced thymidylate synthesis causes folic acid–responsive NTDs and PN in mice and that diabetes sensitizes mice to folic acid–responsive PN. Diabetes induces a special nutritional requirement for high intake of folic acid to prevent PN.</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>https://www.pnas.org/doi/abs/10.1073/pnas.2528095123?mi=eymic2&amp;af=R&amp;access=on&amp;content=articlesChapters&amp;publication=pnas&amp;sortBy=Earliest&amp;target=default</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="E87" t="n">
-        <v>0.120154120028019</v>
-      </c>
-      <c r="F87" t="inlineStr"/>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
-      <c r="I87" t="inlineStr"/>
-      <c r="J87" t="n">
-        <v>-0.02468348853290081</v>
-      </c>
-      <c r="K87" t="n">
-        <v>-0.01601581647992134</v>
-      </c>
-      <c r="L87" t="n">
-        <v>0.04772863537073135</v>
-      </c>
-      <c r="M87" t="n">
-        <v>-0.04878760129213333</v>
-      </c>
-      <c r="N87" t="n">
-        <v>0.1006942018866539</v>
-      </c>
-      <c r="O87" t="n">
-        <v>0.07521982491016388</v>
-      </c>
-      <c r="P87" t="n">
-        <v>-0.004685353022068739</v>
-      </c>
-      <c r="Q87" t="n">
-        <v>0.06158514320850372</v>
-      </c>
-      <c r="R87" t="n">
-        <v>0.120154120028019</v>
-      </c>
-      <c r="S87" t="n">
-        <v>-0.04305624961853027</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Localized Gradient Conductivity Enabled Ultrasensitive Flexible Tactile Sensors with Ultrawide Linearity Range</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Abstract The high sensitivity and wide linearity are crucial for flexible tactile sensors in adapting to diverse application scenarios with high accuracy and reliability. However, conventional optimization strategies of constructing microstructures suffer from the mutual restriction between the high sensitivity and wide linearity. Herein, a novel design of localized gradient conductivity (LGC) with partly covered low‐conductivity (low‐ σ ) carbon/Polydimethylsiloxane layer on high‐conductivity (high‐ σ ) silver nanowires film upon the micro‐dome structure is proposed. The LGC configuration enables a unique pressure‐motivated series‐parallel switching to allow the low‐ σ and high‐ σ components to separately take dominant effects in different pressure ranges. The ultrawide linearity can thus be realized by customizing the segmented linear current variation via the rationally associated coverage degree and conductivity gradient of the low‐ σ and high‐ σ components. Moreover, the ultrahigh sensitivity can be originally endowed by the conductivity difference between the low‐ σ and high‐ σ components without compromising linearity. The optimized sensor exhibits an ultrahigh sensitivity of 1546.35 kPa −1 within an ultrabroad linear sensing range of 0–3000 kPa, which is first reported. With such an excellent sensing performance, the potential applications, e.g., reliable healthcare monitoring, convenient smart home control, and ground detection of intelligent vehicles, are successfully demonstrated.</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>https://advanced.onlinelibrary.wiley.com/doi/10.1002/adma.202511275?af=R</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="E88" t="n">
-        <v>0.1064260080456734</v>
-      </c>
-      <c r="F88" t="inlineStr"/>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
-      <c r="I88" t="inlineStr"/>
-      <c r="J88" t="n">
-        <v>0.0242091566324234</v>
-      </c>
-      <c r="K88" t="n">
-        <v>-0.05577149614691734</v>
-      </c>
-      <c r="L88" t="n">
-        <v>0.04980719834566116</v>
-      </c>
-      <c r="M88" t="n">
-        <v>-0.08281034231185913</v>
-      </c>
-      <c r="N88" t="n">
-        <v>-0.02618293277919292</v>
-      </c>
-      <c r="O88" t="n">
-        <v>0.0585050918161869</v>
-      </c>
-      <c r="P88" t="n">
-        <v>0.04823269322514534</v>
-      </c>
-      <c r="Q88" t="n">
-        <v>0.1064260080456734</v>
-      </c>
-      <c r="R88" t="n">
-        <v>0.04569581896066666</v>
-      </c>
-      <c r="S88" t="n">
         <v>0.01533645112067461</v>
       </c>
     </row>
@@ -18636,7 +18361,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S9"/>
+  <dimension ref="A1:S8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19141,13 +18866,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Wirral Council Urges UK Government to Scrap Peak Cluster CO2 Pipeline</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
+          <t>[ASAP] Manipulating Terminal Iron-Hydroxide Nucleophilicity through Redox</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>We report changes in the reactivity profile of a high-spin, terminal ferrous hydroxo complex (EmL)Fe(OH) as a function of oxidation states (i.e., FeII/FeIII). The terminal, high-spin Fe-OH adducts were isolated within a sterically hindered dipyrrin ligand scaffold. In the ferrous state, (EmL)Fe(OH) exhibits nucleophilic reactivity toward carbon-based electrophiles (e.g., CS2, CO2, nitrile, isocyanate), highlighted by the reversible capture of CO2 to generate (EmL)Fe(κ2-O,O-HCO3) (ΔG° = -2.0 kcal/mol) both in solution and solid state as characterized by single-crystal X-ray crystallography, 57Fe Mössbauer spectroscopy, and IR spectroscopy. We probed the nucleophilic character of ferrous analogues with different terminal ligand motifs (X: -CH3, -NH2, -F, -SH, -H) through a comparison of their reactivity with CO2. In contrast to the nucleophilic character exhibited by (EmL)FeII(OH), its high-spin ferric analogue (EmL)FeIIII(OH) exhibited electrophilic reactivity at the hydroxo ligand, undergoing radical recombination with carboradicals, akin to the radical recombination reactivity observed in hydroxylation from high-valent iron oxenoids. These results highlight the effect of the oxidation level, ligand electronegativity, and basicity on the resulting nucleophilic/electrophilic character of the terminal Fe-X pair.</t>
+        </is>
+      </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://carbonherald.com/wirral-council-urges-uk-government-to-scrap-peak-cluster-co2-pipeline/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=wirral-council-urges-uk-government-to-scrap-peak-cluster-co2-pipeline</t>
+          <t>http://dx.doi.org/10.1021/jacs.5c20166</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -19156,7 +18885,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.3971229791641235</v>
+        <v>0.2864716351032257</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -19171,100 +18900,33 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="n">
-        <v>0.3173895478248596</v>
+        <v>0.2185826450586319</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3247024416923523</v>
+        <v>0.1418805718421936</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2890971899032593</v>
+        <v>0.2466033697128296</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3588145673274994</v>
+        <v>0.1980430036783218</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3082621693611145</v>
+        <v>0.2864716351032257</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3166796565055847</v>
+        <v>0.1758526414632797</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3971229791641235</v>
+        <v>0.08759931474924088</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.3682575523853302</v>
+        <v>0.09547864645719528</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3371207714080811</v>
+        <v>0.07003553211688995</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3637785911560059</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>[ASAP] Manipulating Terminal Iron-Hydroxide Nucleophilicity through Redox</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>We report changes in the reactivity profile of a high-spin, terminal ferrous hydroxo complex (EmL)Fe(OH) as a function of oxidation states (i.e., FeII/FeIII). The terminal, high-spin Fe-OH adducts were isolated within a sterically hindered dipyrrin ligand scaffold. In the ferrous state, (EmL)Fe(OH) exhibits nucleophilic reactivity toward carbon-based electrophiles (e.g., CS2, CO2, nitrile, isocyanate), highlighted by the reversible capture of CO2 to generate (EmL)Fe(κ2-O,O-HCO3) (ΔG° = -2.0 kcal/mol) both in solution and solid state as characterized by single-crystal X-ray crystallography, 57Fe Mössbauer spectroscopy, and IR spectroscopy. We probed the nucleophilic character of ferrous analogues with different terminal ligand motifs (X: -CH3, -NH2, -F, -SH, -H) through a comparison of their reactivity with CO2. In contrast to the nucleophilic character exhibited by (EmL)FeII(OH), its high-spin ferric analogue (EmL)FeIIII(OH) exhibited electrophilic reactivity at the hydroxo ligand, undergoing radical recombination with carboradicals, akin to the radical recombination reactivity observed in hydroxylation from high-valent iron oxenoids. These results highlight the effect of the oxidation level, ligand electronegativity, and basicity on the resulting nucleophilic/electrophilic character of the terminal Fe-X pair.</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>http://dx.doi.org/10.1021/jacs.5c20166</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>CO₂运输与封存</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>0.2864716351032257</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>CO₂运输与封存</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>storage_transport_keywords</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="n">
-        <v>0.2185826450586319</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.1418805718421936</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.2466033697128296</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0.1980430036783218</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0.2864716351032257</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0.1758526414632797</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0.08759931474924088</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0.09547864645719528</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0.07003553211688995</v>
-      </c>
-      <c r="S9" t="n">
         <v>0.01209958177059889</v>
       </c>
     </row>
